--- a/docs/feature_status_tracker.xlsx
+++ b/docs/feature_status_tracker.xlsx
@@ -11,8 +11,9 @@
     <sheet name="Features" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Sub-features" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Phase Gate" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Risks" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Change Log" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Brand Needs" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Risks" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Change Log" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -613,27 +614,27 @@
         </is>
       </c>
       <c r="B5" s="4">
-        <f>COUNTIF('Features'!$E$3:$E$57,"Alpha")</f>
+        <f>COUNTIF('Features'!$E$3:$E$61,"Alpha")</f>
         <v/>
       </c>
       <c r="C5" s="4">
-        <f>COUNTIFS('Features'!$E$3:$E$57,"Alpha",'Features'!$G$3:$G$57,"complete")</f>
+        <f>COUNTIFS('Features'!$E$3:$E$61,"Alpha",'Features'!$G$3:$G$61,"complete")</f>
         <v/>
       </c>
       <c r="D5" s="4">
-        <f>COUNTIFS('Features'!$E$3:$E$57,"Alpha",'Features'!$G$3:$G$57,"in_progress")+COUNTIFS('Features'!$E$3:$E$57,"Alpha",'Features'!$G$3:$G$57,"in_review")</f>
+        <f>COUNTIFS('Features'!$E$3:$E$61,"Alpha",'Features'!$G$3:$G$61,"in_progress")+COUNTIFS('Features'!$E$3:$E$61,"Alpha",'Features'!$G$3:$G$61,"in_review")</f>
         <v/>
       </c>
       <c r="E5" s="4">
-        <f>COUNTIFS('Features'!$E$3:$E$57,"Alpha",'Features'!$G$3:$G$57,"blocked")</f>
+        <f>COUNTIFS('Features'!$E$3:$E$61,"Alpha",'Features'!$G$3:$G$61,"blocked")</f>
         <v/>
       </c>
       <c r="F5" s="4">
-        <f>COUNTIFS('Features'!$E$3:$E$57,"Alpha",'Features'!$G$3:$G$57,"not_started")</f>
+        <f>COUNTIFS('Features'!$E$3:$E$61,"Alpha",'Features'!$G$3:$G$61,"not_started")</f>
         <v/>
       </c>
       <c r="G5" s="5">
-        <f>IFERROR(ROUND(SUMIFS('Features'!$H$3:$H$57,'Features'!$E$3:$E$57,"Alpha")/(B5*100),3),0)</f>
+        <f>IFERROR(ROUND(SUMIFS('Features'!$H$3:$H$61,'Features'!$E$3:$E$61,"Alpha")/(B5*100),3),0)</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -648,27 +649,27 @@
         </is>
       </c>
       <c r="B6" s="4">
-        <f>COUNTIF('Features'!$E$3:$E$57,"Beta")</f>
+        <f>COUNTIF('Features'!$E$3:$E$61,"Beta")</f>
         <v/>
       </c>
       <c r="C6" s="4">
-        <f>COUNTIFS('Features'!$E$3:$E$57,"Beta",'Features'!$G$3:$G$57,"complete")</f>
+        <f>COUNTIFS('Features'!$E$3:$E$61,"Beta",'Features'!$G$3:$G$61,"complete")</f>
         <v/>
       </c>
       <c r="D6" s="4">
-        <f>COUNTIFS('Features'!$E$3:$E$57,"Beta",'Features'!$G$3:$G$57,"in_progress")+COUNTIFS('Features'!$E$3:$E$57,"Beta",'Features'!$G$3:$G$57,"in_review")</f>
+        <f>COUNTIFS('Features'!$E$3:$E$61,"Beta",'Features'!$G$3:$G$61,"in_progress")+COUNTIFS('Features'!$E$3:$E$61,"Beta",'Features'!$G$3:$G$61,"in_review")</f>
         <v/>
       </c>
       <c r="E6" s="4">
-        <f>COUNTIFS('Features'!$E$3:$E$57,"Beta",'Features'!$G$3:$G$57,"blocked")</f>
+        <f>COUNTIFS('Features'!$E$3:$E$61,"Beta",'Features'!$G$3:$G$61,"blocked")</f>
         <v/>
       </c>
       <c r="F6" s="4">
-        <f>COUNTIFS('Features'!$E$3:$E$57,"Beta",'Features'!$G$3:$G$57,"not_started")</f>
+        <f>COUNTIFS('Features'!$E$3:$E$61,"Beta",'Features'!$G$3:$G$61,"not_started")</f>
         <v/>
       </c>
       <c r="G6" s="5">
-        <f>IFERROR(ROUND(SUMIFS('Features'!$H$3:$H$57,'Features'!$E$3:$E$57,"Beta")/(B6*100),3),0)</f>
+        <f>IFERROR(ROUND(SUMIFS('Features'!$H$3:$H$61,'Features'!$E$3:$E$61,"Beta")/(B6*100),3),0)</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -683,27 +684,27 @@
         </is>
       </c>
       <c r="B7" s="4">
-        <f>COUNTIF('Features'!$E$3:$E$57,"GA")</f>
+        <f>COUNTIF('Features'!$E$3:$E$61,"GA")</f>
         <v/>
       </c>
       <c r="C7" s="4">
-        <f>COUNTIFS('Features'!$E$3:$E$57,"GA",'Features'!$G$3:$G$57,"complete")</f>
+        <f>COUNTIFS('Features'!$E$3:$E$61,"GA",'Features'!$G$3:$G$61,"complete")</f>
         <v/>
       </c>
       <c r="D7" s="4">
-        <f>COUNTIFS('Features'!$E$3:$E$57,"GA",'Features'!$G$3:$G$57,"in_progress")+COUNTIFS('Features'!$E$3:$E$57,"GA",'Features'!$G$3:$G$57,"in_review")</f>
+        <f>COUNTIFS('Features'!$E$3:$E$61,"GA",'Features'!$G$3:$G$61,"in_progress")+COUNTIFS('Features'!$E$3:$E$61,"GA",'Features'!$G$3:$G$61,"in_review")</f>
         <v/>
       </c>
       <c r="E7" s="4">
-        <f>COUNTIFS('Features'!$E$3:$E$57,"GA",'Features'!$G$3:$G$57,"blocked")</f>
+        <f>COUNTIFS('Features'!$E$3:$E$61,"GA",'Features'!$G$3:$G$61,"blocked")</f>
         <v/>
       </c>
       <c r="F7" s="4">
-        <f>COUNTIFS('Features'!$E$3:$E$57,"GA",'Features'!$G$3:$G$57,"not_started")</f>
+        <f>COUNTIFS('Features'!$E$3:$E$61,"GA",'Features'!$G$3:$G$61,"not_started")</f>
         <v/>
       </c>
       <c r="G7" s="5">
-        <f>IFERROR(ROUND(SUMIFS('Features'!$H$3:$H$57,'Features'!$E$3:$E$57,"GA")/(B7*100),3),0)</f>
+        <f>IFERROR(ROUND(SUMIFS('Features'!$H$3:$H$61,'Features'!$E$3:$E$61,"GA")/(B7*100),3),0)</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -718,27 +719,27 @@
         </is>
       </c>
       <c r="B8" s="4">
-        <f>COUNTIF('Features'!$E$3:$E$57,"Post-GA")</f>
+        <f>COUNTIF('Features'!$E$3:$E$61,"Post-GA")</f>
         <v/>
       </c>
       <c r="C8" s="4">
-        <f>COUNTIFS('Features'!$E$3:$E$57,"Post-GA",'Features'!$G$3:$G$57,"complete")</f>
+        <f>COUNTIFS('Features'!$E$3:$E$61,"Post-GA",'Features'!$G$3:$G$61,"complete")</f>
         <v/>
       </c>
       <c r="D8" s="4">
-        <f>COUNTIFS('Features'!$E$3:$E$57,"Post-GA",'Features'!$G$3:$G$57,"in_progress")+COUNTIFS('Features'!$E$3:$E$57,"Post-GA",'Features'!$G$3:$G$57,"in_review")</f>
+        <f>COUNTIFS('Features'!$E$3:$E$61,"Post-GA",'Features'!$G$3:$G$61,"in_progress")+COUNTIFS('Features'!$E$3:$E$61,"Post-GA",'Features'!$G$3:$G$61,"in_review")</f>
         <v/>
       </c>
       <c r="E8" s="4">
-        <f>COUNTIFS('Features'!$E$3:$E$57,"Post-GA",'Features'!$G$3:$G$57,"blocked")</f>
+        <f>COUNTIFS('Features'!$E$3:$E$61,"Post-GA",'Features'!$G$3:$G$61,"blocked")</f>
         <v/>
       </c>
       <c r="F8" s="4">
-        <f>COUNTIFS('Features'!$E$3:$E$57,"Post-GA",'Features'!$G$3:$G$57,"not_started")</f>
+        <f>COUNTIFS('Features'!$E$3:$E$61,"Post-GA",'Features'!$G$3:$G$61,"not_started")</f>
         <v/>
       </c>
       <c r="G8" s="5">
-        <f>IFERROR(ROUND(SUMIFS('Features'!$H$3:$H$57,'Features'!$E$3:$E$57,"Post-GA")/(B8*100),3),0)</f>
+        <f>IFERROR(ROUND(SUMIFS('Features'!$H$3:$H$61,'Features'!$E$3:$E$61,"Post-GA")/(B8*100),3),0)</f>
         <v/>
       </c>
       <c r="H8" s="4">
@@ -755,19 +756,19 @@
     </row>
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="4">
-        <f>IFERROR(INDEX('Features'!A3:A57,MATCH("blocked",'Features'!$G$3:$G$57,0)),"None")</f>
+        <f>IFERROR(INDEX('Features'!A3:A61,MATCH("blocked",'Features'!$G$3:$G$61,0)),"None")</f>
         <v/>
       </c>
       <c r="B11" s="4">
-        <f>IFERROR(INDEX('Features'!B3:B57,MATCH("blocked",'Features'!$G$3:$G$57,0)),"None")</f>
+        <f>IFERROR(INDEX('Features'!B3:B61,MATCH("blocked",'Features'!$G$3:$G$61,0)),"None")</f>
         <v/>
       </c>
       <c r="C11" s="4">
-        <f>IFERROR(INDEX('Features'!E3:E57,MATCH("blocked",'Features'!$G$3:$G$57,0)),"")</f>
+        <f>IFERROR(INDEX('Features'!E3:E61,MATCH("blocked",'Features'!$G$3:$G$61,0)),"")</f>
         <v/>
       </c>
       <c r="D11" s="4">
-        <f>IFERROR(INDEX('Features'!I3:I57,MATCH("blocked",'Features'!$G$3:$G$57,0)),"")</f>
+        <f>IFERROR(INDEX('Features'!I3:I61,MATCH("blocked",'Features'!$G$3:$G$61,0)),"")</f>
         <v/>
       </c>
     </row>
@@ -799,7 +800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O57"/>
+  <dimension ref="A1:O61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4328,65 +4329,329 @@
     <row r="57" ht="42" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
         <is>
+          <t>F-053</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>Multiple positioning angles per avatar</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>avatar_builder</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>Support multiple positioning / marketing angle variants for the same avatar — each angle has its own brand strategy doc / canvas section, but shares the underlying avatar.</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>not_started</t>
+        </is>
+      </c>
+      <c r="H57" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" s="4" t="inlineStr"/>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>Matthew</t>
+        </is>
+      </c>
+      <c r="K57" s="4" t="inlineStr">
+        <is>
+          <t>F-008,F-031</t>
+        </is>
+      </c>
+      <c r="L57" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="M57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" s="4" t="inlineStr">
+        <is>
+          <t>Validates A/B angle testing for paying users. Each angle = a strategy variant tied to a canonical avatar. Surfaces in Coach mode and Export. OPEN: schema choice — separate canvases per angle vs angle-tagged sections within one canvas.</t>
+        </is>
+      </c>
+      <c r="O57" s="8" t="n">
+        <v>46155</v>
+      </c>
+    </row>
+    <row r="58" ht="42" customHeight="1">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>F-054</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>Image asset side-by-side comparison and tracking</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>asset_tracking</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>Upload current image/video assets, view side-by-side, tag against avatar + angle, flag gaps and emotional-connection opportunities.</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>not_started</t>
+        </is>
+      </c>
+      <c r="H58" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" s="4" t="inlineStr">
+        <is>
+          <t>Conditional on F-028 (asset tracking decision)</t>
+        </is>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>Matthew</t>
+        </is>
+      </c>
+      <c r="K58" s="4" t="inlineStr">
+        <is>
+          <t>F-028,F-053</t>
+        </is>
+      </c>
+      <c r="L58" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="M58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" s="4" t="inlineStr">
+        <is>
+          <t>Extension of asset_tracking that goes beyond text. Anchored to InfinityVault need N-002 (assess images/videos, identify what's missing, surface emotional-connection opportunities). Requires image storage (Supabase Storage) and a comparison UI.</t>
+        </is>
+      </c>
+      <c r="O58" s="8" t="n">
+        <v>46155</v>
+      </c>
+    </row>
+    <row r="59" ht="42" customHeight="1">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>F-055</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>Design brief creation</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>create_mode</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>Generate a design brief document from the Forensic Canvas + selected positioning angle. Output briefs creative work (image, video, packaging) for designers or agencies.</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>not_started</t>
+        </is>
+      </c>
+      <c r="H59" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" s="4" t="inlineStr"/>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>Matthew</t>
+        </is>
+      </c>
+      <c r="K59" s="4" t="inlineStr">
+        <is>
+          <t>F-008,F-053</t>
+        </is>
+      </c>
+      <c r="L59" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="M59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" s="4" t="inlineStr">
+        <is>
+          <t>Sibling to F-020 (Amazon listing copy) and F-021 (Brand Voice Guide). Bridges the canvas to creative work. Required to make F-054 actionable (gap → brief → asset).</t>
+        </is>
+      </c>
+      <c r="O59" s="8" t="n">
+        <v>46155</v>
+      </c>
+    </row>
+    <row r="60" ht="42" customHeight="1">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>F-056</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>Image generation (coming soon)</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>create_mode</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>Generate brand-aligned imagery directly from canvas + design brief. Marked 'coming soon' — Post-GA feature, not in active build.</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>Post-GA</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>not_started</t>
+        </is>
+      </c>
+      <c r="H60" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" s="4" t="inlineStr"/>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>Matthew</t>
+        </is>
+      </c>
+      <c r="K60" s="4" t="inlineStr">
+        <is>
+          <t>F-055</t>
+        </is>
+      </c>
+      <c r="L60" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="M60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" s="4" t="inlineStr">
+        <is>
+          <t>Surfaced as 'coming soon' in UI (teaser). Closes the loop from canvas → design brief → generated imagery. No model choice locked in; defer until Post-GA stability work is done.</t>
+        </is>
+      </c>
+      <c r="O60" s="8" t="n">
+        <v>46155</v>
+      </c>
+    </row>
+    <row r="61" ht="42" customHeight="1">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
           <t>F-052</t>
         </is>
       </c>
-      <c r="B57" s="4" t="inlineStr">
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>Lovable.dev vs existing codebase decision</t>
         </is>
       </c>
-      <c r="C57" s="4" t="inlineStr">
+      <c r="C61" s="4" t="inlineStr">
         <is>
           <t>infrastructure</t>
         </is>
       </c>
-      <c r="D57" s="4" t="inlineStr">
+      <c r="D61" s="4" t="inlineStr">
         <is>
           <t>Architectural decision: build Gen 3 in Lovable.dev (per Trevor) or extend existing React codebase. Critical risk per Launch Roadmap.</t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr">
+      <c r="E61" s="4" t="inlineStr">
         <is>
           <t>Alpha</t>
         </is>
       </c>
-      <c r="F57" s="4" t="inlineStr">
+      <c r="F61" s="4" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="G57" s="4" t="inlineStr">
+      <c r="G61" s="4" t="inlineStr">
         <is>
           <t>blocked</t>
         </is>
       </c>
-      <c r="H57" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" s="4" t="inlineStr">
+      <c r="H61" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" s="4" t="inlineStr">
         <is>
           <t>Awaiting decision — flagged Critical in Risk Register</t>
         </is>
       </c>
-      <c r="J57" s="4" t="inlineStr">
+      <c r="J61" s="4" t="inlineStr">
         <is>
           <t>Matthew</t>
         </is>
       </c>
-      <c r="K57" s="4" t="inlineStr"/>
-      <c r="L57" s="4" t="n">
+      <c r="K61" s="4" t="inlineStr"/>
+      <c r="L61" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="M57" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" s="4" t="inlineStr">
+      <c r="M61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" s="4" t="inlineStr">
         <is>
           <t>DEFERRED DECISION. Trevor's Gen 3 Brief specifies Lovable; existing codebase is React + Supabase. Don't half-port. Default: extend existing repo until Matthew decides otherwise.</t>
         </is>
       </c>
-      <c r="O57" s="8" t="n">
+      <c r="O61" s="8" t="n">
         <v>46155</v>
       </c>
     </row>
@@ -4394,7 +4659,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
   </mergeCells>
-  <conditionalFormatting sqref="G3:G257">
+  <conditionalFormatting sqref="G3:G261">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="2">
       <formula>"complete"</formula>
     </cfRule>
@@ -4412,16 +4677,16 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation sqref="C3:C257" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Value must match one of the allowed options." type="list">
+    <dataValidation sqref="C3:C261" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Value must match one of the allowed options." type="list">
       <formula1>"conversation,avatar_builder,canvas,create_mode,coach_mode,pay_gate,export,accounts,asset_tracking,feedback_loop,analytics,infrastructure,design_system"</formula1>
     </dataValidation>
-    <dataValidation sqref="E3:E257" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Value must match one of the allowed options." type="list">
+    <dataValidation sqref="E3:E261" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Value must match one of the allowed options." type="list">
       <formula1>"Alpha,Beta,GA,Post-GA"</formula1>
     </dataValidation>
-    <dataValidation sqref="F3:F257" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Value must match one of the allowed options." type="list">
+    <dataValidation sqref="F3:F261" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Value must match one of the allowed options." type="list">
       <formula1>"P0,P1,P2"</formula1>
     </dataValidation>
-    <dataValidation sqref="G3:G257" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Value must match one of the allowed options." type="list">
+    <dataValidation sqref="G3:G261" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Value must match one of the allowed options." type="list">
       <formula1>"not_started,in_progress,blocked,in_review,complete"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7466,7 +7731,7 @@
         </is>
       </c>
       <c r="E5" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$57,"F-001",'Features'!$G$3:$G$57,"blocked")+COUNTIFS('Features'!$A$3:$A$57,"F-002",'Features'!$G$3:$G$57,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$57,"F-001",'Features'!$G$3:$G$57,"complete")+COUNTIFS('Features'!$A$3:$A$57,"F-002",'Features'!$G$3:$G$57,"complete"))=2,"MET","OPEN — "&amp;(2-(COUNTIFS('Features'!$A$3:$A$57,"F-001",'Features'!$G$3:$G$57,"complete")+COUNTIFS('Features'!$A$3:$A$57,"F-002",'Features'!$G$3:$G$57,"complete")))&amp;" of 2 remaining"))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-001",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-002",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-001",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-002",'Features'!$G$3:$G$61,"complete"))=2,"MET","OPEN — "&amp;(2-(COUNTIFS('Features'!$A$3:$A$61,"F-001",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-002",'Features'!$G$3:$G$61,"complete")))&amp;" of 2 remaining"))</f>
         <v/>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -7497,7 +7762,7 @@
         </is>
       </c>
       <c r="E6" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$57,"F-003",'Features'!$G$3:$G$57,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$57,"F-003",'Features'!$G$3:$G$57,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$57,"F-003",'Features'!$G$3:$G$57,"complete")))&amp;" of 1 remaining"))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-003",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-003",'Features'!$G$3:$G$61,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$61,"F-003",'Features'!$G$3:$G$61,"complete")))&amp;" of 1 remaining"))</f>
         <v/>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -7528,7 +7793,7 @@
         </is>
       </c>
       <c r="E7" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$57,"F-004",'Features'!$G$3:$G$57,"blocked")+COUNTIFS('Features'!$A$3:$A$57,"F-005",'Features'!$G$3:$G$57,"blocked")+COUNTIFS('Features'!$A$3:$A$57,"F-006",'Features'!$G$3:$G$57,"blocked")+COUNTIFS('Features'!$A$3:$A$57,"F-007",'Features'!$G$3:$G$57,"blocked")+COUNTIFS('Features'!$A$3:$A$57,"F-009",'Features'!$G$3:$G$57,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$57,"F-004",'Features'!$G$3:$G$57,"complete")+COUNTIFS('Features'!$A$3:$A$57,"F-005",'Features'!$G$3:$G$57,"complete")+COUNTIFS('Features'!$A$3:$A$57,"F-006",'Features'!$G$3:$G$57,"complete")+COUNTIFS('Features'!$A$3:$A$57,"F-007",'Features'!$G$3:$G$57,"complete")+COUNTIFS('Features'!$A$3:$A$57,"F-009",'Features'!$G$3:$G$57,"complete"))=5,"MET","OPEN — "&amp;(5-(COUNTIFS('Features'!$A$3:$A$57,"F-004",'Features'!$G$3:$G$57,"complete")+COUNTIFS('Features'!$A$3:$A$57,"F-005",'Features'!$G$3:$G$57,"complete")+COUNTIFS('Features'!$A$3:$A$57,"F-006",'Features'!$G$3:$G$57,"complete")+COUNTIFS('Features'!$A$3:$A$57,"F-007",'Features'!$G$3:$G$57,"complete")+COUNTIFS('Features'!$A$3:$A$57,"F-009",'Features'!$G$3:$G$57,"complete")))&amp;" of 5 remaining"))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-004",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-005",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-009",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-004",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-005",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-009",'Features'!$G$3:$G$61,"complete"))=5,"MET","OPEN — "&amp;(5-(COUNTIFS('Features'!$A$3:$A$61,"F-004",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-005",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-009",'Features'!$G$3:$G$61,"complete")))&amp;" of 5 remaining"))</f>
         <v/>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -7559,7 +7824,7 @@
         </is>
       </c>
       <c r="E8" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$57,"F-008",'Features'!$G$3:$G$57,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$57,"F-008",'Features'!$G$3:$G$57,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$57,"F-008",'Features'!$G$3:$G$57,"complete")))&amp;" of 1 remaining"))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"complete")))&amp;" of 1 remaining"))</f>
         <v/>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -7590,7 +7855,7 @@
         </is>
       </c>
       <c r="E9" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$57,"F-011",'Features'!$G$3:$G$57,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$57,"F-011",'Features'!$G$3:$G$57,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$57,"F-011",'Features'!$G$3:$G$57,"complete")))&amp;" of 1 remaining"))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-011",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-011",'Features'!$G$3:$G$61,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$61,"F-011",'Features'!$G$3:$G$61,"complete")))&amp;" of 1 remaining"))</f>
         <v/>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -7621,7 +7886,7 @@
         </is>
       </c>
       <c r="E10" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$57,"F-013",'Features'!$G$3:$G$57,"blocked")+COUNTIFS('Features'!$A$3:$A$57,"F-014",'Features'!$G$3:$G$57,"blocked")+COUNTIFS('Features'!$A$3:$A$57,"F-015",'Features'!$G$3:$G$57,"blocked")+COUNTIFS('Features'!$A$3:$A$57,"F-016",'Features'!$G$3:$G$57,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$57,"F-013",'Features'!$G$3:$G$57,"complete")+COUNTIFS('Features'!$A$3:$A$57,"F-014",'Features'!$G$3:$G$57,"complete")+COUNTIFS('Features'!$A$3:$A$57,"F-015",'Features'!$G$3:$G$57,"complete")+COUNTIFS('Features'!$A$3:$A$57,"F-016",'Features'!$G$3:$G$57,"complete"))=4,"MET","OPEN — "&amp;(4-(COUNTIFS('Features'!$A$3:$A$57,"F-013",'Features'!$G$3:$G$57,"complete")+COUNTIFS('Features'!$A$3:$A$57,"F-014",'Features'!$G$3:$G$57,"complete")+COUNTIFS('Features'!$A$3:$A$57,"F-015",'Features'!$G$3:$G$57,"complete")+COUNTIFS('Features'!$A$3:$A$57,"F-016",'Features'!$G$3:$G$57,"complete")))&amp;" of 4 remaining"))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-013",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-014",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-015",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-016",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-013",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-014",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-015",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-016",'Features'!$G$3:$G$61,"complete"))=4,"MET","OPEN — "&amp;(4-(COUNTIFS('Features'!$A$3:$A$61,"F-013",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-014",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-015",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-016",'Features'!$G$3:$G$61,"complete")))&amp;" of 4 remaining"))</f>
         <v/>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -7652,7 +7917,7 @@
         </is>
       </c>
       <c r="E11" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$57,"F-017",'Features'!$G$3:$G$57,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$57,"F-017",'Features'!$G$3:$G$57,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$57,"F-017",'Features'!$G$3:$G$57,"complete")))&amp;" of 1 remaining"))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-017",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-017",'Features'!$G$3:$G$61,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$61,"F-017",'Features'!$G$3:$G$61,"complete")))&amp;" of 1 remaining"))</f>
         <v/>
       </c>
       <c r="F11" s="4" t="inlineStr"/>
@@ -7679,7 +7944,7 @@
         </is>
       </c>
       <c r="E12" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$57,"F-018",'Features'!$G$3:$G$57,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$57,"F-018",'Features'!$G$3:$G$57,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$57,"F-018",'Features'!$G$3:$G$57,"complete")))&amp;" of 1 remaining"))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-018",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-018",'Features'!$G$3:$G$61,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$61,"F-018",'Features'!$G$3:$G$61,"complete")))&amp;" of 1 remaining"))</f>
         <v/>
       </c>
       <c r="F12" s="4" t="inlineStr"/>
@@ -7706,7 +7971,7 @@
         </is>
       </c>
       <c r="E13" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$57,"F-052",'Features'!$G$3:$G$57,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$57,"F-052",'Features'!$G$3:$G$57,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$57,"F-052",'Features'!$G$3:$G$57,"complete")))&amp;" of 1 remaining"))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-052",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-052",'Features'!$G$3:$G$61,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$61,"F-052",'Features'!$G$3:$G$61,"complete")))&amp;" of 1 remaining"))</f>
         <v/>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -7737,7 +8002,7 @@
         </is>
       </c>
       <c r="E14" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$57,"F-016",'Features'!$G$3:$G$57,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$57,"F-016",'Features'!$G$3:$G$57,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$57,"F-016",'Features'!$G$3:$G$57,"complete")))&amp;" of 1 remaining"))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-016",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-016",'Features'!$G$3:$G$61,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$61,"F-016",'Features'!$G$3:$G$61,"complete")))&amp;" of 1 remaining"))</f>
         <v/>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -7768,7 +8033,7 @@
         </is>
       </c>
       <c r="E15" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$57,"F-019",'Features'!$G$3:$G$57,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$57,"F-019",'Features'!$G$3:$G$57,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$57,"F-019",'Features'!$G$3:$G$57,"complete")))&amp;" of 1 remaining"))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-019",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-019",'Features'!$G$3:$G$61,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$61,"F-019",'Features'!$G$3:$G$61,"complete")))&amp;" of 1 remaining"))</f>
         <v/>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -7799,7 +8064,7 @@
         </is>
       </c>
       <c r="E16" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$57,"F-020",'Features'!$G$3:$G$57,"blocked")+COUNTIFS('Features'!$A$3:$A$57,"F-021",'Features'!$G$3:$G$57,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$57,"F-020",'Features'!$G$3:$G$57,"complete")+COUNTIFS('Features'!$A$3:$A$57,"F-021",'Features'!$G$3:$G$57,"complete"))=2,"MET","OPEN — "&amp;(2-(COUNTIFS('Features'!$A$3:$A$57,"F-020",'Features'!$G$3:$G$57,"complete")+COUNTIFS('Features'!$A$3:$A$57,"F-021",'Features'!$G$3:$G$57,"complete")))&amp;" of 2 remaining"))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-020",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-021",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-020",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-021",'Features'!$G$3:$G$61,"complete"))=2,"MET","OPEN — "&amp;(2-(COUNTIFS('Features'!$A$3:$A$61,"F-020",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-021",'Features'!$G$3:$G$61,"complete")))&amp;" of 2 remaining"))</f>
         <v/>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -7830,7 +8095,7 @@
         </is>
       </c>
       <c r="E17" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$57,"F-022",'Features'!$G$3:$G$57,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$57,"F-022",'Features'!$G$3:$G$57,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$57,"F-022",'Features'!$G$3:$G$57,"complete")))&amp;" of 1 remaining"))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"complete")))&amp;" of 1 remaining"))</f>
         <v/>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -7861,7 +8126,7 @@
         </is>
       </c>
       <c r="E18" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$57,"F-023",'Features'!$G$3:$G$57,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$57,"F-023",'Features'!$G$3:$G$57,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$57,"F-023",'Features'!$G$3:$G$57,"complete")))&amp;" of 1 remaining"))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-023",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-023",'Features'!$G$3:$G$61,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$61,"F-023",'Features'!$G$3:$G$61,"complete")))&amp;" of 1 remaining"))</f>
         <v/>
       </c>
       <c r="F18" s="4" t="inlineStr"/>
@@ -7888,7 +8153,7 @@
         </is>
       </c>
       <c r="E19" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$57,"F-028",'Features'!$G$3:$G$57,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$57,"F-028",'Features'!$G$3:$G$57,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$57,"F-028",'Features'!$G$3:$G$57,"complete")))&amp;" of 1 remaining"))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-028",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-028",'Features'!$G$3:$G$61,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$61,"F-028",'Features'!$G$3:$G$61,"complete")))&amp;" of 1 remaining"))</f>
         <v/>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -7919,7 +8184,7 @@
         </is>
       </c>
       <c r="E20" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$57,"F-024",'Features'!$G$3:$G$57,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$57,"F-024",'Features'!$G$3:$G$57,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$57,"F-024",'Features'!$G$3:$G$57,"complete")))&amp;" of 1 remaining"))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-024",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-024",'Features'!$G$3:$G$61,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$61,"F-024",'Features'!$G$3:$G$61,"complete")))&amp;" of 1 remaining"))</f>
         <v/>
       </c>
       <c r="F20" s="4" t="inlineStr"/>
@@ -7946,7 +8211,7 @@
         </is>
       </c>
       <c r="E21" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$57,"F-025",'Features'!$G$3:$G$57,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$57,"F-025",'Features'!$G$3:$G$57,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$57,"F-025",'Features'!$G$3:$G$57,"complete")))&amp;" of 1 remaining"))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-025",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-025",'Features'!$G$3:$G$61,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$61,"F-025",'Features'!$G$3:$G$61,"complete")))&amp;" of 1 remaining"))</f>
         <v/>
       </c>
       <c r="F21" s="4" t="inlineStr"/>
@@ -7973,7 +8238,7 @@
         </is>
       </c>
       <c r="E22" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$57,"F-027",'Features'!$G$3:$G$57,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$57,"F-027",'Features'!$G$3:$G$57,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$57,"F-027",'Features'!$G$3:$G$57,"complete")))&amp;" of 1 remaining"))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-027",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-027",'Features'!$G$3:$G$61,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$61,"F-027",'Features'!$G$3:$G$61,"complete")))&amp;" of 1 remaining"))</f>
         <v/>
       </c>
       <c r="F22" s="4" t="inlineStr"/>
@@ -8000,7 +8265,7 @@
         </is>
       </c>
       <c r="E23" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$57,"F-031",'Features'!$G$3:$G$57,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$57,"F-031",'Features'!$G$3:$G$57,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$57,"F-031",'Features'!$G$3:$G$57,"complete")))&amp;" of 1 remaining"))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-031",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-031",'Features'!$G$3:$G$61,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$61,"F-031",'Features'!$G$3:$G$61,"complete")))&amp;" of 1 remaining"))</f>
         <v/>
       </c>
       <c r="F23" s="4" t="inlineStr"/>
@@ -8027,7 +8292,7 @@
         </is>
       </c>
       <c r="E24" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$57,"F-032",'Features'!$G$3:$G$57,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$57,"F-032",'Features'!$G$3:$G$57,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$57,"F-032",'Features'!$G$3:$G$57,"complete")))&amp;" of 1 remaining"))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-032",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-032",'Features'!$G$3:$G$61,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$61,"F-032",'Features'!$G$3:$G$61,"complete")))&amp;" of 1 remaining"))</f>
         <v/>
       </c>
       <c r="F24" s="4" t="inlineStr"/>
@@ -8054,7 +8319,7 @@
         </is>
       </c>
       <c r="E25" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$57,"F-033",'Features'!$G$3:$G$57,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$57,"F-033",'Features'!$G$3:$G$57,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$57,"F-033",'Features'!$G$3:$G$57,"complete")))&amp;" of 1 remaining"))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-033",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-033",'Features'!$G$3:$G$61,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$61,"F-033",'Features'!$G$3:$G$61,"complete")))&amp;" of 1 remaining"))</f>
         <v/>
       </c>
       <c r="F25" s="4" t="inlineStr"/>
@@ -8081,7 +8346,7 @@
         </is>
       </c>
       <c r="E26" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$57,"F-034",'Features'!$G$3:$G$57,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$57,"F-034",'Features'!$G$3:$G$57,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$57,"F-034",'Features'!$G$3:$G$57,"complete")))&amp;" of 1 remaining"))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-034",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-034",'Features'!$G$3:$G$61,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$61,"F-034",'Features'!$G$3:$G$61,"complete")))&amp;" of 1 remaining"))</f>
         <v/>
       </c>
       <c r="F26" s="4" t="inlineStr"/>
@@ -8108,7 +8373,7 @@
         </is>
       </c>
       <c r="E27" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$57,"F-037",'Features'!$G$3:$G$57,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$57,"F-037",'Features'!$G$3:$G$57,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$57,"F-037",'Features'!$G$3:$G$57,"complete")))&amp;" of 1 remaining"))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-037",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-037",'Features'!$G$3:$G$61,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$61,"F-037",'Features'!$G$3:$G$61,"complete")))&amp;" of 1 remaining"))</f>
         <v/>
       </c>
       <c r="F27" s="4" t="inlineStr"/>
@@ -8135,7 +8400,7 @@
         </is>
       </c>
       <c r="E28" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$57,"F-035",'Features'!$G$3:$G$57,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$57,"F-035",'Features'!$G$3:$G$57,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$57,"F-035",'Features'!$G$3:$G$57,"complete")))&amp;" of 1 remaining"))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-035",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-035",'Features'!$G$3:$G$61,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$61,"F-035",'Features'!$G$3:$G$61,"complete")))&amp;" of 1 remaining"))</f>
         <v/>
       </c>
       <c r="F28" s="4" t="inlineStr"/>
@@ -8162,7 +8427,7 @@
         </is>
       </c>
       <c r="E29" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$57,"F-036",'Features'!$G$3:$G$57,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$57,"F-036",'Features'!$G$3:$G$57,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$57,"F-036",'Features'!$G$3:$G$57,"complete")))&amp;" of 1 remaining"))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-036",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-036",'Features'!$G$3:$G$61,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$61,"F-036",'Features'!$G$3:$G$61,"complete")))&amp;" of 1 remaining"))</f>
         <v/>
       </c>
       <c r="F29" s="4" t="inlineStr"/>
@@ -8189,7 +8454,7 @@
         </is>
       </c>
       <c r="E30" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$57,"F-034",'Features'!$G$3:$G$57,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$57,"F-034",'Features'!$G$3:$G$57,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$57,"F-034",'Features'!$G$3:$G$57,"complete")))&amp;" of 1 remaining"))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-034",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-034",'Features'!$G$3:$G$61,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$61,"F-034",'Features'!$G$3:$G$61,"complete")))&amp;" of 1 remaining"))</f>
         <v/>
       </c>
       <c r="F30" s="4" t="inlineStr"/>
@@ -8216,7 +8481,7 @@
         </is>
       </c>
       <c r="E31" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$57,"F-038",'Features'!$G$3:$G$57,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$57,"F-038",'Features'!$G$3:$G$57,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$57,"F-038",'Features'!$G$3:$G$57,"complete")))&amp;" of 1 remaining"))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-038",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-038",'Features'!$G$3:$G$61,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$61,"F-038",'Features'!$G$3:$G$61,"complete")))&amp;" of 1 remaining"))</f>
         <v/>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -8251,6 +8516,213 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Brand Needs — concrete user needs mapped to features</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Anchors the feature inventory to real brand use cases. Each leaf need maps to one or more feature ids. fulfilment_status is derived: MET if all mapped features complete, BLOCKED if any are blocked, otherwise OPEN with count.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>need_id</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>need</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>mapped_features</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>fulfilment_status</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="42" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>N-001</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>InfinityVault</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Create brand strategy doc using the Coach for the 'collector' avatar</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>F-001,F-004,F-005,F-006,F-007,F-008,F-022,F-023</t>
+        </is>
+      </c>
+      <c r="E5" s="4">
+        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-001",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-004",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-005",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-023",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-001",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-004",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-005",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-023",'Features'!$G$3:$G$61,"complete"))=8,"MET","OPEN — "&amp;(8-(COUNTIFS('Features'!$A$3:$A$61,"F-001",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-004",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-005",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-023",'Features'!$G$3:$G$61,"complete")))&amp;" of 8 remaining"))</f>
+        <v/>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>End-to-end happy path: Layer 1 conversation → Avatar Builder (collector) → Forensic Canvas → Coach refinement → Export. Validates the core product loop with a real brand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="42" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>N-002</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>InfinityVault</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Assess current set of images and videos</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>F-054</t>
+        </is>
+      </c>
+      <c r="E6" s="4">
+        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-054",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-054",'Features'!$G$3:$G$61,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$61,"F-054",'Features'!$G$3:$G$61,"complete")))&amp;" of 1 remaining"))</f>
+        <v/>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Top-level need under which the gap-identification and emotional-connection needs sit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>N-002.1</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>InfinityVault</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Identify what's missing in the current image/video set</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>F-054</t>
+        </is>
+      </c>
+      <c r="E7" s="4">
+        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-054",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-054",'Features'!$G$3:$G$61,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$61,"F-054",'Features'!$G$3:$G$61,"complete")))&amp;" of 1 remaining"))</f>
+        <v/>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Gap analysis on visual assets — requires side-by-side comparison + tagging against the canvas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="42" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>N-002.1.1</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>InfinityVault</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Surface opportunities to improve emotional connection with the customer</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>F-006,F-007,F-054,F-055</t>
+        </is>
+      </c>
+      <c r="E8" s="4">
+        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-054",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-055",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-054",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-055",'Features'!$G$3:$G$61,"complete"))=4,"MET","OPEN — "&amp;(4-(COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-054",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-055",'Features'!$G$3:$G$61,"complete")))&amp;" of 4 remaining"))</f>
+        <v/>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Connects Emotional Journey Mapping (Avatar Builder Sec 3) + Voice of Customer (Sec 4) to the asset gaps surfaced by F-054, with design briefs (F-055) closing the loop into action.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="E5:E8">
+    <cfRule type="expression" priority="1" dxfId="2">
+      <formula>E5="MET"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>ISNUMBER(SEARCH("BLOCKED",E5))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="1">
+      <formula>ISNUMBER(SEARCH("OPEN",E5))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8985,13 +9457,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9051,6 +9523,28 @@
         </is>
       </c>
     </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Matthew (via Claude Code)</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Added F-053..F-056 + Brand Needs sheet</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Captured multi-angle, image comparison, design brief, and (post-GA) image generation features. Added Brand Needs sheet seeded with InfinityVault as the first validation case.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>

--- a/docs/feature_status_tracker.xlsx
+++ b/docs/feature_status_tracker.xlsx
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="H5" s="7" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="I5" s="4" t="inlineStr"/>
       <c r="J5" s="4" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>Edge function exists for canvas synthesis. DRAFT badge + Forensic upgrade CTA needs design pass.</t>
+          <t>generate-brand-strategy-document edge function ships a unified strategy doc today. The Gen 3 Draft-vs-Forensic *tier* split (lighter doc after Layer 1, heavier after Avatar Builder) is the gap — current code doesn't distinguish them yet. DRAFT badge + Forensic upgrade CTA still needs design.</t>
         </is>
       </c>
       <c r="O5" s="8" t="n">
@@ -1388,11 +1388,11 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>not_started</t>
+          <t>in_review</t>
         </is>
       </c>
       <c r="H10" s="7" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I10" s="4" t="inlineStr"/>
       <c r="J10" s="4" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>Differential vs Draft Canvas is the core demonstration of value.</t>
+          <t>Brand strategy doc generation is the Forensic Canvas synthesis in current code: generate-brand-strategy-document (1164 LoC, pgvector RAG, Haiku, client-side orchestration to avoid 150s timeout) + generate-brand-strategy-section + MarkdownExportService. Remaining: explicit 'Strategic Entry Point' Trigger Moment callout and the Draft↔Forensic toggle (F-008.4). Sub-feature percent should override this.</t>
         </is>
       </c>
       <c r="O10" s="8" t="n">
@@ -2335,11 +2335,11 @@
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>not_started</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="H25" s="7" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="I25" s="4" t="inlineStr"/>
       <c r="J25" s="4" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
-          <t>Required to deliver the canvas-as-artifact promise.</t>
+          <t>PDF + Markdown shipped: BrandCanvasPDFExport, MarkdownPDFExporter, BrandMarkdownExport, generate-brand-strategy-pdf edge function. Word (.docx) export is the remaining gap. Once Draft/Forensic tier split lands in F-003/F-008, ensure both tiers export.</t>
         </is>
       </c>
       <c r="O25" s="8" t="n">

--- a/docs/feature_status_tracker.xlsx
+++ b/docs/feature_status_tracker.xlsx
@@ -8,12 +8,13 @@
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Features" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sub-features" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Phase Gate" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Brand Needs" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Risks" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Change Log" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Problems" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Features" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sub-features" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Phase Gate" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Brand Needs" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Risks" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Change Log" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -158,14 +159,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFBDD7EE"/>
+          <fgColor rgb="FFD9D9D9"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFD9D9D9"/>
+          <fgColor rgb="FFBDD7EE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -800,7 +801,560 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O61"/>
+  <dimension ref="A1:I14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Problems — the grand-vision list, mapped to features</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Each problem is mapped to the features that help solve it. fulfilment_status derives from the status of mapped features. alpha_testable = whether Alpha-stage features alone are enough to validate this problem with testers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>problem_id</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>problem_statement</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>earliest_phase_solvable</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>alpha_testable</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>mapped_features</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>feature_count</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>complete_or_review_count</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>fulfilment_status</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="48" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>P-001</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Generic AI doesn't know my customer deeply enough.</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>F-004,F-005,F-006,F-007,F-008,F-009,F-012,F-022</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="G5" s="4">
+        <f>(COUNTIFS('Features'!$A$3:$A$61,"F-004",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-004",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-005",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-005",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-009",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-009",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-012",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-012",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"in_review"))</f>
+        <v/>
+      </c>
+      <c r="H5" s="4">
+        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-004",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-005",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-009",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-012",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-004",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-004",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-005",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-005",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-009",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-009",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-012",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-012",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"in_review"))=8,"MET",IF((COUNTIFS('Features'!$A$3:$A$61,"F-004",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-004",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-005",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-005",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-009",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-009",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-012",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-012",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"in_review"))=0,"OPEN — 0 of 8","PARTIAL — "&amp;(COUNTIFS('Features'!$A$3:$A$61,"F-004",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-004",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-005",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-005",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-009",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-009",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-012",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-012",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"in_review"))&amp;" of 8")))</f>
+        <v/>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>Core Alpha thesis: Avatar Builder + Forensic Canvas produce a depth of customer understanding generic prompting can't reach. F-022 (Coach mode) extends this in Beta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>P-002</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>I don't know what to ask myself about my customer.</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>F-001,F-004,F-005,F-006,F-007,F-009</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G6" s="4">
+        <f>(COUNTIFS('Features'!$A$3:$A$61,"F-001",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-001",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-004",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-004",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-005",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-005",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-009",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-009",'Features'!$G$3:$G$61,"in_review"))</f>
+        <v/>
+      </c>
+      <c r="H6" s="4">
+        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-001",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-004",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-005",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-009",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-001",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-001",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-004",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-004",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-005",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-005",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-009",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-009",'Features'!$G$3:$G$61,"in_review"))=6,"MET",IF((COUNTIFS('Features'!$A$3:$A$61,"F-001",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-001",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-004",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-004",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-005",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-005",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-009",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-009",'Features'!$G$3:$G$61,"in_review"))=0,"OPEN — 0 of 6","PARTIAL — "&amp;(COUNTIFS('Features'!$A$3:$A$61,"F-001",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-001",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-004",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-004",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-005",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-005",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-009",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-009",'Features'!$G$3:$G$61,"in_review"))&amp;" of 6")))</f>
+        <v/>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>10-Q conversation + 4 Avatar Builder sections provide the inquiry structure. F-009 'Think About This' mode explicitly generates reflective questions per field.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="48" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>P-003</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>My brand strategy doc is shallow or doesn't exist.</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>F-003,F-008,F-023,F-053</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G7" s="4">
+        <f>(COUNTIFS('Features'!$A$3:$A$61,"F-003",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-003",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-023",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-023",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-053",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-053",'Features'!$G$3:$G$61,"in_review"))</f>
+        <v/>
+      </c>
+      <c r="H7" s="4">
+        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-003",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-023",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-053",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-003",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-003",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-023",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-023",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-053",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-053",'Features'!$G$3:$G$61,"in_review"))=4,"MET",IF((COUNTIFS('Features'!$A$3:$A$61,"F-003",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-003",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-023",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-023",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-053",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-053",'Features'!$G$3:$G$61,"in_review"))=0,"OPEN — 0 of 4","PARTIAL — "&amp;(COUNTIFS('Features'!$A$3:$A$61,"F-003",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-003",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-023",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-023",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-053",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-053",'Features'!$G$3:$G$61,"in_review"))&amp;" of 4")))</f>
+        <v/>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>F-008 (Forensic Canvas via generate-brand-strategy-document) is the primary fulfilment — substantially shipped. Polished Word export (F-023) and multi-angle (F-053) are Beta extensions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="48" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>P-004</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>My copy and creative aren't grounded in strategy.</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>F-008,F-020,F-021,F-055</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G8" s="4">
+        <f>(COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-020",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-020",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-021",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-021",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-055",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-055",'Features'!$G$3:$G$61,"in_review"))</f>
+        <v/>
+      </c>
+      <c r="H8" s="4">
+        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-020",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-021",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-055",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-020",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-020",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-021",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-021",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-055",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-055",'Features'!$G$3:$G$61,"in_review"))=4,"MET",IF((COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-020",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-020",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-021",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-021",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-055",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-055",'Features'!$G$3:$G$61,"in_review"))=0,"OPEN — 0 of 4","PARTIAL — "&amp;(COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-020",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-020",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-021",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-021",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-055",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-055",'Features'!$G$3:$G$61,"in_review"))&amp;" of 4")))</f>
+        <v/>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>Requires Create mode outputs (F-020 Amazon, F-021 Voice Guide, F-055 Design brief). None ship in Alpha. The canvas (F-008) is the anchor but not the deliverable for this problem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="48" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>P-005</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>My customer's actual language doesn't make it into my copy.</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>F-007,F-008,F-020,F-021</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G9" s="4">
+        <f>(COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-020",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-020",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-021",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-021",'Features'!$G$3:$G$61,"in_review"))</f>
+        <v/>
+      </c>
+      <c r="H9" s="4">
+        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-020",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-021",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-020",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-020",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-021",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-021",'Features'!$G$3:$G$61,"in_review"))=4,"MET",IF((COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-020",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-020",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-021",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-021",'Features'!$G$3:$G$61,"in_review"))=0,"OPEN — 0 of 4","PARTIAL — "&amp;(COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-020",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-020",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-021",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-021",'Features'!$G$3:$G$61,"in_review"))&amp;" of 4")))</f>
+        <v/>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>F-007 Voice of Customer extracts verbatim language in Alpha. F-020/F-021 (Beta) consume it. Alpha can prove 'we capture the language'; only Beta proves 'it shows up in your copy'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>P-006</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>My existing image/video set is doing something — but I can't tell what's missing or off.</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>F-006,F-007,F-054,F-055</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G10" s="4">
+        <f>(COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-054",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-054",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-055",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-055",'Features'!$G$3:$G$61,"in_review"))</f>
+        <v/>
+      </c>
+      <c r="H10" s="4">
+        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-054",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-055",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-054",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-054",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-055",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-055",'Features'!$G$3:$G$61,"in_review"))=4,"MET",IF((COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-054",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-054",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-055",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-055",'Features'!$G$3:$G$61,"in_review"))=0,"OPEN — 0 of 4","PARTIAL — "&amp;(COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-054",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-054",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-055",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-055",'Features'!$G$3:$G$61,"in_review"))&amp;" of 4")))</f>
+        <v/>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>InfinityVault's specific need (N-002). F-054 is conditional on the asset-tracking decision gate. F-006/F-007 supply the 'what should this connect to' context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="48" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>P-007</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>I have no thinking partner who remembers my brand.</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>F-022,F-031,F-049</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" s="4">
+        <f>(COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-031",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-031",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-049",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-049",'Features'!$G$3:$G$61,"in_review"))</f>
+        <v/>
+      </c>
+      <c r="H11" s="4">
+        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-031",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-049",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-031",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-031",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-049",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-049",'Features'!$G$3:$G$61,"in_review"))=3,"MET",IF((COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-031",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-031",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-049",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-049",'Features'!$G$3:$G$61,"in_review"))=0,"OPEN — 0 of 3","PARTIAL — "&amp;(COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-031",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-031",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-049",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-049",'Features'!$G$3:$G$61,"in_review"))&amp;" of 3")))</f>
+        <v/>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>F-022 Coach mode is the answer. RAG (F-049) makes the memory queryable. F-031 (My Brands) lets the partner know which brand we're discussing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="48" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>P-008</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>I can't cheaply test multiple positioning angles.</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>F-042,F-053,F-055</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" s="4">
+        <f>(COUNTIFS('Features'!$A$3:$A$61,"F-042",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-042",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-053",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-053",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-055",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-055",'Features'!$G$3:$G$61,"in_review"))</f>
+        <v/>
+      </c>
+      <c r="H12" s="4">
+        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-042",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-053",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-055",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-042",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-042",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-053",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-053",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-055",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-055",'Features'!$G$3:$G$61,"in_review"))=3,"MET",IF((COUNTIFS('Features'!$A$3:$A$61,"F-042",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-042",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-053",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-053",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-055",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-055",'Features'!$G$3:$G$61,"in_review"))=0,"OPEN — 0 of 3","PARTIAL — "&amp;(COUNTIFS('Features'!$A$3:$A$61,"F-042",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-042",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-053",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-053",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-055",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-055",'Features'!$G$3:$G$61,"in_review"))&amp;" of 3")))</f>
+        <v/>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>F-053 is the primary fulfilment. F-055 lets each angle drive its own design brief. F-042 comparison view (GA) lets the user A/B them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="48" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>P-009</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>I can't tell when my strategy and my live assets have drifted apart.</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>F-028,F-029,F-030,F-043,F-054</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G13" s="4">
+        <f>(COUNTIFS('Features'!$A$3:$A$61,"F-028",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-028",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-029",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-029",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-030",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-030",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-043",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-043",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-054",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-054",'Features'!$G$3:$G$61,"in_review"))</f>
+        <v/>
+      </c>
+      <c r="H13" s="4">
+        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-028",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-029",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-030",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-043",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-054",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-028",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-028",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-029",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-029",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-030",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-030",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-043",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-043",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-054",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-054",'Features'!$G$3:$G$61,"in_review"))=5,"MET",IF((COUNTIFS('Features'!$A$3:$A$61,"F-028",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-028",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-029",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-029",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-030",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-030",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-043",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-043",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-054",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-054",'Features'!$G$3:$G$61,"in_review"))=0,"OPEN — 0 of 5","PARTIAL — "&amp;(COUNTIFS('Features'!$A$3:$A$61,"F-028",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-028",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-029",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-029",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-030",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-030",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-043",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-043",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-054",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-054",'Features'!$G$3:$G$61,"in_review"))&amp;" of 5")))</f>
+        <v/>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>Conditional on the asset-tracking decision. F-043 field edit history adds the temporal dimension on the strategy side.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="48" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>P-010</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Every marketing decision feels reactive.</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>F-008,F-022,F-038,F-053</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G14" s="4">
+        <f>(COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-038",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-038",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-053",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-053",'Features'!$G$3:$G$61,"in_review"))</f>
+        <v/>
+      </c>
+      <c r="H14" s="4">
+        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-038",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-053",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-038",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-038",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-053",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-053",'Features'!$G$3:$G$61,"in_review"))=4,"MET",IF((COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-038",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-038",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-053",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-053",'Features'!$G$3:$G$61,"in_review"))=0,"OPEN — 0 of 4","PARTIAL — "&amp;(COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-038",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-038",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-053",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-053",'Features'!$G$3:$G$61,"in_review"))&amp;" of 4")))</f>
+        <v/>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>Forensic Canvas as North Star (F-008), Coach for ongoing decisions (F-022), performance metrics (F-038) close the loop. F-053 lets decisions live at the angle level.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="H5:H14">
+    <cfRule type="expression" priority="1" dxfId="2">
+      <formula>H5="MET"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>ISNUMBER(SEARCH("BLOCKED",H5))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="1">
+      <formula>ISNUMBER(SEARCH("PARTIAL",H5))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="3">
+      <formula>ISNUMBER(SEARCH("OPEN",H5))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D5:D14">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="2">
+      <formula>"Yes"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="1">
+      <formula>"Partial"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="7" operator="equal" dxfId="3">
+      <formula>"No"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation sqref="C5:C64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Value must match one of the allowed options." type="list">
+      <formula1>"Alpha,Beta,GA,Post-GA"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D5:D64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Value must match one of the allowed options." type="list">
+      <formula1>"Yes,Partial,No"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -814,10 +1368,11 @@
     <col width="32" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="60" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -885,20 +1440,25 @@
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
+          <t>problems_addressed</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
           <t>effort_estimate_hours</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>actual_hours</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="O2" s="3" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
+      <c r="P2" s="3" t="inlineStr">
         <is>
           <t>last_updated</t>
         </is>
@@ -954,18 +1514,23 @@
           <t>F-018</t>
         </is>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>P-002</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="M3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="N3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t>Existing chat infrastructure (SupabaseChatService) is the substrate. Needs Trevor-voice prompt set + 10-Q question script wired.</t>
         </is>
       </c>
-      <c r="O3" s="8" t="n">
+      <c r="P3" s="8" t="n">
         <v>46155</v>
       </c>
     </row>
@@ -1019,18 +1584,19 @@
           <t>F-001,F-012</t>
         </is>
       </c>
-      <c r="L4" s="4" t="n">
+      <c r="L4" s="4" t="inlineStr"/>
+      <c r="M4" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="M4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="N4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>Field extraction pipeline exists; sidebar render needs to subscribe to extraction events.</t>
         </is>
       </c>
-      <c r="O4" s="8" t="n">
+      <c r="P4" s="8" t="n">
         <v>46155</v>
       </c>
     </row>
@@ -1084,18 +1650,23 @@
           <t>F-001,F-018</t>
         </is>
       </c>
-      <c r="L5" s="4" t="n">
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>P-003</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="M5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="4" t="inlineStr">
+      <c r="N5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="4" t="inlineStr">
         <is>
           <t>generate-brand-strategy-document edge function ships a unified strategy doc today. The Gen 3 Draft-vs-Forensic *tier* split (lighter doc after Layer 1, heavier after Avatar Builder) is the gap — current code doesn't distinguish them yet. DRAFT badge + Forensic upgrade CTA still needs design.</t>
         </is>
       </c>
-      <c r="O5" s="8" t="n">
+      <c r="P5" s="8" t="n">
         <v>46155</v>
       </c>
     </row>
@@ -1149,18 +1720,23 @@
           <t>F-003,F-009</t>
         </is>
       </c>
-      <c r="L6" s="4" t="n">
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>P-001,P-002</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="M6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="N6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="4" t="inlineStr">
         <is>
           <t>Gen 3 spec is the source of truth. Existing V2 PRD predates Gen 3; verify field list.</t>
         </is>
       </c>
-      <c r="O6" s="8" t="n">
+      <c r="P6" s="8" t="n">
         <v>46155</v>
       </c>
     </row>
@@ -1214,14 +1790,19 @@
           <t>F-004</t>
         </is>
       </c>
-      <c r="L7" s="4" t="n">
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>P-001,P-002</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="M7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="4" t="inlineStr"/>
-      <c r="O7" s="8" t="n">
+      <c r="N7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="4" t="inlineStr"/>
+      <c r="P7" s="8" t="n">
         <v>46155</v>
       </c>
     </row>
@@ -1275,18 +1856,23 @@
           <t>F-005</t>
         </is>
       </c>
-      <c r="L8" s="4" t="n">
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>P-001,P-002,P-006</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="M8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="N8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="4" t="inlineStr">
         <is>
           <t>Trigger Moment is Trevor's flagged most-important field — must surface prominently.</t>
         </is>
       </c>
-      <c r="O8" s="8" t="n">
+      <c r="P8" s="8" t="n">
         <v>46155</v>
       </c>
     </row>
@@ -1340,18 +1926,23 @@
           <t>F-006</t>
         </is>
       </c>
-      <c r="L9" s="4" t="n">
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>P-001,P-002,P-005,P-006</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="M9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="4" t="inlineStr">
+      <c r="N9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="4" t="inlineStr">
         <is>
           <t>Requires voice-of-customer-analysis edge function.</t>
         </is>
       </c>
-      <c r="O9" s="8" t="n">
+      <c r="P9" s="8" t="n">
         <v>46155</v>
       </c>
     </row>
@@ -1405,18 +1996,23 @@
           <t>F-004,F-005,F-006,F-007</t>
         </is>
       </c>
-      <c r="L10" s="4" t="n">
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>P-001,P-003,P-004,P-005,P-010</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="M10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="N10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="4" t="inlineStr">
         <is>
           <t>Brand strategy doc generation is the Forensic Canvas synthesis in current code: generate-brand-strategy-document (1164 LoC, pgvector RAG, Haiku, client-side orchestration to avoid 150s timeout) + generate-brand-strategy-section + MarkdownExportService. Remaining: explicit 'Strategic Entry Point' Trigger Moment callout and the Draft↔Forensic toggle (F-008.4). Sub-feature percent should override this.</t>
         </is>
       </c>
-      <c r="O10" s="8" t="n">
+      <c r="P10" s="8" t="n">
         <v>46155</v>
       </c>
     </row>
@@ -1470,18 +2066,23 @@
           <t>F-018</t>
         </is>
       </c>
-      <c r="L11" s="4" t="n">
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>P-001,P-002</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="M11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="4" t="inlineStr">
+      <c r="N11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="4" t="inlineStr">
         <is>
           <t>AIAssistant component exists for V2 fields; needs Gen 3 mode expansion.</t>
         </is>
       </c>
-      <c r="O11" s="8" t="n">
+      <c r="P11" s="8" t="n">
         <v>46155</v>
       </c>
     </row>
@@ -1531,18 +2132,19 @@
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr"/>
-      <c r="L12" s="4" t="n">
+      <c r="L12" s="4" t="inlineStr"/>
+      <c r="M12" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="M12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="4" t="inlineStr">
+      <c r="N12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="4" t="inlineStr">
         <is>
           <t>Existing V2 UI is form-shaped. Trevor's Risk Register flag: 'feels like a form, not a conversation' is Critical.</t>
         </is>
       </c>
-      <c r="O12" s="8" t="n">
+      <c r="P12" s="8" t="n">
         <v>46155</v>
       </c>
     </row>
@@ -1592,18 +2194,19 @@
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr"/>
-      <c r="L13" s="4" t="n">
+      <c r="L13" s="4" t="inlineStr"/>
+      <c r="M13" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="M13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="4" t="inlineStr">
+      <c r="N13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="4" t="inlineStr">
         <is>
           <t>Trust foundation per Trevor + existing PRD constraint. Partially present in V2 quality badge code.</t>
         </is>
       </c>
-      <c r="O13" s="8" t="n">
+      <c r="P13" s="8" t="n">
         <v>46155</v>
       </c>
     </row>
@@ -1653,18 +2256,23 @@
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr"/>
-      <c r="L14" s="4" t="n">
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>P-001</t>
+        </is>
+      </c>
+      <c r="M14" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="M14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="4" t="inlineStr">
+      <c r="N14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="4" t="inlineStr">
         <is>
           <t>Field extraction shipped recently (commit 77ae116 — IDEA Brand Coach quality score badges).</t>
         </is>
       </c>
-      <c r="O14" s="8" t="n">
+      <c r="P14" s="8" t="n">
         <v>46155</v>
       </c>
     </row>
@@ -1718,18 +2326,19 @@
           <t>F-003,F-017</t>
         </is>
       </c>
-      <c r="L15" s="4" t="n">
+      <c r="L15" s="4" t="inlineStr"/>
+      <c r="M15" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="M15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="4" t="inlineStr">
+      <c r="N15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="4" t="inlineStr">
         <is>
           <t>Spec lives in Launch Roadmap › Feedback Loop sheet.</t>
         </is>
       </c>
-      <c r="O15" s="8" t="n">
+      <c r="P15" s="8" t="n">
         <v>46155</v>
       </c>
     </row>
@@ -1783,18 +2392,19 @@
           <t>F-008,F-017</t>
         </is>
       </c>
-      <c r="L16" s="4" t="n">
+      <c r="L16" s="4" t="inlineStr"/>
+      <c r="M16" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="M16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="4" t="inlineStr">
+      <c r="N16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="4" t="inlineStr">
         <is>
           <t>% selecting 'update existing assets' is the Alpha→Beta asset-tracking gate.</t>
         </is>
       </c>
-      <c r="O16" s="8" t="n">
+      <c r="P16" s="8" t="n">
         <v>46155</v>
       </c>
     </row>
@@ -1848,18 +2458,19 @@
           <t>F-017</t>
         </is>
       </c>
-      <c r="L17" s="4" t="n">
+      <c r="L17" s="4" t="inlineStr"/>
+      <c r="M17" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="M17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="4" t="inlineStr">
+      <c r="N17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="4" t="inlineStr">
         <is>
           <t>Requires scheduled-send infrastructure (Resend / Supabase cron).</t>
         </is>
       </c>
-      <c r="O17" s="8" t="n">
+      <c r="P17" s="8" t="n">
         <v>46155</v>
       </c>
     </row>
@@ -1909,18 +2520,19 @@
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr"/>
-      <c r="L18" s="4" t="n">
+      <c r="L18" s="4" t="inlineStr"/>
+      <c r="M18" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="M18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="4" t="inlineStr">
+      <c r="N18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="4" t="inlineStr">
         <is>
           <t>Single destination simplifies the alpha findings synthesis step.</t>
         </is>
       </c>
-      <c r="O18" s="8" t="n">
+      <c r="P18" s="8" t="n">
         <v>46155</v>
       </c>
     </row>
@@ -1970,18 +2582,19 @@
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr"/>
-      <c r="L19" s="4" t="n">
+      <c r="L19" s="4" t="inlineStr"/>
+      <c r="M19" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="M19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="4" t="inlineStr">
+      <c r="N19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="4" t="inlineStr">
         <is>
           <t>Cheap to install. Risk Register flags that testers won't report half the bugs.</t>
         </is>
       </c>
-      <c r="O19" s="8" t="n">
+      <c r="P19" s="8" t="n">
         <v>46155</v>
       </c>
     </row>
@@ -2031,18 +2644,19 @@
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr"/>
-      <c r="L20" s="4" t="n">
+      <c r="L20" s="4" t="inlineStr"/>
+      <c r="M20" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="M20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="4" t="inlineStr">
+      <c r="N20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="4" t="inlineStr">
         <is>
           <t>No tutorial. Sets expectation that this is alpha and feedback is the deliverable.</t>
         </is>
       </c>
-      <c r="O20" s="8" t="n">
+      <c r="P20" s="8" t="n">
         <v>46155</v>
       </c>
     </row>
@@ -2096,18 +2710,19 @@
           <t>F-008</t>
         </is>
       </c>
-      <c r="L21" s="4" t="n">
+      <c r="L21" s="4" t="inlineStr"/>
+      <c r="M21" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="M21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" s="4" t="inlineStr">
+      <c r="N21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="4" t="inlineStr">
         <is>
           <t>Central conversion test of beta. Pay-gate previews must use real canvas data.</t>
         </is>
       </c>
-      <c r="O21" s="8" t="n">
+      <c r="P21" s="8" t="n">
         <v>46155</v>
       </c>
     </row>
@@ -2161,18 +2776,23 @@
           <t>F-008,F-019</t>
         </is>
       </c>
-      <c r="L22" s="4" t="n">
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>P-004,P-005</t>
+        </is>
+      </c>
+      <c r="M22" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="M22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" s="4" t="inlineStr">
+      <c r="N22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="4" t="inlineStr">
         <is>
           <t>First Create-mode output. Anchors the pay-gate preview.</t>
         </is>
       </c>
-      <c r="O22" s="8" t="n">
+      <c r="P22" s="8" t="n">
         <v>46155</v>
       </c>
     </row>
@@ -2226,14 +2846,19 @@
           <t>F-008,F-019</t>
         </is>
       </c>
-      <c r="L23" s="4" t="n">
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>P-004,P-005</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="M23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" s="4" t="inlineStr"/>
-      <c r="O23" s="8" t="n">
+      <c r="N23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="4" t="inlineStr"/>
+      <c r="P23" s="8" t="n">
         <v>46155</v>
       </c>
     </row>
@@ -2287,18 +2912,23 @@
           <t>F-008</t>
         </is>
       </c>
-      <c r="L24" s="4" t="n">
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>P-001,P-007,P-010</t>
+        </is>
+      </c>
+      <c r="M24" s="4" t="n">
         <v>56</v>
       </c>
-      <c r="M24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" s="4" t="inlineStr">
+      <c r="N24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="4" t="inlineStr">
         <is>
           <t>Required to deliver the £29/mo subscription value prop per Trevor's spec.</t>
         </is>
       </c>
-      <c r="O24" s="8" t="n">
+      <c r="P24" s="8" t="n">
         <v>46155</v>
       </c>
     </row>
@@ -2352,18 +2982,23 @@
           <t>F-003,F-008</t>
         </is>
       </c>
-      <c r="L25" s="4" t="n">
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>P-003</t>
+        </is>
+      </c>
+      <c r="M25" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="M25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" s="4" t="inlineStr">
+      <c r="N25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="4" t="inlineStr">
         <is>
           <t>PDF + Markdown shipped: BrandCanvasPDFExport, MarkdownPDFExporter, BrandMarkdownExport, generate-brand-strategy-pdf edge function. Word (.docx) export is the remaining gap. Once Draft/Forensic tier split lands in F-003/F-008, ensure both tiers export.</t>
         </is>
       </c>
-      <c r="O25" s="8" t="n">
+      <c r="P25" s="8" t="n">
         <v>46155</v>
       </c>
     </row>
@@ -2413,18 +3048,19 @@
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr"/>
-      <c r="L26" s="4" t="n">
+      <c r="L26" s="4" t="inlineStr"/>
+      <c r="M26" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="M26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" s="4" t="inlineStr">
+      <c r="N26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="4" t="inlineStr">
         <is>
           <t>Conversion data is the whole point of beta.</t>
         </is>
       </c>
-      <c r="O26" s="8" t="n">
+      <c r="P26" s="8" t="n">
         <v>46155</v>
       </c>
     </row>
@@ -2474,18 +3110,19 @@
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr"/>
-      <c r="L27" s="4" t="n">
+      <c r="L27" s="4" t="inlineStr"/>
+      <c r="M27" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="M27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" s="4" t="inlineStr">
+      <c r="N27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="4" t="inlineStr">
         <is>
           <t>Refund-rate risk is partly a support-responsiveness problem.</t>
         </is>
       </c>
-      <c r="O27" s="8" t="n">
+      <c r="P27" s="8" t="n">
         <v>46155</v>
       </c>
     </row>
@@ -2539,18 +3176,19 @@
           <t>F-015</t>
         </is>
       </c>
-      <c r="L28" s="4" t="n">
+      <c r="L28" s="4" t="inlineStr"/>
+      <c r="M28" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="M28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" s="4" t="inlineStr">
+      <c r="N28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="4" t="inlineStr">
         <is>
           <t>Target: 5+ verified testimonials by end of Beta; 10+ within 3 months.</t>
         </is>
       </c>
-      <c r="O28" s="8" t="n">
+      <c r="P28" s="8" t="n">
         <v>46155</v>
       </c>
     </row>
@@ -2600,18 +3238,19 @@
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr"/>
-      <c r="L29" s="4" t="n">
+      <c r="L29" s="4" t="inlineStr"/>
+      <c r="M29" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="M29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" s="4" t="inlineStr">
+      <c r="N29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" s="4" t="inlineStr">
         <is>
           <t>Diagnostic largely exists (FreeDiagnostic + BetaFeedback components). Handoff into Layer 1 still loose.</t>
         </is>
       </c>
-      <c r="O29" s="8" t="n">
+      <c r="P29" s="8" t="n">
         <v>46155</v>
       </c>
     </row>
@@ -2669,18 +3308,23 @@
           <t>F-014</t>
         </is>
       </c>
-      <c r="L30" s="4" t="n">
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>P-009</t>
+        </is>
+      </c>
+      <c r="M30" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="M30" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" s="4" t="inlineStr">
+      <c r="N30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="4" t="inlineStr">
         <is>
           <t>DEFERRED DECISION. Gate at end of Alpha. Default is NO. Trevor's Gen 3 spec does not include asset tracking — only ship if Moment 2 signal is ≥40%.</t>
         </is>
       </c>
-      <c r="O30" s="8" t="n">
+      <c r="P30" s="8" t="n">
         <v>46155</v>
       </c>
     </row>
@@ -2738,18 +3382,23 @@
           <t>F-028</t>
         </is>
       </c>
-      <c r="L31" s="4" t="n">
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>P-009</t>
+        </is>
+      </c>
+      <c r="M31" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="M31" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" s="4" t="inlineStr">
+      <c r="N31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="4" t="inlineStr">
         <is>
           <t>Introduces the temporal signal — user can see what's out of date.</t>
         </is>
       </c>
-      <c r="O31" s="8" t="n">
+      <c r="P31" s="8" t="n">
         <v>46155</v>
       </c>
     </row>
@@ -2807,18 +3456,23 @@
           <t>F-029</t>
         </is>
       </c>
-      <c r="L32" s="4" t="n">
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>P-009</t>
+        </is>
+      </c>
+      <c r="M32" s="4" t="n">
         <v>56</v>
       </c>
-      <c r="M32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" s="4" t="inlineStr">
+      <c r="N32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="4" t="inlineStr">
         <is>
           <t>Likely a GA-era feature per brief; listed for completeness.</t>
         </is>
       </c>
-      <c r="O32" s="8" t="n">
+      <c r="P32" s="8" t="n">
         <v>46155</v>
       </c>
     </row>
@@ -2872,18 +3526,23 @@
           <t>F-046</t>
         </is>
       </c>
-      <c r="L33" s="4" t="n">
+      <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>P-007</t>
+        </is>
+      </c>
+      <c r="M33" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="M33" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" s="4" t="inlineStr">
+      <c r="N33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="4" t="inlineStr">
         <is>
           <t>Power users will have multiple brands; product caps out at one customer without this.</t>
         </is>
       </c>
-      <c r="O33" s="8" t="n">
+      <c r="P33" s="8" t="n">
         <v>46155</v>
       </c>
     </row>
@@ -2937,18 +3596,19 @@
           <t>F-027</t>
         </is>
       </c>
-      <c r="L34" s="4" t="n">
+      <c r="L34" s="4" t="inlineStr"/>
+      <c r="M34" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="M34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" s="4" t="inlineStr">
+      <c r="N34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="4" t="inlineStr">
         <is>
           <t>Top-of-funnel users drop off without this.</t>
         </is>
       </c>
-      <c r="O34" s="8" t="n">
+      <c r="P34" s="8" t="n">
         <v>46155</v>
       </c>
     </row>
@@ -2998,18 +3658,19 @@
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr"/>
-      <c r="L35" s="4" t="n">
+      <c r="L35" s="4" t="inlineStr"/>
+      <c r="M35" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="M35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" s="4" t="inlineStr">
+      <c r="N35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="4" t="inlineStr">
         <is>
           <t>Public launch means support cost scales with users — self-serve protects margin.</t>
         </is>
       </c>
-      <c r="O35" s="8" t="n">
+      <c r="P35" s="8" t="n">
         <v>46155</v>
       </c>
     </row>
@@ -3063,18 +3724,19 @@
           <t>F-019</t>
         </is>
       </c>
-      <c r="L36" s="4" t="n">
+      <c r="L36" s="4" t="inlineStr"/>
+      <c r="M36" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="M36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" s="4" t="inlineStr">
+      <c r="N36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="4" t="inlineStr">
         <is>
           <t>Conversion surface for non-warm visitors.</t>
         </is>
       </c>
-      <c r="O36" s="8" t="n">
+      <c r="P36" s="8" t="n">
         <v>46155</v>
       </c>
     </row>
@@ -3124,18 +3786,19 @@
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr"/>
-      <c r="L37" s="4" t="n">
+      <c r="L37" s="4" t="inlineStr"/>
+      <c r="M37" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="M37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" s="4" t="inlineStr">
+      <c r="N37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="4" t="inlineStr">
         <is>
           <t>Trust signal required for paid users.</t>
         </is>
       </c>
-      <c r="O37" s="8" t="n">
+      <c r="P37" s="8" t="n">
         <v>46155</v>
       </c>
     </row>
@@ -3189,18 +3852,19 @@
           <t>F-025</t>
         </is>
       </c>
-      <c r="L38" s="4" t="n">
+      <c r="L38" s="4" t="inlineStr"/>
+      <c r="M38" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="M38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" s="4" t="inlineStr">
+      <c r="N38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="4" t="inlineStr">
         <is>
           <t>Reduces ticket volume and improves time-to-value.</t>
         </is>
       </c>
-      <c r="O38" s="8" t="n">
+      <c r="P38" s="8" t="n">
         <v>46155</v>
       </c>
     </row>
@@ -3250,18 +3914,19 @@
         </is>
       </c>
       <c r="K39" s="4" t="inlineStr"/>
-      <c r="L39" s="4" t="n">
+      <c r="L39" s="4" t="inlineStr"/>
+      <c r="M39" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="M39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" s="4" t="inlineStr">
+      <c r="N39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" s="4" t="inlineStr">
         <is>
           <t>Legal hygiene required for paid public product.</t>
         </is>
       </c>
-      <c r="O39" s="8" t="n">
+      <c r="P39" s="8" t="n">
         <v>46155</v>
       </c>
     </row>
@@ -3315,18 +3980,23 @@
           <t>F-046</t>
         </is>
       </c>
-      <c r="L40" s="4" t="n">
+      <c r="L40" s="4" t="inlineStr">
+        <is>
+          <t>P-010</t>
+        </is>
+      </c>
+      <c r="M40" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="M40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" s="4" t="inlineStr">
+      <c r="N40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="4" t="inlineStr">
         <is>
           <t>OPEN QUESTION: existing V2 PRD scopes this as a P0 V2 feature. Trevor's Gen 3 spec does not address it. Treated here as GA P0; needs Matthew sign-off.</t>
         </is>
       </c>
-      <c r="O40" s="8" t="n">
+      <c r="P40" s="8" t="n">
         <v>46155</v>
       </c>
     </row>
@@ -3380,18 +4050,19 @@
           <t>F-019</t>
         </is>
       </c>
-      <c r="L41" s="4" t="n">
+      <c r="L41" s="4" t="inlineStr"/>
+      <c r="M41" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="M41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" s="4" t="inlineStr">
+      <c r="N41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" s="4" t="inlineStr">
         <is>
           <t>Acquisition lever from GA Plan.</t>
         </is>
       </c>
-      <c r="O41" s="8" t="n">
+      <c r="P41" s="8" t="n">
         <v>46155</v>
       </c>
     </row>
@@ -3441,18 +4112,19 @@
         </is>
       </c>
       <c r="K42" s="4" t="inlineStr"/>
-      <c r="L42" s="4" t="n">
+      <c r="L42" s="4" t="inlineStr"/>
+      <c r="M42" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="M42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" s="4" t="inlineStr">
+      <c r="N42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" s="4" t="inlineStr">
         <is>
           <t>Brand strategist partner channel needs attribution before outreach.</t>
         </is>
       </c>
-      <c r="O42" s="8" t="n">
+      <c r="P42" s="8" t="n">
         <v>46155</v>
       </c>
     </row>
@@ -3502,18 +4174,19 @@
         </is>
       </c>
       <c r="K43" s="4" t="inlineStr"/>
-      <c r="L43" s="4" t="n">
+      <c r="L43" s="4" t="inlineStr"/>
+      <c r="M43" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="M43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" s="4" t="inlineStr">
+      <c r="N43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" s="4" t="inlineStr">
         <is>
           <t>Three-month organic ramp — start at beginning of beta to earn GA traffic.</t>
         </is>
       </c>
-      <c r="O43" s="8" t="n">
+      <c r="P43" s="8" t="n">
         <v>46155</v>
       </c>
     </row>
@@ -3567,18 +4240,23 @@
           <t>F-031</t>
         </is>
       </c>
-      <c r="L44" s="4" t="n">
+      <c r="L44" s="4" t="inlineStr">
+        <is>
+          <t>P-008</t>
+        </is>
+      </c>
+      <c r="M44" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="M44" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" s="4" t="inlineStr">
+      <c r="N44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" s="4" t="inlineStr">
         <is>
           <t>Power-user feature; rewards multi-canvas usage.</t>
         </is>
       </c>
-      <c r="O44" s="8" t="n">
+      <c r="P44" s="8" t="n">
         <v>46155</v>
       </c>
     </row>
@@ -3632,18 +4310,23 @@
           <t>F-046</t>
         </is>
       </c>
-      <c r="L45" s="4" t="n">
+      <c r="L45" s="4" t="inlineStr">
+        <is>
+          <t>P-009</t>
+        </is>
+      </c>
+      <c r="M45" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="M45" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" s="4" t="inlineStr">
+      <c r="N45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" s="4" t="inlineStr">
         <is>
           <t>Schema needs field_edit_history table.</t>
         </is>
       </c>
-      <c r="O45" s="8" t="n">
+      <c r="P45" s="8" t="n">
         <v>46155</v>
       </c>
     </row>
@@ -3697,18 +4380,19 @@
           <t>F-031</t>
         </is>
       </c>
-      <c r="L46" s="4" t="n">
+      <c r="L46" s="4" t="inlineStr"/>
+      <c r="M46" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="M46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" s="4" t="inlineStr">
+      <c r="N46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" s="4" t="inlineStr">
         <is>
           <t>Power-user feature.</t>
         </is>
       </c>
-      <c r="O46" s="8" t="n">
+      <c r="P46" s="8" t="n">
         <v>46155</v>
       </c>
     </row>
@@ -3762,18 +4446,19 @@
           <t>F-034</t>
         </is>
       </c>
-      <c r="L47" s="4" t="n">
+      <c r="L47" s="4" t="inlineStr"/>
+      <c r="M47" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="M47" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" s="4" t="inlineStr">
+      <c r="N47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" s="4" t="inlineStr">
         <is>
           <t>TikTok integration is GA+4wks per Launch Roadmap; not a build dependency.</t>
         </is>
       </c>
-      <c r="O47" s="8" t="n">
+      <c r="P47" s="8" t="n">
         <v>46155</v>
       </c>
     </row>
@@ -3827,14 +4512,15 @@
           <t>F-024</t>
         </is>
       </c>
-      <c r="L48" s="4" t="n">
+      <c r="L48" s="4" t="inlineStr"/>
+      <c r="M48" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="M48" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" s="4" t="inlineStr"/>
-      <c r="O48" s="8" t="n">
+      <c r="N48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" s="4" t="inlineStr"/>
+      <c r="P48" s="8" t="n">
         <v>46155</v>
       </c>
     </row>
@@ -3884,14 +4570,15 @@
         </is>
       </c>
       <c r="K49" s="4" t="inlineStr"/>
-      <c r="L49" s="4" t="n">
+      <c r="L49" s="4" t="inlineStr"/>
+      <c r="M49" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="M49" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" s="4" t="inlineStr"/>
-      <c r="O49" s="8" t="n">
+      <c r="N49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" s="4" t="inlineStr"/>
+      <c r="P49" s="8" t="n">
         <v>46155</v>
       </c>
     </row>
@@ -3941,18 +4628,19 @@
         </is>
       </c>
       <c r="K50" s="4" t="inlineStr"/>
-      <c r="L50" s="4" t="n">
+      <c r="L50" s="4" t="inlineStr"/>
+      <c r="M50" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="M50" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" s="4" t="inlineStr">
+      <c r="N50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" s="4" t="inlineStr">
         <is>
           <t>Pairs with UTM data to triangulate true attribution.</t>
         </is>
       </c>
-      <c r="O50" s="8" t="n">
+      <c r="P50" s="8" t="n">
         <v>46155</v>
       </c>
     </row>
@@ -4002,18 +4690,19 @@
         </is>
       </c>
       <c r="K51" s="4" t="inlineStr"/>
-      <c r="L51" s="4" t="n">
+      <c r="L51" s="4" t="inlineStr"/>
+      <c r="M51" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="M51" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" s="4" t="inlineStr">
+      <c r="N51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" s="4" t="inlineStr">
         <is>
           <t>Additive only. RLS policies in F-047.</t>
         </is>
       </c>
-      <c r="O51" s="8" t="n">
+      <c r="P51" s="8" t="n">
         <v>46155</v>
       </c>
     </row>
@@ -4067,14 +4756,15 @@
           <t>F-046</t>
         </is>
       </c>
-      <c r="L52" s="4" t="n">
+      <c r="L52" s="4" t="inlineStr"/>
+      <c r="M52" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="M52" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" s="4" t="inlineStr"/>
-      <c r="O52" s="8" t="n">
+      <c r="N52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" s="4" t="inlineStr"/>
+      <c r="P52" s="8" t="n">
         <v>46155</v>
       </c>
     </row>
@@ -4124,18 +4814,19 @@
         </is>
       </c>
       <c r="K53" s="4" t="inlineStr"/>
-      <c r="L53" s="4" t="n">
+      <c r="L53" s="4" t="inlineStr"/>
+      <c r="M53" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="M53" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" s="4" t="inlineStr">
+      <c r="N53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" s="4" t="inlineStr">
         <is>
           <t>idea-framework-consultant exists; Gen 3 functions partially overlap. Audit needed.</t>
         </is>
       </c>
-      <c r="O53" s="8" t="n">
+      <c r="P53" s="8" t="n">
         <v>46155</v>
       </c>
     </row>
@@ -4189,18 +4880,23 @@
           <t>F-048</t>
         </is>
       </c>
-      <c r="L54" s="4" t="n">
+      <c r="L54" s="4" t="inlineStr">
+        <is>
+          <t>P-007</t>
+        </is>
+      </c>
+      <c r="M54" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="M54" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" s="4" t="inlineStr">
+      <c r="N54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" s="4" t="inlineStr">
         <is>
           <t>OpenAI embeddings removed in commit 260128b (consolidated to Claude/internal embeddings) — verify RAG pipeline still wired.</t>
         </is>
       </c>
-      <c r="O54" s="8" t="n">
+      <c r="P54" s="8" t="n">
         <v>46155</v>
       </c>
     </row>
@@ -4250,18 +4946,19 @@
         </is>
       </c>
       <c r="K55" s="4" t="inlineStr"/>
-      <c r="L55" s="4" t="n">
+      <c r="L55" s="4" t="inlineStr"/>
+      <c r="M55" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="M55" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" s="4" t="inlineStr">
+      <c r="N55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" s="4" t="inlineStr">
         <is>
           <t>Hook already exists. Audit V2 routes for missing gates.</t>
         </is>
       </c>
-      <c r="O55" s="8" t="n">
+      <c r="P55" s="8" t="n">
         <v>46155</v>
       </c>
     </row>
@@ -4311,18 +5008,19 @@
         </is>
       </c>
       <c r="K56" s="4" t="inlineStr"/>
-      <c r="L56" s="4" t="n">
+      <c r="L56" s="4" t="inlineStr"/>
+      <c r="M56" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="M56" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" s="4" t="inlineStr">
+      <c r="N56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="4" t="inlineStr">
         <is>
           <t>Refactor patterns shipped (SupabaseChatService split, FieldSyncService, AIAssistant decomposition). Verify all Gen 3 work picks up new patterns.</t>
         </is>
       </c>
-      <c r="O56" s="8" t="n">
+      <c r="P56" s="8" t="n">
         <v>46155</v>
       </c>
     </row>
@@ -4376,18 +5074,23 @@
           <t>F-008,F-031</t>
         </is>
       </c>
-      <c r="L57" s="4" t="n">
+      <c r="L57" s="4" t="inlineStr">
+        <is>
+          <t>P-003,P-008,P-010</t>
+        </is>
+      </c>
+      <c r="M57" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="M57" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" s="4" t="inlineStr">
+      <c r="N57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" s="4" t="inlineStr">
         <is>
           <t>Validates A/B angle testing for paying users. Each angle = a strategy variant tied to a canonical avatar. Surfaces in Coach mode and Export. OPEN: schema choice — separate canvases per angle vs angle-tagged sections within one canvas.</t>
         </is>
       </c>
-      <c r="O57" s="8" t="n">
+      <c r="P57" s="8" t="n">
         <v>46155</v>
       </c>
     </row>
@@ -4445,18 +5148,23 @@
           <t>F-028,F-053</t>
         </is>
       </c>
-      <c r="L58" s="4" t="n">
+      <c r="L58" s="4" t="inlineStr">
+        <is>
+          <t>P-006,P-009</t>
+        </is>
+      </c>
+      <c r="M58" s="4" t="n">
         <v>56</v>
       </c>
-      <c r="M58" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" s="4" t="inlineStr">
+      <c r="N58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" s="4" t="inlineStr">
         <is>
           <t>Extension of asset_tracking that goes beyond text. Anchored to InfinityVault need N-002 (assess images/videos, identify what's missing, surface emotional-connection opportunities). Requires image storage (Supabase Storage) and a comparison UI.</t>
         </is>
       </c>
-      <c r="O58" s="8" t="n">
+      <c r="P58" s="8" t="n">
         <v>46155</v>
       </c>
     </row>
@@ -4510,18 +5218,23 @@
           <t>F-008,F-053</t>
         </is>
       </c>
-      <c r="L59" s="4" t="n">
+      <c r="L59" s="4" t="inlineStr">
+        <is>
+          <t>P-004,P-006,P-008</t>
+        </is>
+      </c>
+      <c r="M59" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="M59" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" s="4" t="inlineStr">
+      <c r="N59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" s="4" t="inlineStr">
         <is>
           <t>Sibling to F-020 (Amazon listing copy) and F-021 (Brand Voice Guide). Bridges the canvas to creative work. Required to make F-054 actionable (gap → brief → asset).</t>
         </is>
       </c>
-      <c r="O59" s="8" t="n">
+      <c r="P59" s="8" t="n">
         <v>46155</v>
       </c>
     </row>
@@ -4575,18 +5288,19 @@
           <t>F-055</t>
         </is>
       </c>
-      <c r="L60" s="4" t="n">
+      <c r="L60" s="4" t="inlineStr"/>
+      <c r="M60" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="M60" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" s="4" t="inlineStr">
+      <c r="N60" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" s="4" t="inlineStr">
         <is>
           <t>Surfaced as 'coming soon' in UI (teaser). Closes the loop from canvas → design brief → generated imagery. No model choice locked in; defer until Post-GA stability work is done.</t>
         </is>
       </c>
-      <c r="O60" s="8" t="n">
+      <c r="P60" s="8" t="n">
         <v>46155</v>
       </c>
     </row>
@@ -4640,30 +5354,31 @@
         </is>
       </c>
       <c r="K61" s="4" t="inlineStr"/>
-      <c r="L61" s="4" t="n">
+      <c r="L61" s="4" t="inlineStr"/>
+      <c r="M61" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="M61" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N61" s="4" t="inlineStr">
+      <c r="N61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" s="4" t="inlineStr">
         <is>
           <t>DEFERRED DECISION. Trevor's Gen 3 Brief specifies Lovable; existing codebase is React + Supabase. Don't half-port. Default: extend existing repo until Matthew decides otherwise.</t>
         </is>
       </c>
-      <c r="O61" s="8" t="n">
+      <c r="P61" s="8" t="n">
         <v>46155</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A1:P1"/>
   </mergeCells>
   <conditionalFormatting sqref="G3:G261">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="2">
       <formula>"complete"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="3">
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="4">
       <formula>"in_review"</formula>
     </cfRule>
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="1">
@@ -4672,7 +5387,7 @@
     <cfRule type="cellIs" priority="4" operator="equal" dxfId="0">
       <formula>"blocked"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="3">
       <formula>"not_started"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4694,7 +5409,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7624,7 +8339,7 @@
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="2">
       <formula>"complete"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="3">
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="4">
       <formula>"in_review"</formula>
     </cfRule>
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="1">
@@ -7633,7 +8348,7 @@
     <cfRule type="cellIs" priority="4" operator="equal" dxfId="0">
       <formula>"blocked"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="3">
       <formula>"not_started"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7646,7 +8361,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8515,7 +9230,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8722,7 +9437,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9415,7 +10130,7 @@
     <mergeCell ref="A1:I1"/>
   </mergeCells>
   <conditionalFormatting sqref="E4:E117">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="4">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="3">
       <formula>"monitoring"</formula>
     </cfRule>
     <cfRule type="cellIs" priority="2" operator="equal" dxfId="0">
@@ -9438,7 +10153,7 @@
     <cfRule type="cellIs" priority="7" operator="equal" dxfId="1">
       <formula>"Medium"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="8" operator="equal" dxfId="4">
+    <cfRule type="cellIs" priority="8" operator="equal" dxfId="3">
       <formula>"Low"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9457,13 +10172,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9545,6 +10260,28 @@
         </is>
       </c>
     </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Matthew (via Claude Code)</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Corrected status for brand strategy doc + PDF export; added Problems sheet</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>F-008 was wrongly marked not_started — corrected to in_review 80% based on shipped generate-brand-strategy-document. F-023 corrected to in_progress 65% (PDF + Markdown shipped, Word still missing). Added Problems sheet with the 10 problems we solve mapped to features; added problems_addressed column on Features.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>

--- a/docs/feature_status_tracker.xlsx
+++ b/docs/feature_status_tracker.xlsx
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="P3" s="8" t="n">
-        <v>46155</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="4" ht="42" customHeight="1">
@@ -1597,7 +1597,7 @@
         </is>
       </c>
       <c r="P4" s="8" t="n">
-        <v>46155</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="5" ht="42" customHeight="1">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="P5" s="8" t="n">
-        <v>46155</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1">
@@ -1737,7 +1737,7 @@
         </is>
       </c>
       <c r="P6" s="8" t="n">
-        <v>46155</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="7" ht="42" customHeight="1">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="O7" s="4" t="inlineStr"/>
       <c r="P7" s="8" t="n">
-        <v>46155</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="8" ht="42" customHeight="1">
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="P8" s="8" t="n">
-        <v>46155</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="9" ht="42" customHeight="1">
@@ -1943,7 +1943,7 @@
         </is>
       </c>
       <c r="P9" s="8" t="n">
-        <v>46155</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="10" ht="42" customHeight="1">
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="P10" s="8" t="n">
-        <v>46155</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="11" ht="42" customHeight="1">
@@ -2083,7 +2083,7 @@
         </is>
       </c>
       <c r="P11" s="8" t="n">
-        <v>46155</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="12" ht="42" customHeight="1">
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="P12" s="8" t="n">
-        <v>46155</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="13" ht="42" customHeight="1">
@@ -2207,7 +2207,7 @@
         </is>
       </c>
       <c r="P13" s="8" t="n">
-        <v>46155</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="14" ht="42" customHeight="1">
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="P14" s="8" t="n">
-        <v>46155</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="15" ht="42" customHeight="1">
@@ -2339,7 +2339,7 @@
         </is>
       </c>
       <c r="P15" s="8" t="n">
-        <v>46155</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="16" ht="42" customHeight="1">
@@ -2405,7 +2405,7 @@
         </is>
       </c>
       <c r="P16" s="8" t="n">
-        <v>46155</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="17" ht="42" customHeight="1">
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="P17" s="8" t="n">
-        <v>46155</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="18" ht="42" customHeight="1">
@@ -2533,7 +2533,7 @@
         </is>
       </c>
       <c r="P18" s="8" t="n">
-        <v>46155</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="19" ht="42" customHeight="1">
@@ -2595,7 +2595,7 @@
         </is>
       </c>
       <c r="P19" s="8" t="n">
-        <v>46155</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="20" ht="42" customHeight="1">
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="P20" s="8" t="n">
-        <v>46155</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="21" ht="42" customHeight="1">
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="P21" s="8" t="n">
-        <v>46155</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="22" ht="42" customHeight="1">
@@ -2793,7 +2793,7 @@
         </is>
       </c>
       <c r="P22" s="8" t="n">
-        <v>46155</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="23" ht="42" customHeight="1">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="O23" s="4" t="inlineStr"/>
       <c r="P23" s="8" t="n">
-        <v>46155</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="24" ht="42" customHeight="1">
@@ -2929,7 +2929,7 @@
         </is>
       </c>
       <c r="P24" s="8" t="n">
-        <v>46155</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="25" ht="42" customHeight="1">
@@ -2999,7 +2999,7 @@
         </is>
       </c>
       <c r="P25" s="8" t="n">
-        <v>46155</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="26" ht="42" customHeight="1">
@@ -3061,7 +3061,7 @@
         </is>
       </c>
       <c r="P26" s="8" t="n">
-        <v>46155</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="27" ht="42" customHeight="1">
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="P27" s="8" t="n">
-        <v>46155</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="28" ht="42" customHeight="1">
@@ -3189,7 +3189,7 @@
         </is>
       </c>
       <c r="P28" s="8" t="n">
-        <v>46155</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="29" ht="42" customHeight="1">
@@ -3251,7 +3251,7 @@
         </is>
       </c>
       <c r="P29" s="8" t="n">
-        <v>46155</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="30" ht="42" customHeight="1">
@@ -3325,7 +3325,7 @@
         </is>
       </c>
       <c r="P30" s="8" t="n">
-        <v>46155</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="31" ht="42" customHeight="1">
@@ -3399,7 +3399,7 @@
         </is>
       </c>
       <c r="P31" s="8" t="n">
-        <v>46155</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="32" ht="42" customHeight="1">
@@ -3473,7 +3473,7 @@
         </is>
       </c>
       <c r="P32" s="8" t="n">
-        <v>46155</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="33" ht="42" customHeight="1">
@@ -3543,7 +3543,7 @@
         </is>
       </c>
       <c r="P33" s="8" t="n">
-        <v>46155</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="34" ht="42" customHeight="1">
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="P34" s="8" t="n">
-        <v>46155</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="35" ht="42" customHeight="1">
@@ -3671,7 +3671,7 @@
         </is>
       </c>
       <c r="P35" s="8" t="n">
-        <v>46155</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="36" ht="42" customHeight="1">
@@ -3737,7 +3737,7 @@
         </is>
       </c>
       <c r="P36" s="8" t="n">
-        <v>46155</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="37" ht="42" customHeight="1">
@@ -3799,7 +3799,7 @@
         </is>
       </c>
       <c r="P37" s="8" t="n">
-        <v>46155</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="38" ht="42" customHeight="1">
@@ -3865,7 +3865,7 @@
         </is>
       </c>
       <c r="P38" s="8" t="n">
-        <v>46155</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="39" ht="42" customHeight="1">
@@ -3927,7 +3927,7 @@
         </is>
       </c>
       <c r="P39" s="8" t="n">
-        <v>46155</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="40" ht="42" customHeight="1">
@@ -3997,7 +3997,7 @@
         </is>
       </c>
       <c r="P40" s="8" t="n">
-        <v>46155</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="41" ht="42" customHeight="1">
@@ -4063,7 +4063,7 @@
         </is>
       </c>
       <c r="P41" s="8" t="n">
-        <v>46155</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="42" ht="42" customHeight="1">
@@ -4125,7 +4125,7 @@
         </is>
       </c>
       <c r="P42" s="8" t="n">
-        <v>46155</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="43" ht="42" customHeight="1">
@@ -4187,7 +4187,7 @@
         </is>
       </c>
       <c r="P43" s="8" t="n">
-        <v>46155</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="44" ht="42" customHeight="1">
@@ -4257,7 +4257,7 @@
         </is>
       </c>
       <c r="P44" s="8" t="n">
-        <v>46155</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="45" ht="42" customHeight="1">
@@ -4327,7 +4327,7 @@
         </is>
       </c>
       <c r="P45" s="8" t="n">
-        <v>46155</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="46" ht="42" customHeight="1">
@@ -4393,7 +4393,7 @@
         </is>
       </c>
       <c r="P46" s="8" t="n">
-        <v>46155</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="47" ht="42" customHeight="1">
@@ -4459,7 +4459,7 @@
         </is>
       </c>
       <c r="P47" s="8" t="n">
-        <v>46155</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="48" ht="42" customHeight="1">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="O48" s="4" t="inlineStr"/>
       <c r="P48" s="8" t="n">
-        <v>46155</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="49" ht="42" customHeight="1">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="O49" s="4" t="inlineStr"/>
       <c r="P49" s="8" t="n">
-        <v>46155</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="50" ht="42" customHeight="1">
@@ -4641,7 +4641,7 @@
         </is>
       </c>
       <c r="P50" s="8" t="n">
-        <v>46155</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="51" ht="42" customHeight="1">
@@ -4703,7 +4703,7 @@
         </is>
       </c>
       <c r="P51" s="8" t="n">
-        <v>46155</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="52" ht="42" customHeight="1">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="O52" s="4" t="inlineStr"/>
       <c r="P52" s="8" t="n">
-        <v>46155</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="53" ht="42" customHeight="1">
@@ -4827,7 +4827,7 @@
         </is>
       </c>
       <c r="P53" s="8" t="n">
-        <v>46155</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="54" ht="42" customHeight="1">
@@ -4897,7 +4897,7 @@
         </is>
       </c>
       <c r="P54" s="8" t="n">
-        <v>46155</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="55" ht="42" customHeight="1">
@@ -4959,7 +4959,7 @@
         </is>
       </c>
       <c r="P55" s="8" t="n">
-        <v>46155</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="56" ht="42" customHeight="1">
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="P56" s="8" t="n">
-        <v>46155</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="57" ht="42" customHeight="1">
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="P57" s="8" t="n">
-        <v>46155</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="58" ht="42" customHeight="1">
@@ -5165,7 +5165,7 @@
         </is>
       </c>
       <c r="P58" s="8" t="n">
-        <v>46155</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="59" ht="42" customHeight="1">
@@ -5235,7 +5235,7 @@
         </is>
       </c>
       <c r="P59" s="8" t="n">
-        <v>46155</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="60" ht="42" customHeight="1">
@@ -5301,7 +5301,7 @@
         </is>
       </c>
       <c r="P60" s="8" t="n">
-        <v>46155</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="61" ht="42" customHeight="1">
@@ -5367,7 +5367,7 @@
         </is>
       </c>
       <c r="P61" s="8" t="n">
-        <v>46155</v>
+        <v>46158</v>
       </c>
     </row>
   </sheetData>
@@ -10263,7 +10263,7 @@
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">

--- a/docs/feature_status_tracker.xlsx
+++ b/docs/feature_status_tracker.xlsx
@@ -9443,7 +9443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10125,11 +10125,58 @@
       </c>
       <c r="I17" s="4" t="inlineStr"/>
     </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>R-015</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Product doesn't solve enough user problems well enough to earn value</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>monitoring</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>At Alpha exit, fewer than 2 of {P-001, P-002, P-003} verified PARTIAL+ via tester debriefs; OR &lt;50% of testers can articulate one concrete way the canvas changed how they think about their customer; OR fewer than 60% of shipped features map to ≥1 problem.</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>Matthew</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>Problems sheet operationalises tracking. Alpha feedback Moments 1 + 2 measure perceived value directly. If signal is low at Alpha midpoint, narrow scope to deepen 1-2 problems rather than adding features.</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>Meta-risk above R-003 (form not conversation) and R-007 (no testimonials). The failure mode where every feature ships on time but the product still doesn't matter to anyone. Operational tool: the Problems sheet — every feature should tag to at least one problem.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
-  <conditionalFormatting sqref="E4:E117">
+  <conditionalFormatting sqref="E4:E118">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="3">
       <formula>"monitoring"</formula>
     </cfRule>
@@ -10143,7 +10190,7 @@
       <formula>"resolved"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D4:D117">
+  <conditionalFormatting sqref="D4:D118">
     <cfRule type="cellIs" priority="5" operator="equal" dxfId="5">
       <formula>"Critical"</formula>
     </cfRule>
@@ -10158,13 +10205,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="C4:C117" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Value must match one of the allowed options." type="list">
+    <dataValidation sqref="C4:C118" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Value must match one of the allowed options." type="list">
       <formula1>"Alpha,Beta,GA,Post-GA,All"</formula1>
     </dataValidation>
-    <dataValidation sqref="D4:D117" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Value must match one of the allowed options." type="list">
+    <dataValidation sqref="D4:D118" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Value must match one of the allowed options." type="list">
       <formula1>"Critical,High,Medium,Low"</formula1>
     </dataValidation>
-    <dataValidation sqref="E4:E117" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Value must match one of the allowed options." type="list">
+    <dataValidation sqref="E4:E118" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Value must match one of the allowed options." type="list">
       <formula1>"monitoring,triggered,mitigated,resolved"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/feature_status_tracker.xlsx
+++ b/docs/feature_status_tracker.xlsx
@@ -9519,17 +9519,17 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Alpha testers don't complete the flow</t>
+          <t>Product doesn't solve enough user problems well enough to earn value</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Alpha</t>
+          <t>All</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -9539,7 +9539,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>&lt;5 of 8 complete full flow by day 7</t>
+          <t>At Alpha exit, fewer than 2 of {P-001, P-002, P-003} verified PARTIAL+ via tester debriefs; OR &lt;50% of testers can articulate one concrete way the canvas changed how they think about their customer; OR fewer than 60% of shipped features map to ≥1 problem.</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
@@ -9549,10 +9549,14 @@
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>Pre-flight QA checklist + daily monitoring + aggressive debrief follow-up planned</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr"/>
+          <t>Problems sheet operationalises tracking. Alpha feedback Moments 1 + 2 measure perceived value directly. If signal is low at Alpha midpoint, narrow scope to deepen 1-2 problems rather than adding features.</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>Meta-risk above R-004 (form not conversation) and R-008 (no testimonials). The failure mode where every feature ships on time but the product still doesn't matter to anyone. Operational tool: the Problems sheet — every feature should tag to at least one problem.</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="42" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -9562,7 +9566,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Trevor's voice doesn't land for younger demographic</t>
+          <t>Alpha testers don't complete the flow</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -9572,7 +9576,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -9582,17 +9586,17 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>3+ testers flag 'sounds old' or 'corporate'</t>
+          <t>&lt;5 of 8 complete full flow by day 7</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>Trevor</t>
+          <t>Matthew</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>Mixed-experience tester pool; tone question in feedback Moment 1</t>
+          <t>Pre-flight QA checklist + daily monitoring + aggressive debrief follow-up planned</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr"/>
@@ -9605,7 +9609,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Avatar Builder feels like a form not a conversation</t>
+          <t>Trevor's voice doesn't land for younger demographic</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -9615,7 +9619,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -9625,24 +9629,20 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Any tester says 'this is just a long form'</t>
+          <t>3+ testers flag 'sounds old' or 'corporate'</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>Matthew</t>
+          <t>Trevor</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>F-009 AI assistance wired before alpha; F-010 progressive disclosure tested; question phrasing reviewed by Trevor</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>Kills Trevor's core thesis if it materialises.</t>
-        </is>
-      </c>
+          <t>Mixed-experience tester pool; tone question in feedback Moment 1</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
     </row>
     <row r="7" ht="42" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Pay gate conversion too low</t>
+          <t>Avatar Builder feels like a form not a conversation</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Beta</t>
+          <t>Alpha</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -9672,7 +9672,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>&lt;8% Draft viewers convert at 4-week mark</t>
+          <t>Any tester says 'this is just a long form'</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -9682,10 +9682,14 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>Pay-gate previews use actual canvas data; pricing differentiated by job not features; A/B test framing</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr"/>
+          <t>F-009 AI assistance wired before alpha; F-010 progressive disclosure tested; question phrasing reviewed by Trevor</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>Kills Trevor's core thesis if it materialises. Specific symptom of R-001.</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="42" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -9695,7 +9699,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Refund rate is high</t>
+          <t>Pay gate conversion too low</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -9705,7 +9709,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -9715,7 +9719,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>&gt;10% refund rate</t>
+          <t>&lt;8% Draft viewers convert at 4-week mark</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
@@ -9725,7 +9729,7 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>Forensic canvas over-delivers vs pay-gate promise; 14-day refund window</t>
+          <t>Pay-gate previews use actual canvas data; pricing differentiated by job not features; A/B test framing</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr"/>
@@ -9738,7 +9742,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Asset tracking sucks Beta scope dry</t>
+          <t>Refund rate is high</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -9758,7 +9762,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Builder spending &gt;2 weeks on asset tracking in beta phase</t>
+          <t>&gt;10% refund rate</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -9768,7 +9772,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>Decision gate at end of Alpha with hard threshold; v1 only if shipped</t>
+          <t>Forensic canvas over-delivers vs pay-gate promise; 14-day refund window</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr"/>
@@ -9781,7 +9785,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>ROI testimonials don't materialise</t>
+          <t>Asset tracking sucks Beta scope dry</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -9791,7 +9795,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -9801,7 +9805,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>&lt;3 testimonials by week 4 of beta</t>
+          <t>Builder spending &gt;2 weeks on asset tracking in beta phase</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -9811,14 +9815,10 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>Testimonial harvest sequence baked in from day 1; results-focused user selection</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>Kills the marketing engine if it materialises.</t>
-        </is>
-      </c>
+          <t>Decision gate at end of Alpha with hard threshold; v1 only if shipped</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr"/>
     </row>
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
@@ -9828,12 +9828,12 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>GA acquisition CAC too high</t>
+          <t>ROI testimonials don't materialise</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>Beta</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -9848,7 +9848,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Paid CAC payback &gt;4 months after 30 days of spend</t>
+          <t>&lt;3 testimonials by week 4 of beta</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
@@ -9858,10 +9858,14 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>Build organic foundation in beta; don't scale paid until CAC payback known</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr"/>
+          <t>Testimonial harvest sequence baked in from day 1; results-focused user selection</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>Kills the marketing engine if it materialises. Downstream symptom of R-001.</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="42" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
@@ -9871,7 +9875,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Retention below unit economics floor</t>
+          <t>GA acquisition CAC too high</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -9881,7 +9885,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -9891,7 +9895,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>&lt;50% retention at week 4</t>
+          <t>Paid CAC payback &gt;4 months after 30 days of spend</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -9901,7 +9905,7 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>Retention motion built before GA; quarterly Voice of Customer refresh designed in</t>
+          <t>Build organic foundation in beta; don't scale paid until CAC payback known</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr"/>
@@ -9914,17 +9918,17 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>TikTok algorithm de-prioritises long-form B2B content</t>
+          <t>Retention below unit economics floor</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Post-GA</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -9934,7 +9938,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Organic engagement &lt;2% after 30 days of content</t>
+          <t>&lt;50% retention at week 4</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
@@ -9944,7 +9948,7 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Organic test before paid; cap spend at £500/wk in test phase</t>
+          <t>Retention motion built before GA; quarterly Voice of Customer refresh designed in</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr"/>
@@ -9957,12 +9961,12 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Trevor's bandwidth limits content production</t>
+          <t>TikTok algorithm de-prioritises long-form B2B content</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Post-GA</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -9977,7 +9981,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Trevor unavailable &gt;2 weeks consecutively</t>
+          <t>Organic engagement &lt;2% after 30 days of content</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
@@ -9987,7 +9991,7 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>Batch recording; async content review; develop a second voice as backup</t>
+          <t>Organic test before paid; cap spend at £500/wk in test phase</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr"/>
@@ -10000,27 +10004,27 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Lovable.dev vs existing codebase architectural collision</t>
+          <t>Trevor's bandwidth limits content production</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Alpha</t>
+          <t>All</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>triggered</t>
+          <t>monitoring</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Two parallel codebases active &gt;1 week</t>
+          <t>Trevor unavailable &gt;2 weeks consecutively</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
@@ -10030,14 +10034,10 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>Decide explicitly at sprint start which is canonical (F-052)</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>Status set to triggered because the decision is currently open and Gen 3 work is paused on this call.</t>
-        </is>
-      </c>
+          <t>Batch recording; async content review; develop a second voice as backup</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr"/>
     </row>
     <row r="16" ht="42" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
@@ -10047,27 +10047,27 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Competitor launches similar tool</t>
+          <t>Lovable.dev vs existing codebase architectural collision</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Beta</t>
+          <t>Alpha</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>monitoring</t>
+          <t>triggered</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Competitor announcement or feature ship</t>
+          <t>Two parallel codebases active &gt;1 week</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
@@ -10077,10 +10077,14 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>Speed; first-mover positioning on Forensic Avatar Builder; lean into Voice of Customer differentiator</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="inlineStr"/>
+          <t>Decide explicitly at sprint start which is canonical (F-052)</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>Status set to triggered because the decision is currently open and Gen 3 work is paused on this call.</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="42" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
@@ -10090,17 +10094,17 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Trevor changes framework spec mid-build</t>
+          <t>Competitor launches similar tool</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Beta</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -10110,7 +10114,7 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Any framework field change requested post-Alpha launch</t>
+          <t>Competitor announcement or feature ship</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
@@ -10120,7 +10124,7 @@
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>Lock the v2 Brief; require written sign-off on changes; version-tag the build</t>
+          <t>Speed; first-mover positioning on Forensic Avatar Builder; lean into Voice of Customer differentiator</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr"/>
@@ -10133,7 +10137,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Product doesn't solve enough user problems well enough to earn value</t>
+          <t>Trevor changes framework spec mid-build</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -10143,7 +10147,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -10153,7 +10157,7 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>At Alpha exit, fewer than 2 of {P-001, P-002, P-003} verified PARTIAL+ via tester debriefs; OR &lt;50% of testers can articulate one concrete way the canvas changed how they think about their customer; OR fewer than 60% of shipped features map to ≥1 problem.</t>
+          <t>Any framework field change requested post-Alpha launch</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
@@ -10163,14 +10167,10 @@
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>Problems sheet operationalises tracking. Alpha feedback Moments 1 + 2 measure perceived value directly. If signal is low at Alpha midpoint, narrow scope to deepen 1-2 problems rather than adding features.</t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>Meta-risk above R-003 (form not conversation) and R-007 (no testimonials). The failure mode where every feature ships on time but the product still doesn't matter to anyone. Operational tool: the Problems sheet — every feature should tag to at least one problem.</t>
-        </is>
-      </c>
+          <t>Lock the v2 Brief; require written sign-off on changes; version-tag the build</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/docs/feature_status_tracker.xlsx
+++ b/docs/feature_status_tracker.xlsx
@@ -1501,7 +1501,7 @@
         </is>
       </c>
       <c r="H3" s="7" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="I3" s="4" t="inlineStr"/>
       <c r="J3" s="4" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="O3" s="4" t="inlineStr">
         <is>
-          <t>Existing chat infrastructure (SupabaseChatService) is the substrate. Needs Trevor-voice prompt set + 10-Q question script wired.</t>
+          <t>AUDIT 2026-05-16: Trevor persona prompt + free-form Claude streaming exist; the *10-question script* and per-question off-topic fallbacks DO NOT (F-001.1/F-001.2). Streaming + persistence are solid. Mobile keyboard handling minimal.</t>
         </is>
       </c>
       <c r="P3" s="8" t="n">
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="H4" s="7" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="I4" s="4" t="inlineStr"/>
       <c r="J4" s="4" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="O4" s="4" t="inlineStr">
         <is>
-          <t>Field extraction pipeline exists; sidebar render needs to subscribe to extraction events.</t>
+          <t>AUDIT 2026-05-16: Field-extraction → sidebar pipeline is mature (F-002.1, 80%). Quality badges render BUT use value heuristics (fieldQualityScore) not extractor confidence — acceptance criterion not literally met (F-002.2 reduced from 100→75). Mobile sheet works but state not persisted (F-002.3).</t>
         </is>
       </c>
       <c r="P4" s="8" t="n">
@@ -1637,7 +1637,7 @@
         </is>
       </c>
       <c r="H5" s="7" t="n">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="I5" s="4" t="inlineStr"/>
       <c r="J5" s="4" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
-          <t>generate-brand-strategy-document edge function ships a unified strategy doc today. The Gen 3 Draft-vs-Forensic *tier* split (lighter doc after Layer 1, heavier after Avatar Builder) is the gap — current code doesn't distinguish them yet. DRAFT badge + Forensic upgrade CTA still needs design.</t>
+          <t>AUDIT 2026-05-16: Tier distinction is conceptual only — zero structural code hits for 'DRAFT'/'tier'. Synthesis with Trevor voice exists (generate-brand-strategy-section + voice.ts) but generates the full doc, not a Draft subset. DRAFT badge and Forensic upgrade CTA both 0%.</t>
         </is>
       </c>
       <c r="P5" s="8" t="n">
@@ -1703,11 +1703,11 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>not_started</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="H6" s="7" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="I6" s="4" t="inlineStr"/>
       <c r="J6" s="4" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
-          <t>Gen 3 spec is the source of truth. Existing V2 PRD predates Gen 3; verify field list.</t>
+          <t>AUDIT 2026-05-16: V2 chapter UI delivers progressive disclosure + persistence well, but field schema flattens Gen 3 psychographic dimensions into coarse textareas (F-004.1 60%). 3 of 4 AI modes present; FieldChatButton missing from V2 (F-004.3 35%). Completion gate logic exists but button not mounted in render tree (F-004.5 55%).</t>
         </is>
       </c>
       <c r="P6" s="8" t="n">
@@ -1773,11 +1773,11 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>not_started</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="H7" s="7" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="I7" s="4" t="inlineStr"/>
       <c r="J7" s="4" t="inlineStr">
@@ -1801,7 +1801,11 @@
       <c r="N7" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="O7" s="4" t="inlineStr"/>
+      <c r="O7" s="4" t="inlineStr">
+        <is>
+          <t>AUDIT 2026-05-16: V2 chapter map has no dedicated 'Buying Behaviour' chapter — closest is BUYER_INTENT which is conceptually different. V1 AvatarBuilder has the right tab. Data shape exists; UI split V1↔V2.</t>
+        </is>
+      </c>
       <c r="P7" s="8" t="n">
         <v>46158</v>
       </c>
@@ -1839,11 +1843,11 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>not_started</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="H8" s="7" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="I8" s="4" t="inlineStr"/>
       <c r="J8" s="4" t="inlineStr">
@@ -1869,7 +1873,7 @@
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>Trigger Moment is Trevor's flagged most-important field — must surface prominently.</t>
+          <t>AUDIT 2026-05-16: Emotional fields exist (EMOTIONAL_CONNECTION + CUSTOMER_EXPERIENCE chapters) but Gen 3 Emotional Journey framing absent; Trigger Moment field with elevated visual treatment (F-006.2) is the most prominent miss — zero hits in codebase.</t>
         </is>
       </c>
       <c r="P8" s="8" t="n">
@@ -1909,11 +1913,11 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>not_started</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="H9" s="7" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I9" s="4" t="inlineStr"/>
       <c r="J9" s="4" t="inlineStr">
@@ -1939,7 +1943,7 @@
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>Requires voice-of-customer-analysis edge function.</t>
+          <t>AUDIT 2026-05-16: Review intake is URL/ASIN-driven via ReviewAnalyzerModal (scrape model), not Gen 3 paste-raw-reviews model. voice-of-customer-analysis edge function DOES NOT EXIST. V1 analysis is fully mocked. Use/discard phrase cards (F-007.3) ~10%.</t>
         </is>
       </c>
       <c r="P9" s="8" t="n">
@@ -1979,11 +1983,11 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>in_review</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="H10" s="7" t="n">
-        <v>80</v>
+        <v>39</v>
       </c>
       <c r="I10" s="4" t="inlineStr"/>
       <c r="J10" s="4" t="inlineStr">
@@ -2009,7 +2013,7 @@
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>Brand strategy doc generation is the Forensic Canvas synthesis in current code: generate-brand-strategy-document (1164 LoC, pgvector RAG, Haiku, client-side orchestration to avoid 150s timeout) + generate-brand-strategy-section + MarkdownExportService. Remaining: explicit 'Strategic Entry Point' Trigger Moment callout and the Draft↔Forensic toggle (F-008.4). Sub-feature percent should override this.</t>
+          <t>AUDIT 2026-05-16: 35-field schema exists (exceeds 28+) and Markdown export pipeline is mature, but Forensic *tier* differentiation does NOT exist — single unified synthesis path. Trigger Moment 'Strategic Entry Point' callout (F-008.3) and Draft↔Forensic toggle (F-008.4) both 0%. Rollup dropped from 80→39%: the doc ships, but the criteria asking for tier-specific behaviour are unmet.</t>
         </is>
       </c>
       <c r="P10" s="8" t="n">
@@ -2053,7 +2057,7 @@
         </is>
       </c>
       <c r="H11" s="7" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="I11" s="4" t="inlineStr"/>
       <c r="J11" s="4" t="inlineStr">
@@ -2079,7 +2083,7 @@
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>AIAssistant component exists for V2 fields; needs Gen 3 mode expansion.</t>
+          <t>AUDIT 2026-05-16: Only ONE AI mode is independently invocable — a single 'Generate with AI' button per field (AIButton.tsx). 'Think About This' and 'Real-World Examples' modes don't exist; 'Auto-Populate' is delivered implicitly via chat extraction + ghost text. No 4-mode selector UI. Rollup dropped from 30→19%.</t>
         </is>
       </c>
       <c r="P11" s="8" t="n">
@@ -2119,11 +2123,11 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>in_progress</t>
+          <t>not_started</t>
         </is>
       </c>
       <c r="H12" s="7" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="I12" s="4" t="inlineStr"/>
       <c r="J12" s="4" t="inlineStr">
@@ -2141,7 +2145,7 @@
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>Existing V2 UI is form-shaped. Trevor's Risk Register flag: 'feels like a form, not a conversation' is Critical.</t>
+          <t>AUDIT 2026-05-16: shadcn Accordion used informally for chapter disclosure; no documented disclosure pattern, no mobile-first audit committed. Rollup dropped from 25→3%.</t>
         </is>
       </c>
       <c r="P12" s="8" t="n">
@@ -2185,7 +2189,7 @@
         </is>
       </c>
       <c r="H13" s="7" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I13" s="4" t="inlineStr"/>
       <c r="J13" s="4" t="inlineStr">
@@ -2203,7 +2207,7 @@
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>Trust foundation per Trevor + existing PRD constraint. Partially present in V2 quality badge code.</t>
+          <t>AUDIT 2026-05-16: field_source ('ai'|'manual') exists and survives reload BUT is not the same as a 'manuallyEdited' boolean — system pairs it with separate is_locked user-toggle. AI overwrite guard works only for *explicitly locked* fields (F-011.2 65%), not for manually edited unlocked ones. F-011.1 reduced from 100→70% in_review.</t>
         </is>
       </c>
       <c r="P13" s="8" t="n">
@@ -2247,7 +2251,7 @@
         </is>
       </c>
       <c r="H14" s="7" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="I14" s="4" t="inlineStr"/>
       <c r="J14" s="4" t="inlineStr">
@@ -2269,7 +2273,7 @@
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>Field extraction shipped recently (commit 77ae116 — IDEA Brand Coach quality score badges).</t>
+          <t>AUDIT 2026-05-16: Edge function returns confidence scores (F-012.1 85%), but no confidence→badge mapping is implemented (F-012.2 was 100% wrongly — now 50%). Two unrelated badge systems coexist (heuristic on sidebar, percentage on chat).</t>
         </is>
       </c>
       <c r="P14" s="8" t="n">
@@ -2335,7 +2339,7 @@
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>Spec lives in Launch Roadmap › Feedback Loop sheet.</t>
+          <t>AUDIT 2026-05-16: Nothing exists. BrandCanvas page has no first-view detection, no modal, no 'entry signal' question copy, no moment-tagged write path. Greenfield build needed.</t>
         </is>
       </c>
       <c r="P15" s="8" t="n">
@@ -2401,7 +2405,7 @@
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>% selecting 'update existing assets' is the Alpha→Beta asset-tracking gate.</t>
+          <t>AUDIT 2026-05-16: Nothing exists. No inline panel, no 'use intent' multi-select, no 'update existing assets' option (which drives the asset-tracking gate), no moment-2 write path. Greenfield build needed.</t>
         </is>
       </c>
       <c r="P16" s="8" t="n">
@@ -2467,7 +2471,7 @@
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>Requires scheduled-send infrastructure (Resend / Supabase cron).</t>
+          <t>AUDIT 2026-05-16: Nothing exists. No scheduled-send infrastructure (pg_cron not enabled, no day-offset queue), no 14-day email template, no inbound reply parsing. Resend exists only for synchronous send-framework-email (different feature). Greenfield build needed.</t>
         </is>
       </c>
       <c r="P17" s="8" t="n">
@@ -2529,7 +2533,7 @@
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>Single destination simplifies the alpha findings synthesis step.</t>
+          <t>AUDIT 2026-05-16: Existing beta_feedback table is wide-form (overall_rating/liked_most/improvements/issues) — wrong shape for moment-tagged events. Need new feedback_events table with (moment, user_id, timestamp, payload JSONB). Existing BetaFeedback infrastructure will NOT compose — treat as separate older system; build moment infra fresh.</t>
         </is>
       </c>
       <c r="P18" s="8" t="n">
@@ -2591,7 +2595,7 @@
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>Cheap to install. Risk Register flags that testers won't report half the bugs.</t>
+          <t>AUDIT 2026-05-16: Nothing exists. No Sentry/Rollbar/Bugsnag/LogRocket/Datadog in package.json. ErrorBoundary.tsx only console.errors with a commented placeholder. No source-map upload, no CI workflows directory. Greenfield install.</t>
         </is>
       </c>
       <c r="P19" s="8" t="n">
@@ -2631,11 +2635,11 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>not_started</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="H20" s="7" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I20" s="4" t="inlineStr"/>
       <c r="J20" s="4" t="inlineStr">
@@ -2653,7 +2657,7 @@
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>No tutorial. Sets expectation that this is alpha and feedback is the deliverable.</t>
+          <t>AUDIT 2026-05-16: BetaWelcome page exists at /beta but is a self-serve registration form gated by localStorage — not auto-shown on first login, doesn't name Trevor or framework, not dismissable. StartHere has a Vimeo intro (not Loom). No invitation template, no 'first 10'/'7-day'/'30-min debrief' language. Resend not configured for invitations.</t>
         </is>
       </c>
       <c r="P20" s="8" t="n">
@@ -5523,11 +5527,11 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>in_progress</t>
+          <t>not_started</t>
         </is>
       </c>
       <c r="G3" s="7" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="H3" s="4" t="n">
         <v>8</v>
@@ -5538,7 +5542,7 @@
       <c r="J3" s="4" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>Pull canonical wording from Trevor's Knowledge doc.</t>
+          <t>Trevor persona prompt exists (idea-framework-consultant-claude/prompt.ts) and FIELD_QUESTIONS bank has 110 candidates (src/config/fieldQuestions.ts), but no 10-question script, no fixed rendering order, getFieldQuestion() is dead code.</t>
         </is>
       </c>
     </row>
@@ -5570,11 +5574,11 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>in_progress</t>
+          <t>not_started</t>
         </is>
       </c>
       <c r="G4" s="7" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="H4" s="4" t="n">
         <v>6</v>
@@ -5583,7 +5587,11 @@
         <v>0</v>
       </c>
       <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="4" t="inlineStr"/>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>Two empty-response fallbacks exist (edge function stream.ts:129-137 + ChatService:166-173) but they trigger on 'no text', not off-topic. No per-question fallback variation, no Trevor-voice phrasing.</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="42" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -5628,7 +5636,7 @@
       <c r="J5" s="4" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>Leverages existing local-first sync.</t>
+          <t>Session + message + chapter-progress persistence all work and survive refresh (useChatSessions, useChat, useChapterProgress); missing piece is an explicit 'last unanswered question' pointer (free-form conversation has no scripted position to resume to).</t>
         </is>
       </c>
     </row>
@@ -5664,7 +5672,7 @@
         </is>
       </c>
       <c r="G6" s="7" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H6" s="4" t="n">
         <v>8</v>
@@ -5675,7 +5683,7 @@
       <c r="J6" s="4" t="inlineStr"/>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>Capture raw SSE bytes to distinguish frontend fallback from edge function errors (see feedback_sse_stream_capture).</t>
+          <t>Streaming pipeline (edge SSE → ChatStreamParser → React state → ChatMessageList) is wired end-to-end and works; SSE-error-to-Trevor-voice fallback NOT met (errors render as generic destructive toast). No &lt;500ms latency assertion.</t>
         </is>
       </c>
     </row>
@@ -5707,11 +5715,11 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>not_started</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="G7" s="7" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H7" s="4" t="n">
         <v>6</v>
@@ -5722,7 +5730,7 @@
       <c r="J7" s="4" t="inlineStr"/>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>Mobile-primary testers are &gt;=50% of the alpha pool.</t>
+          <t>Basic mobile-friendly touch targets, pb-safe padding, and 16px font (avoids iOS zoom) in ChatInputBar; missing VisualViewport API usage, keyboard-show scroll-into-view, and no cross-device validation.</t>
         </is>
       </c>
     </row>
@@ -5758,7 +5766,7 @@
         </is>
       </c>
       <c r="G8" s="7" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="H8" s="4" t="n">
         <v>8</v>
@@ -5767,7 +5775,11 @@
         <v>0</v>
       </c>
       <c r="J8" s="4" t="inlineStr"/>
-      <c r="K8" s="4" t="inlineStr"/>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>Field-extraction events flow edge SSE → useChat → useFieldExtractionOrchestrator → ChapterSectionAccordion (auto-expands affected chapter, surfaces pending ghost values); behaviour-complete but no latency test and applied via 'pending ghost' rather than direct write.</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="42" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
@@ -5797,11 +5809,11 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="G9" s="7" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>4</v>
@@ -5812,7 +5824,7 @@
       <c r="J9" s="4" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>Quality badges shipped in commit 77ae116.</t>
+          <t>Quality badges render with tiered colors on sidebar fields (ChapterFieldSet:112-135), but they reflect value-quality heuristics (fieldQualityScore.ts word-count/specificity) rather than the AI extraction confidence score — acceptance criterion 'low-confidence amber, high-confidence green from extractor confidence' is not literally met.</t>
         </is>
       </c>
     </row>
@@ -5844,11 +5856,11 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>not_started</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="G10" s="7" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H10" s="4" t="n">
         <v>4</v>
@@ -5857,7 +5869,11 @@
         <v>0</v>
       </c>
       <c r="J10" s="4" t="inlineStr"/>
-      <c r="K10" s="4" t="inlineStr"/>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>Mobile sheet overlay for chapter panel works (TwoPanelTemplate:129-141 + BookOpen-icon toggle); state is in-memory only (useState in useBrandCoachV2State), does not persist across navigation; trigger is BookOpen icon, not hamburger.</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
@@ -5900,7 +5916,11 @@
         <v>0</v>
       </c>
       <c r="J11" s="4" t="inlineStr"/>
-      <c r="K11" s="4" t="inlineStr"/>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>No DRAFT badge component. Tier distinction is conceptual only — grep across src/ + edge functions for 'DRAFT'/'tier'/'forensic' returns ~zero structural hits. Gold/amber tokens exist (hsl(var(--gold-warm))) as mount-ready primitives.</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="42" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
@@ -5934,7 +5954,7 @@
         </is>
       </c>
       <c r="G12" s="7" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H12" s="4" t="n">
         <v>12</v>
@@ -5945,7 +5965,7 @@
       <c r="J12" s="4" t="inlineStr"/>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>Existing function present; needs Gen 3 prompt update.</t>
+          <t>Per-section synthesis with Trevor voice (generate-brand-strategy-section + voice.ts TREVOR_VOICE_DIRECTIVE on Haiku) exists but generates the full document — no Draft-tier subset, no low-confidence flagging, no &lt;8s latency guarantee. Reusable as Draft once a tier filter is added.</t>
         </is>
       </c>
     </row>
@@ -5990,7 +6010,11 @@
         <v>0</v>
       </c>
       <c r="J13" s="4" t="inlineStr"/>
-      <c r="K13" s="4" t="inlineStr"/>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>No Forensic upgrade CTA anywhere. BrandCoachHeader and inline section locations exist as natural mount points; 'upgrade' string returns no matches in BrandCanvas.tsx/BrandCoachV2.tsx.</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="42" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
@@ -6033,7 +6057,11 @@
         <v>0</v>
       </c>
       <c r="J14" s="4" t="inlineStr"/>
-      <c r="K14" s="4" t="inlineStr"/>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>Blocked on F-003.1/F-003.2 producing a distinct Draft output to review. Trevor sign-off process not documented in repo.</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="42" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
@@ -6063,11 +6091,11 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>not_started</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="G15" s="7" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H15" s="4" t="n">
         <v>4</v>
@@ -6076,7 +6104,11 @@
         <v>0</v>
       </c>
       <c r="J15" s="4" t="inlineStr"/>
-      <c r="K15" s="4" t="inlineStr"/>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>TypeScript schema (AvatarPsychographics in src/types/avatar.ts) matches Gen 3 (values/fears/desires/triggers arrays) and persists via avatars table JSONB column. BUT: V2 chapter UI (CUSTOMER_AVATAR chapter in chapterFields.ts:176-220) flattens into two coarse textareas; Avatar 2.0 five-field discrete schema (skills/04-avatar-five-fields.md) NOT modelled as typed fields.</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="42" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
@@ -6106,11 +6138,11 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>not_started</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="G16" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H16" s="4" t="n">
         <v>12</v>
@@ -6119,7 +6151,11 @@
         <v>0</v>
       </c>
       <c r="J16" s="4" t="inlineStr"/>
-      <c r="K16" s="4" t="inlineStr"/>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>Accordion delivers '&lt;=4 fields at once on mobile' (ChapterSectionAccordion:241-289 + active-chapter-only-open pattern; mobile Sheet via TwoPanelTemplate). Progressive disclosure is at chapter level, not Gen 3 sub-section level.</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="42" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
@@ -6149,11 +6185,11 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>not_started</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="G17" s="7" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H17" s="4" t="n">
         <v>8</v>
@@ -6164,7 +6200,7 @@
       <c r="J17" s="4" t="inlineStr"/>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>Depends on F-009.</t>
+          <t>Three of four AI modes exist as shared infra (ghost text via GhostTextFieldWrapper; review modal via AdaptiveFieldReview; chat-extracted badges via FieldExtractionBadges). The fourth (FieldChatButton used in V1 AvatarBuilder) is NOT integrated into V2 ChapterFieldSet.</t>
         </is>
       </c>
     </row>
@@ -6196,11 +6232,11 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>not_started</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="G18" s="7" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H18" s="4" t="n">
         <v>4</v>
@@ -6209,7 +6245,11 @@
         <v>0</v>
       </c>
       <c r="J18" s="4" t="inlineStr"/>
-      <c r="K18" s="4" t="inlineStr"/>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>Persistence + resume via FieldPersistenceService + localStorage + realtime subscription (useFieldExtraction:104-449). Tested in src/hooks/__tests__/useFieldExtraction.test.tsx.</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="42" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
@@ -6239,11 +6279,11 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>not_started</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="G19" s="7" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H19" s="4" t="n">
         <v>4</v>
@@ -6254,7 +6294,7 @@
       <c r="J19" s="4" t="inlineStr"/>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>Gen 3 spec discourages hard gates; mirror that here.</t>
+          <t>Validation logic in useChapterProceeding (58-131): all-required-fields check, auto-accept pending ghost text, flash first empty field. BUT: button surface not mounted in BrandCoachV2.tsx render tree. 'Required-minimum' enforcement is all-required, not Gen 3 minimum-subset.</t>
         </is>
       </c>
     </row>
@@ -6286,11 +6326,11 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>not_started</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="G20" s="7" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H20" s="4" t="n">
         <v>4</v>
@@ -6299,7 +6339,11 @@
         <v>0</v>
       </c>
       <c r="J20" s="4" t="inlineStr"/>
-      <c r="K20" s="4" t="inlineStr"/>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>AvatarBuyingBehavior type (src/types/avatar.ts:48-60) with persistence exists. BUT: V2 chapter map has no dedicated 'Buying Behaviour' chapter — closest is BUYER_INTENT which is conceptually buyer-intent not buying-behavior. Shopper Type taxonomy (skills/04) not codified.</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="42" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
@@ -6329,11 +6373,11 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>not_started</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="G21" s="7" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H21" s="4" t="n">
         <v>12</v>
@@ -6342,7 +6386,11 @@
         <v>0</v>
       </c>
       <c r="J21" s="4" t="inlineStr"/>
-      <c r="K21" s="4" t="inlineStr"/>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>V1 AvatarBuilder.tsx:309 has a 'Buying Behavior' tab with the right fields. V2 (the surface being tracked) does NOT have a discrete Buying Behaviour chapter; data shape exists but UI is split between V1 tab and V2 BUYER_INTENT chapter.</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="42" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
@@ -6372,11 +6420,11 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>not_started</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="G22" s="7" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H22" s="4" t="n">
         <v>8</v>
@@ -6385,7 +6433,11 @@
         <v>0</v>
       </c>
       <c r="J22" s="4" t="inlineStr"/>
-      <c r="K22" s="4" t="inlineStr"/>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>Same gap as F-004.3 — three of four AI modes via shared ChapterFieldSet; FieldChatButton (V1 only) missing from V2.</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="42" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
@@ -6415,11 +6467,11 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>not_started</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="G23" s="7" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H23" s="4" t="n">
         <v>4</v>
@@ -6428,7 +6480,11 @@
         <v>0</v>
       </c>
       <c r="J23" s="4" t="inlineStr"/>
-      <c r="K23" s="4" t="inlineStr"/>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>Persistence via shared FieldPersistenceService + realtime subscription; closing/reopening restores via DB + localStorage merge.</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="42" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
@@ -6458,11 +6514,11 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>not_started</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="G24" s="7" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H24" s="4" t="n">
         <v>4</v>
@@ -6473,7 +6529,7 @@
       <c r="J24" s="4" t="inlineStr"/>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>Trevor flagged Trigger Moment as the single most important field.</t>
+          <t>Emotional fields exist (EMOTIONAL_CONNECTION chapter:378-413 + CUSTOMER_EXPERIENCE chapter:415-450) but Gen 3 'Emotional Journey Mapping' framing with distinguished Trigger Moment NOT present; emotionalTriggers is a flat array, not a journey.</t>
         </is>
       </c>
     </row>
@@ -6518,7 +6574,11 @@
         <v>0</v>
       </c>
       <c r="J25" s="4" t="inlineStr"/>
-      <c r="K25" s="4" t="inlineStr"/>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>'Trigger Moment' as a distinct field with elevated visual treatment does not exist. Zero matches for 'Trigger Moment'/'trigger_moment' in src/. ChapterFieldSet renders all fields identically; no per-field visual emphasis system.</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="42" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
@@ -6548,11 +6608,11 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>not_started</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="G26" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H26" s="4" t="n">
         <v>12</v>
@@ -6561,7 +6621,11 @@
         <v>0</v>
       </c>
       <c r="J26" s="4" t="inlineStr"/>
-      <c r="K26" s="4" t="inlineStr"/>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>Same accordion progressive-disclosure mechanics as F-004.2 apply to EMOTIONAL_CONNECTION chapter (3 fields, under 4-field mobile target).</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="42" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
@@ -6591,11 +6655,11 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>not_started</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="G27" s="7" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H27" s="4" t="n">
         <v>12</v>
@@ -6604,7 +6668,11 @@
         <v>0</v>
       </c>
       <c r="J27" s="4" t="inlineStr"/>
-      <c r="K27" s="4" t="inlineStr"/>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>General AI assistance carries through; no Trigger-Moment-specific prompts in brand-ai-assistant/index.ts or idea-framework-consultant-claude/.</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="42" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
@@ -6634,11 +6702,11 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>not_started</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="G28" s="7" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H28" s="4" t="n">
         <v>4</v>
@@ -6647,7 +6715,11 @@
         <v>0</v>
       </c>
       <c r="J28" s="4" t="inlineStr"/>
-      <c r="K28" s="4" t="inlineStr"/>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>Inherited from shared FieldPersistenceService + realtime subscription.</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="42" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
@@ -6677,11 +6749,11 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>not_started</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="G29" s="7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H29" s="4" t="n">
         <v>8</v>
@@ -6690,7 +6762,11 @@
         <v>0</v>
       </c>
       <c r="J29" s="4" t="inlineStr"/>
-      <c r="K29" s="4" t="inlineStr"/>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>Review intake exists but is URL/ASIN-driven via ReviewAnalyzerModal:199-219 (scrape model), not the Gen 3 paste-raw-reviews-and-chunk model. V1 has a raw voiceOfCustomer textarea (AvatarBuilder.tsx:140-146).</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="42" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
@@ -6720,11 +6796,11 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>not_started</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="G30" s="7" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H30" s="4" t="n">
         <v>16</v>
@@ -6735,7 +6811,7 @@
       <c r="J30" s="4" t="inlineStr"/>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>Critical for differentiation per Trevor.</t>
+          <t>voice-of-customer-analysis edge function does NOT exist. review-scraper / review-scraper-deep edge functions exist but only scrape, don't rank phrases with frequency + valence. V1 analysis (analyzeVoiceOfCustomer at AvatarBuilder.tsx:217-274) is fully MOCKED (setTimeout + hardcoded data).</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6847,7 @@
         </is>
       </c>
       <c r="G31" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H31" s="4" t="n">
         <v>8</v>
@@ -6780,7 +6856,11 @@
         <v>0</v>
       </c>
       <c r="J31" s="4" t="inlineStr"/>
-      <c r="K31" s="4" t="inlineStr"/>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>No extracted-phrase UI with use/discard actions exists. V1 shows mock keyPhrases as text; ReviewAnalyzerModal shows review counts + ratings, no phrase-level flag-and-keep cards.</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="42" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
@@ -6810,11 +6890,11 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>not_started</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="G32" s="7" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H32" s="4" t="n">
         <v>4</v>
@@ -6823,7 +6903,11 @@
         <v>0</v>
       </c>
       <c r="J32" s="4" t="inlineStr"/>
-      <c r="K32" s="4" t="inlineStr"/>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>Raw voiceOfCustomer paste persists via usePersistedField in V1; flagged phrases have no persistence because the flag UI doesn't exist.</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="42" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
@@ -6853,11 +6937,11 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>not_started</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="G33" s="7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H33" s="4" t="n">
         <v>4</v>
@@ -6866,7 +6950,11 @@
         <v>0</v>
       </c>
       <c r="J33" s="4" t="inlineStr"/>
-      <c r="K33" s="4" t="inlineStr"/>
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>35-field canvas schema exists across 11 chapters (src/config/chapterFields.ts:99-537 + src/types/chapter.ts; UI confirms '35 fields captured'). Exceeds 28+ threshold but no explicit 'Forensic Canvas' label; field-by-field Gen 3 reconciliation outstanding.</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="42" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
@@ -6896,11 +6984,11 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>not_started</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="G34" s="7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H34" s="4" t="n">
         <v>16</v>
@@ -6909,7 +6997,11 @@
         <v>0</v>
       </c>
       <c r="J34" s="4" t="inlineStr"/>
-      <c r="K34" s="4" t="inlineStr"/>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>Full-canvas synthesis works end-to-end (two paths: generate-brand-strategy-document v1/gpt-4o 1164L; generate-brand-strategy-section v2/Haiku per-section + MarkdownExportService orchestration). No Draft/Forensic differentiation — single unified pipeline; output is Markdown not enforced JSON. v1/v2 are pipeline versions, NOT tier versions.</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="42" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
@@ -6954,7 +7046,7 @@
       <c r="J35" s="4" t="inlineStr"/>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>Trevor flagged this explicitly.</t>
+          <t>'Trigger Moment' / 'Strategic Entry Point' concept absent from code — zero structural hits across src/ and edge functions. No field, callout, schema entry, or generator section captures it.</t>
         </is>
       </c>
     </row>
@@ -7001,7 +7093,7 @@
       <c r="J36" s="4" t="inlineStr"/>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>Core demonstration of value per Alpha Plan.</t>
+          <t>No two synthesis outputs exist to compare (single unified path). No toggle component, no diff renderer. Prerequisites in F-003.2 + F-008.2 missing.</t>
         </is>
       </c>
     </row>
@@ -7033,11 +7125,11 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>not_started</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="G37" s="7" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H37" s="4" t="n">
         <v>4</v>
@@ -7048,7 +7140,7 @@
       <c r="J37" s="4" t="inlineStr"/>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>Reuses existing canvas-markdown design (see CANVAS_MARKDOWN_EXPORT_DESIGN.md).</t>
+          <t>Markdown export pipeline is mature (MarkdownExportService + BrandMarkdownExport + templates/sections/ for BrandCanvas, CustomerAvatar, IDEAFramework, etc.). Round-trip (parse back into canvas) not implemented — export is one-way.</t>
         </is>
       </c>
     </row>
@@ -7080,11 +7172,11 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>in_progress</t>
+          <t>not_started</t>
         </is>
       </c>
       <c r="G38" s="7" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H38" s="4" t="n">
         <v>8</v>
@@ -7095,7 +7187,7 @@
       <c r="J38" s="4" t="inlineStr"/>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>AIAssistant component scaffolding exists.</t>
+          <t>No 'Think About This' mode. AIAssistant uses a single 'Generate with AI' button → brand-ai-assistant edge function whose prompt explicitly says 'Generate the ACTUAL content for the field, not suggestions or feedback' — opposite of reflective questions. contextual-help/index.ts exists but isn't wired to a 'Think About This' surface.</t>
         </is>
       </c>
     </row>
@@ -7127,11 +7219,11 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>in_progress</t>
+          <t>not_started</t>
         </is>
       </c>
       <c r="G39" s="7" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H39" s="4" t="n">
         <v>8</v>
@@ -7140,7 +7232,11 @@
         <v>0</v>
       </c>
       <c r="J39" s="4" t="inlineStr"/>
-      <c r="K39" s="4" t="inlineStr"/>
+      <c r="K39" s="4" t="inlineStr">
+        <is>
+          <t>No 'Real-World Examples' mode. brand-ai-assistant returns single suggestion text only. RAG infra (sync-diagnostic-to-embeddings) exists but for user KB, not anonymised System KB examples.</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="42" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
@@ -7174,7 +7270,7 @@
         </is>
       </c>
       <c r="G40" s="7" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="H40" s="4" t="n">
         <v>8</v>
@@ -7183,7 +7279,11 @@
         <v>0</v>
       </c>
       <c r="J40" s="4" t="inlineStr"/>
-      <c r="K40" s="4" t="inlineStr"/>
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t>Single-suggestion generator works end-to-end (AIAssistant → AISuggestionHandler → brand-ai-assistant edge function, with accept/reject preview). Missing the '2-3 alternatives' criterion and the explicit mode label.</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="42" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
@@ -7217,7 +7317,7 @@
         </is>
       </c>
       <c r="G41" s="7" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="H41" s="4" t="n">
         <v>12</v>
@@ -7226,7 +7326,11 @@
         <v>0</v>
       </c>
       <c r="J41" s="4" t="inlineStr"/>
-      <c r="K41" s="4" t="inlineStr"/>
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>Chat-driven auto-extraction populates many fields with lock-skip logic (useFieldExtraction:179-248, line 192 skips locked); GhostTextFieldWrapper Tab-accept exists. NO dedicated per-field 'Auto-Populate' button. Manual-edit-aware overwrite is lock-based, not edit-flag-based.</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="42" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
@@ -7256,11 +7360,11 @@
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>in_progress</t>
+          <t>not_started</t>
         </is>
       </c>
       <c r="G42" s="7" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="H42" s="4" t="n">
         <v>12</v>
@@ -7271,7 +7375,7 @@
       <c r="J42" s="4" t="inlineStr"/>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>AISuggestionHandler component exists.</t>
+          <t>No 4-mode selector UI. AIButton.tsx:32-52 is a single 'Generate with AI' button per field. Tooltip explaining modes absent.</t>
         </is>
       </c>
     </row>
@@ -7303,11 +7407,11 @@
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>in_progress</t>
+          <t>not_started</t>
         </is>
       </c>
       <c r="G43" s="7" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H43" s="4" t="n">
         <v>4</v>
@@ -7316,7 +7420,11 @@
         <v>0</v>
       </c>
       <c r="J43" s="4" t="inlineStr"/>
-      <c r="K43" s="4" t="inlineStr"/>
+      <c r="K43" s="4" t="inlineStr">
+        <is>
+          <t>shadcn Accordion is used informally as the chapter-disclosure pattern (ChapterSectionAccordion) but no documented disclosure pattern guide; docs/lovable/04_UI_DESIGN_SYSTEM.md doesn't formalise it.</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="42" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
@@ -7346,11 +7454,11 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>in_progress</t>
+          <t>not_started</t>
         </is>
       </c>
       <c r="G44" s="7" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H44" s="4" t="n">
         <v>4</v>
@@ -7359,7 +7467,11 @@
         <v>0</v>
       </c>
       <c r="J44" s="4" t="inlineStr"/>
-      <c r="K44" s="4" t="inlineStr"/>
+      <c r="K44" s="4" t="inlineStr">
+        <is>
+          <t>No mobile-first audit report committed. Responsive behaviour exists per-component (e.g., GhostTextFieldWrapper:102 hides on mobile) but no systematic audit document, no tracked gap list.</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="42" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
@@ -7389,11 +7501,11 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>in_review</t>
         </is>
       </c>
       <c r="G45" s="7" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="H45" s="4" t="n">
         <v>4</v>
@@ -7404,7 +7516,7 @@
       <c r="J45" s="4" t="inlineStr"/>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>Partially shipped with quality badge work.</t>
+          <t>field_source: 'ai' | 'manual' exists (useFieldExtraction:35-43, setFieldManual:299-312) and survives reload (FieldPersistenceService:65-125). NOT the same as a 'manuallyEdited' boolean — system pairs it with separate is_locked user-toggle. Spec ambiguity: manual edit alone does NOT trigger overwrite protection; only an explicit lock does.</t>
         </is>
       </c>
     </row>
@@ -7440,7 +7552,7 @@
         </is>
       </c>
       <c r="G46" s="7" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H46" s="4" t="n">
         <v>4</v>
@@ -7449,7 +7561,11 @@
         <v>0</v>
       </c>
       <c r="J46" s="4" t="inlineStr"/>
-      <c r="K46" s="4" t="inlineStr"/>
+      <c r="K46" s="4" t="inlineStr">
+        <is>
+          <t>AI overwrite guard works for chat extraction (useFieldExtraction:190-203) and realtime sync (399-422), but ONLY when user explicitly locked the field (useFieldLocking.setFieldLock). No automatic guard for manually-edited-but-unlocked fields. Per-field AIAssistant button bypasses lock entirely.</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="42" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
@@ -7483,7 +7599,7 @@
         </is>
       </c>
       <c r="G47" s="7" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H47" s="4" t="n">
         <v>4</v>
@@ -7492,7 +7608,11 @@
         <v>0</v>
       </c>
       <c r="J47" s="4" t="inlineStr"/>
-      <c r="K47" s="4" t="inlineStr"/>
+      <c r="K47" s="4" t="inlineStr">
+        <is>
+          <t>Amber border/bg on FieldExtractionBadges:42-43 indicates lock, but no dedicated lock icon, no tooltip explaining it, no user-facing toggle. setFieldLock is only called programmatically.</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="42" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
@@ -7526,7 +7646,7 @@
         </is>
       </c>
       <c r="G48" s="7" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="H48" s="4" t="n">
         <v>12</v>
@@ -7537,7 +7657,7 @@
       <c r="J48" s="4" t="inlineStr"/>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>Recent commits indicate substantial work shipped.</t>
+          <t>Edge function returns field updates with 0-1 confidence via streaming tool-use (idea-framework-consultant-claude/tools.ts:54-93 + stream.ts:93-105); confidence flows through orchestrator; missing latency assertion/test and dedicated tool extraction tests.</t>
         </is>
       </c>
     </row>
@@ -7569,11 +7689,11 @@
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="G49" s="7" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H49" s="4" t="n">
         <v>4</v>
@@ -7584,7 +7704,7 @@
       <c r="J49" s="4" t="inlineStr"/>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>Shipped (commit 77ae116).</t>
+          <t>Two distinct badge systems exist (heuristic quality tiers on sidebar via fieldQualityScore.ts; raw percentage on chat badges in FieldExtractionBadges:194-198) but neither is a documented confidence→badge mapping — spec criterion 'Mapping documented; consistent across fields' is not met.</t>
         </is>
       </c>
     </row>
@@ -7629,7 +7749,11 @@
         <v>0</v>
       </c>
       <c r="J50" s="4" t="inlineStr"/>
-      <c r="K50" s="4" t="inlineStr"/>
+      <c r="K50" s="4" t="inlineStr">
+        <is>
+          <t>No re-extraction-on-edit behaviour. Pasting a paragraph into a single field just stores it as that field's value with no offer to split. ChapterFieldSet handleInputChange has no multi-field detection.</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="42" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
@@ -7672,7 +7796,11 @@
         <v>0</v>
       </c>
       <c r="J51" s="4" t="inlineStr"/>
-      <c r="K51" s="4" t="inlineStr"/>
+      <c r="K51" s="4" t="inlineStr">
+        <is>
+          <t>No modal trigger exists. BrandCanvas page has no first-view detection or modal mounting; nothing distinguishes 'Draft' vs 'Forensic' canvas state.</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="42" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
@@ -7715,7 +7843,11 @@
         <v>0</v>
       </c>
       <c r="J52" s="4" t="inlineStr"/>
-      <c r="K52" s="4" t="inlineStr"/>
+      <c r="K52" s="4" t="inlineStr">
+        <is>
+          <t>No entry-signal question copy or component. Existing BetaFeedback form is generic rating/likes/issues, unrelated to 'did the conversation reveal new territory'.</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="42" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
@@ -7760,7 +7892,7 @@
       <c r="J53" s="4" t="inlineStr"/>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>Depends on F-016.</t>
+          <t>No write path tagged 'moment_1' or 'entry_signal'. Existing save-beta-feedback edge function lacks moment discriminator; central sheet (F-016) hasn't been designed.</t>
         </is>
       </c>
     </row>
@@ -7805,7 +7937,11 @@
         <v>0</v>
       </c>
       <c r="J54" s="4" t="inlineStr"/>
-      <c r="K54" s="4" t="inlineStr"/>
+      <c r="K54" s="4" t="inlineStr">
+        <is>
+          <t>No inline panel rendered below Canvas. No concept of 'Forensic Canvas' distinct rendering state in the codebase to gate the panel against.</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="42" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
@@ -7850,7 +7986,7 @@
       <c r="J55" s="4" t="inlineStr"/>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>Critical for asset-tracking gate.</t>
+          <t>No multi-select question component or option set. The 'update existing assets' option that drives the asset-tracking decision gate is entirely unbuilt.</t>
         </is>
       </c>
     </row>
@@ -7895,7 +8031,11 @@
         <v>0</v>
       </c>
       <c r="J56" s="4" t="inlineStr"/>
-      <c r="K56" s="4" t="inlineStr"/>
+      <c r="K56" s="4" t="inlineStr">
+        <is>
+          <t>No Moment-2-specific write path. Would need new endpoint or moment_type discriminator on existing endpoint plus F-016 sheet.</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="42" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
@@ -7938,7 +8078,11 @@
         <v>0</v>
       </c>
       <c r="J57" s="4" t="inlineStr"/>
-      <c r="K57" s="4" t="inlineStr"/>
+      <c r="K57" s="4" t="inlineStr">
+        <is>
+          <t>No scheduled-send infrastructure. pg_cron not enabled, no day-offset queue table, no idempotency keys. Only synchronous Resend call exists (send-framework-email) for a different feature.</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="42" customHeight="1">
       <c r="A58" s="4" t="inlineStr">
@@ -7981,7 +8125,11 @@
         <v>0</v>
       </c>
       <c r="J58" s="4" t="inlineStr"/>
-      <c r="K58" s="4" t="inlineStr"/>
+      <c r="K58" s="4" t="inlineStr">
+        <is>
+          <t>No 14-day email template, no inbound reply parsing webhook. Resend inbound parsing not configured.</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="42" customHeight="1">
       <c r="A59" s="4" t="inlineStr">
@@ -8024,7 +8172,11 @@
         <v>0</v>
       </c>
       <c r="J59" s="4" t="inlineStr"/>
-      <c r="K59" s="4" t="inlineStr"/>
+      <c r="K59" s="4" t="inlineStr">
+        <is>
+          <t>Existing beta_feedback table is wide-form (overall_rating, liked_most, improvements, issues) — wrong shape. F-016 spec requires narrow event-row schema (moment, user_id, timestamp, payload JSONB).</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="42" customHeight="1">
       <c r="A60" s="4" t="inlineStr">
@@ -8067,7 +8219,11 @@
         <v>0</v>
       </c>
       <c r="J60" s="4" t="inlineStr"/>
-      <c r="K60" s="4" t="inlineStr"/>
+      <c r="K60" s="4" t="inlineStr">
+        <is>
+          <t>No write path from the three moments exists, because the three moments themselves don't exist. The endpoint exists but the contract is wrong for moment-tagged events.</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="42" customHeight="1">
       <c r="A61" s="4" t="inlineStr">
@@ -8110,7 +8266,11 @@
         <v>0</v>
       </c>
       <c r="J61" s="4" t="inlineStr"/>
-      <c r="K61" s="4" t="inlineStr"/>
+      <c r="K61" s="4" t="inlineStr">
+        <is>
+          <t>No Sentry (or Rollbar/Bugsnag/LogRocket/Datadog) dep in package.json or lock. ErrorBoundary.tsx:58-61 has only a commented-out placeholder; errors only console.error'd. No edge function error helper.</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="42" customHeight="1">
       <c r="A62" s="4" t="inlineStr">
@@ -8153,7 +8313,11 @@
         <v>0</v>
       </c>
       <c r="J62" s="4" t="inlineStr"/>
-      <c r="K62" s="4" t="inlineStr"/>
+      <c r="K62" s="4" t="inlineStr">
+        <is>
+          <t>No documented daily Sentry review cadence; precondition (Sentry itself) also absent.</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="42" customHeight="1">
       <c r="A63" s="4" t="inlineStr">
@@ -8196,7 +8360,11 @@
         <v>0</v>
       </c>
       <c r="J63" s="4" t="inlineStr"/>
-      <c r="K63" s="4" t="inlineStr"/>
+      <c r="K63" s="4" t="inlineStr">
+        <is>
+          <t>vite.config.ts sets no sourcemap option (defaults false); no @sentry/vite-plugin; .github/workflows/ does not exist; build script invokes plain vite build with no source-map upload.</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="42" customHeight="1">
       <c r="A64" s="4" t="inlineStr">
@@ -8230,7 +8398,7 @@
         </is>
       </c>
       <c r="G64" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H64" s="4" t="n">
         <v>3</v>
@@ -8239,7 +8407,11 @@
         <v>0</v>
       </c>
       <c r="J64" s="4" t="inlineStr"/>
-      <c r="K64" s="4" t="inlineStr"/>
+      <c r="K64" s="4" t="inlineStr">
+        <is>
+          <t>Resend SDK pattern exists in send-framework-email (different feature). save-beta-tester explicitly disables email ('Resend integration not yet configured'). No invitation template (.html/.tsx/.md), no 'first 10'/'7-day'/'30-min debrief' language anywhere.</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="42" customHeight="1">
       <c r="A65" s="4" t="inlineStr">
@@ -8273,7 +8445,7 @@
         </is>
       </c>
       <c r="G65" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H65" s="4" t="n">
         <v>3</v>
@@ -8284,7 +8456,7 @@
       <c r="J65" s="4" t="inlineStr"/>
       <c r="K65" s="4" t="inlineStr">
         <is>
-          <t>Matthew records the Loom.</t>
+          <t>StartHere.tsx has a Vimeo (not Loom) intro video. No one-page written guide. Docs flag training content as missing (BRIEF_ANALYSIS_COMPREHENSIVE.md:288 'No training pages exist'). Not linked from any invitation.</t>
         </is>
       </c>
     </row>
@@ -8316,11 +8488,11 @@
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>not_started</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="G66" s="7" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H66" s="4" t="n">
         <v>2</v>
@@ -8329,7 +8501,11 @@
         <v>0</v>
       </c>
       <c r="J66" s="4" t="inlineStr"/>
-      <c r="K66" s="4" t="inlineStr"/>
+      <c r="K66" s="4" t="inlineStr">
+        <is>
+          <t>BetaWelcome page exists at /beta with 'Beta Testing Program' framing + registration form, but does NOT auto-show on first login, does NOT name Trevor or the framework, is NOT dismissable, gated by localStorage not auth.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -10225,7 +10401,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10329,6 +10505,28 @@
         </is>
       </c>
     </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Matthew (via Claude Code)</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Full sub-feature audit against the codebase (6 parallel agents)</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Audited all 64 sub-features against actual code on main. Major findings: (a) F-008 dropped 80→39% — the strategy doc ships but the Forensic *tier* concept and Trigger Moment callout don't exist in code; (b) F-002.2 + F-012.2 reduced from 100% — quality badges use value heuristics, not extractor confidence; (c) F-009 dropped 30→19% — only ONE AI mode is independently invocable, not four; (d) F-011.1 reduced from 100→70% — code uses field_source + separate is_locked, not a manuallyEdited boolean; (e) all of F-013/F-014/F-015/F-016 confirmed 0 — no three-moment infra exists; existing BetaFeedback is a separate older system that won't compose; (f) F-017 confirmed 0 — no Sentry installed. Per-sub-feature notes updated with file:line evidence; parent features rolled up to averages.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>

--- a/docs/feature_status_tracker.xlsx
+++ b/docs/feature_status_tracker.xlsx
@@ -615,27 +615,27 @@
         </is>
       </c>
       <c r="B5" s="4">
-        <f>COUNTIF('Features'!$E$3:$E$61,"Alpha")</f>
+        <f>COUNTIF('Features'!$E$3:$E$72,"Alpha")</f>
         <v/>
       </c>
       <c r="C5" s="4">
-        <f>COUNTIFS('Features'!$E$3:$E$61,"Alpha",'Features'!$G$3:$G$61,"complete")</f>
+        <f>COUNTIFS('Features'!$E$3:$E$72,"Alpha",'Features'!$G$3:$G$72,"complete")</f>
         <v/>
       </c>
       <c r="D5" s="4">
-        <f>COUNTIFS('Features'!$E$3:$E$61,"Alpha",'Features'!$G$3:$G$61,"in_progress")+COUNTIFS('Features'!$E$3:$E$61,"Alpha",'Features'!$G$3:$G$61,"in_review")</f>
+        <f>COUNTIFS('Features'!$E$3:$E$72,"Alpha",'Features'!$G$3:$G$72,"in_progress")+COUNTIFS('Features'!$E$3:$E$72,"Alpha",'Features'!$G$3:$G$72,"in_review")</f>
         <v/>
       </c>
       <c r="E5" s="4">
-        <f>COUNTIFS('Features'!$E$3:$E$61,"Alpha",'Features'!$G$3:$G$61,"blocked")</f>
+        <f>COUNTIFS('Features'!$E$3:$E$72,"Alpha",'Features'!$G$3:$G$72,"blocked")</f>
         <v/>
       </c>
       <c r="F5" s="4">
-        <f>COUNTIFS('Features'!$E$3:$E$61,"Alpha",'Features'!$G$3:$G$61,"not_started")</f>
+        <f>COUNTIFS('Features'!$E$3:$E$72,"Alpha",'Features'!$G$3:$G$72,"not_started")</f>
         <v/>
       </c>
       <c r="G5" s="5">
-        <f>IFERROR(ROUND(SUMIFS('Features'!$H$3:$H$61,'Features'!$E$3:$E$61,"Alpha")/(B5*100),3),0)</f>
+        <f>IFERROR(ROUND(SUMIFS('Features'!$H$3:$H$72,'Features'!$E$3:$E$72,"Alpha")/(B5*100),3),0)</f>
         <v/>
       </c>
       <c r="H5" s="4">
@@ -650,27 +650,27 @@
         </is>
       </c>
       <c r="B6" s="4">
-        <f>COUNTIF('Features'!$E$3:$E$61,"Beta")</f>
+        <f>COUNTIF('Features'!$E$3:$E$72,"Beta")</f>
         <v/>
       </c>
       <c r="C6" s="4">
-        <f>COUNTIFS('Features'!$E$3:$E$61,"Beta",'Features'!$G$3:$G$61,"complete")</f>
+        <f>COUNTIFS('Features'!$E$3:$E$72,"Beta",'Features'!$G$3:$G$72,"complete")</f>
         <v/>
       </c>
       <c r="D6" s="4">
-        <f>COUNTIFS('Features'!$E$3:$E$61,"Beta",'Features'!$G$3:$G$61,"in_progress")+COUNTIFS('Features'!$E$3:$E$61,"Beta",'Features'!$G$3:$G$61,"in_review")</f>
+        <f>COUNTIFS('Features'!$E$3:$E$72,"Beta",'Features'!$G$3:$G$72,"in_progress")+COUNTIFS('Features'!$E$3:$E$72,"Beta",'Features'!$G$3:$G$72,"in_review")</f>
         <v/>
       </c>
       <c r="E6" s="4">
-        <f>COUNTIFS('Features'!$E$3:$E$61,"Beta",'Features'!$G$3:$G$61,"blocked")</f>
+        <f>COUNTIFS('Features'!$E$3:$E$72,"Beta",'Features'!$G$3:$G$72,"blocked")</f>
         <v/>
       </c>
       <c r="F6" s="4">
-        <f>COUNTIFS('Features'!$E$3:$E$61,"Beta",'Features'!$G$3:$G$61,"not_started")</f>
+        <f>COUNTIFS('Features'!$E$3:$E$72,"Beta",'Features'!$G$3:$G$72,"not_started")</f>
         <v/>
       </c>
       <c r="G6" s="5">
-        <f>IFERROR(ROUND(SUMIFS('Features'!$H$3:$H$61,'Features'!$E$3:$E$61,"Beta")/(B6*100),3),0)</f>
+        <f>IFERROR(ROUND(SUMIFS('Features'!$H$3:$H$72,'Features'!$E$3:$E$72,"Beta")/(B6*100),3),0)</f>
         <v/>
       </c>
       <c r="H6" s="4">
@@ -685,27 +685,27 @@
         </is>
       </c>
       <c r="B7" s="4">
-        <f>COUNTIF('Features'!$E$3:$E$61,"GA")</f>
+        <f>COUNTIF('Features'!$E$3:$E$72,"GA")</f>
         <v/>
       </c>
       <c r="C7" s="4">
-        <f>COUNTIFS('Features'!$E$3:$E$61,"GA",'Features'!$G$3:$G$61,"complete")</f>
+        <f>COUNTIFS('Features'!$E$3:$E$72,"GA",'Features'!$G$3:$G$72,"complete")</f>
         <v/>
       </c>
       <c r="D7" s="4">
-        <f>COUNTIFS('Features'!$E$3:$E$61,"GA",'Features'!$G$3:$G$61,"in_progress")+COUNTIFS('Features'!$E$3:$E$61,"GA",'Features'!$G$3:$G$61,"in_review")</f>
+        <f>COUNTIFS('Features'!$E$3:$E$72,"GA",'Features'!$G$3:$G$72,"in_progress")+COUNTIFS('Features'!$E$3:$E$72,"GA",'Features'!$G$3:$G$72,"in_review")</f>
         <v/>
       </c>
       <c r="E7" s="4">
-        <f>COUNTIFS('Features'!$E$3:$E$61,"GA",'Features'!$G$3:$G$61,"blocked")</f>
+        <f>COUNTIFS('Features'!$E$3:$E$72,"GA",'Features'!$G$3:$G$72,"blocked")</f>
         <v/>
       </c>
       <c r="F7" s="4">
-        <f>COUNTIFS('Features'!$E$3:$E$61,"GA",'Features'!$G$3:$G$61,"not_started")</f>
+        <f>COUNTIFS('Features'!$E$3:$E$72,"GA",'Features'!$G$3:$G$72,"not_started")</f>
         <v/>
       </c>
       <c r="G7" s="5">
-        <f>IFERROR(ROUND(SUMIFS('Features'!$H$3:$H$61,'Features'!$E$3:$E$61,"GA")/(B7*100),3),0)</f>
+        <f>IFERROR(ROUND(SUMIFS('Features'!$H$3:$H$72,'Features'!$E$3:$E$72,"GA")/(B7*100),3),0)</f>
         <v/>
       </c>
       <c r="H7" s="4">
@@ -720,27 +720,27 @@
         </is>
       </c>
       <c r="B8" s="4">
-        <f>COUNTIF('Features'!$E$3:$E$61,"Post-GA")</f>
+        <f>COUNTIF('Features'!$E$3:$E$72,"Post-GA")</f>
         <v/>
       </c>
       <c r="C8" s="4">
-        <f>COUNTIFS('Features'!$E$3:$E$61,"Post-GA",'Features'!$G$3:$G$61,"complete")</f>
+        <f>COUNTIFS('Features'!$E$3:$E$72,"Post-GA",'Features'!$G$3:$G$72,"complete")</f>
         <v/>
       </c>
       <c r="D8" s="4">
-        <f>COUNTIFS('Features'!$E$3:$E$61,"Post-GA",'Features'!$G$3:$G$61,"in_progress")+COUNTIFS('Features'!$E$3:$E$61,"Post-GA",'Features'!$G$3:$G$61,"in_review")</f>
+        <f>COUNTIFS('Features'!$E$3:$E$72,"Post-GA",'Features'!$G$3:$G$72,"in_progress")+COUNTIFS('Features'!$E$3:$E$72,"Post-GA",'Features'!$G$3:$G$72,"in_review")</f>
         <v/>
       </c>
       <c r="E8" s="4">
-        <f>COUNTIFS('Features'!$E$3:$E$61,"Post-GA",'Features'!$G$3:$G$61,"blocked")</f>
+        <f>COUNTIFS('Features'!$E$3:$E$72,"Post-GA",'Features'!$G$3:$G$72,"blocked")</f>
         <v/>
       </c>
       <c r="F8" s="4">
-        <f>COUNTIFS('Features'!$E$3:$E$61,"Post-GA",'Features'!$G$3:$G$61,"not_started")</f>
+        <f>COUNTIFS('Features'!$E$3:$E$72,"Post-GA",'Features'!$G$3:$G$72,"not_started")</f>
         <v/>
       </c>
       <c r="G8" s="5">
-        <f>IFERROR(ROUND(SUMIFS('Features'!$H$3:$H$61,'Features'!$E$3:$E$61,"Post-GA")/(B8*100),3),0)</f>
+        <f>IFERROR(ROUND(SUMIFS('Features'!$H$3:$H$72,'Features'!$E$3:$E$72,"Post-GA")/(B8*100),3),0)</f>
         <v/>
       </c>
       <c r="H8" s="4">
@@ -757,19 +757,19 @@
     </row>
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="4">
-        <f>IFERROR(INDEX('Features'!A3:A61,MATCH("blocked",'Features'!$G$3:$G$61,0)),"None")</f>
+        <f>IFERROR(INDEX('Features'!A3:A72,MATCH("blocked",'Features'!$G$3:$G$72,0)),"None")</f>
         <v/>
       </c>
       <c r="B11" s="4">
-        <f>IFERROR(INDEX('Features'!B3:B61,MATCH("blocked",'Features'!$G$3:$G$61,0)),"None")</f>
+        <f>IFERROR(INDEX('Features'!B3:B72,MATCH("blocked",'Features'!$G$3:$G$72,0)),"None")</f>
         <v/>
       </c>
       <c r="C11" s="4">
-        <f>IFERROR(INDEX('Features'!E3:E61,MATCH("blocked",'Features'!$G$3:$G$61,0)),"")</f>
+        <f>IFERROR(INDEX('Features'!E3:E72,MATCH("blocked",'Features'!$G$3:$G$72,0)),"")</f>
         <v/>
       </c>
       <c r="D11" s="4">
-        <f>IFERROR(INDEX('Features'!I3:I61,MATCH("blocked",'Features'!$G$3:$G$61,0)),"")</f>
+        <f>IFERROR(INDEX('Features'!I3:I72,MATCH("blocked",'Features'!$G$3:$G$72,0)),"")</f>
         <v/>
       </c>
     </row>
@@ -801,7 +801,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -899,23 +899,23 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>F-004,F-005,F-006,F-007,F-008,F-009,F-012,F-022</t>
+          <t>F-004,F-005,F-006,F-007,F-008,F-009,F-012,F-022,F-058,F-060</t>
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G5" s="4">
-        <f>(COUNTIFS('Features'!$A$3:$A$61,"F-004",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-004",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-005",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-005",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-009",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-009",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-012",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-012",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"in_review"))</f>
+        <f>(COUNTIFS('Features'!$A$3:$A$72,"F-004",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-004",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-005",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-005",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-006",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-006",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-007",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-007",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-008",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-008",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-009",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-009",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-012",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-012",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-022",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-022",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-058",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-058",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-060",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-060",'Features'!$G$3:$G$72,"in_review"))</f>
         <v/>
       </c>
       <c r="H5" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-004",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-005",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-009",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-012",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-004",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-004",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-005",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-005",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-009",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-009",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-012",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-012",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"in_review"))=8,"MET",IF((COUNTIFS('Features'!$A$3:$A$61,"F-004",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-004",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-005",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-005",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-009",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-009",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-012",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-012",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"in_review"))=0,"OPEN — 0 of 8","PARTIAL — "&amp;(COUNTIFS('Features'!$A$3:$A$61,"F-004",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-004",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-005",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-005",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-009",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-009",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-012",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-012",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"in_review"))&amp;" of 8")))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$72,"F-004",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-005",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-006",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-007",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-008",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-009",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-012",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-022",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-058",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-060",'Features'!$G$3:$G$72,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$72,"F-004",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-004",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-005",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-005",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-006",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-006",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-007",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-007",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-008",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-008",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-009",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-009",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-012",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-012",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-022",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-022",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-058",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-058",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-060",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-060",'Features'!$G$3:$G$72,"in_review"))=10,"MET",IF((COUNTIFS('Features'!$A$3:$A$72,"F-004",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-004",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-005",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-005",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-006",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-006",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-007",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-007",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-008",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-008",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-009",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-009",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-012",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-012",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-022",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-022",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-058",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-058",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-060",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-060",'Features'!$G$3:$G$72,"in_review"))=0,"OPEN — 0 of 10","PARTIAL — "&amp;(COUNTIFS('Features'!$A$3:$A$72,"F-004",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-004",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-005",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-005",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-006",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-006",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-007",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-007",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-008",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-008",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-009",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-009",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-012",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-012",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-022",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-022",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-058",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-058",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-060",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-060",'Features'!$G$3:$G$72,"in_review"))&amp;" of 10")))</f>
         <v/>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>Core Alpha thesis: Avatar Builder + Forensic Canvas produce a depth of customer understanding generic prompting can't reach. F-022 (Coach mode) extends this in Beta.</t>
+          <t>Core Alpha thesis: Avatar Builder + Forensic Canvas produce a depth of customer understanding generic prompting can't reach. F-022 (Coach mode) extends this in Beta. GEN3 (2026-05-25): = cannot articulate what the customer is actually buying → The Signature (F-060) is the answer; the Decision Trigger (F-058) sharpens it. MVP-critical, validate first. Free tier.</t>
         </is>
       </c>
     </row>
@@ -942,18 +942,18 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>F-001,F-004,F-005,F-006,F-007,F-009</t>
+          <t>F-001,F-004,F-005,F-006,F-007,F-009,F-060,F-061,F-062</t>
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G6" s="4">
-        <f>(COUNTIFS('Features'!$A$3:$A$61,"F-001",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-001",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-004",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-004",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-005",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-005",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-009",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-009",'Features'!$G$3:$G$61,"in_review"))</f>
+        <f>(COUNTIFS('Features'!$A$3:$A$72,"F-001",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-001",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-004",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-004",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-005",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-005",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-006",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-006",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-007",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-007",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-009",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-009",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-060",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-060",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-061",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-061",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-062",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-062",'Features'!$G$3:$G$72,"in_review"))</f>
         <v/>
       </c>
       <c r="H6" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-001",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-004",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-005",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-009",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-001",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-001",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-004",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-004",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-005",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-005",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-009",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-009",'Features'!$G$3:$G$61,"in_review"))=6,"MET",IF((COUNTIFS('Features'!$A$3:$A$61,"F-001",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-001",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-004",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-004",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-005",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-005",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-009",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-009",'Features'!$G$3:$G$61,"in_review"))=0,"OPEN — 0 of 6","PARTIAL — "&amp;(COUNTIFS('Features'!$A$3:$A$61,"F-001",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-001",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-004",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-004",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-005",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-005",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-009",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-009",'Features'!$G$3:$G$61,"in_review"))&amp;" of 6")))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$72,"F-001",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-004",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-005",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-006",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-007",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-009",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-060",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-061",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-062",'Features'!$G$3:$G$72,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$72,"F-001",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-001",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-004",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-004",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-005",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-005",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-006",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-006",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-007",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-007",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-009",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-009",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-060",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-060",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-061",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-061",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-062",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-062",'Features'!$G$3:$G$72,"in_review"))=9,"MET",IF((COUNTIFS('Features'!$A$3:$A$72,"F-001",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-001",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-004",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-004",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-005",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-005",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-006",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-006",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-007",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-007",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-009",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-009",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-060",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-060",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-061",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-061",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-062",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-062",'Features'!$G$3:$G$72,"in_review"))=0,"OPEN — 0 of 9","PARTIAL — "&amp;(COUNTIFS('Features'!$A$3:$A$72,"F-001",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-001",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-004",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-004",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-005",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-005",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-006",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-006",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-007",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-007",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-009",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-009",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-060",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-060",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-061",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-061",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-062",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-062",'Features'!$G$3:$G$72,"in_review"))&amp;" of 9")))</f>
         <v/>
       </c>
       <c r="I6" s="4" t="inlineStr">
@@ -992,11 +992,11 @@
         <v>4</v>
       </c>
       <c r="G7" s="4">
-        <f>(COUNTIFS('Features'!$A$3:$A$61,"F-003",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-003",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-023",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-023",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-053",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-053",'Features'!$G$3:$G$61,"in_review"))</f>
+        <f>(COUNTIFS('Features'!$A$3:$A$72,"F-003",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-003",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-008",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-008",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-023",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-023",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-053",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-053",'Features'!$G$3:$G$72,"in_review"))</f>
         <v/>
       </c>
       <c r="H7" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-003",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-023",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-053",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-003",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-003",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-023",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-023",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-053",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-053",'Features'!$G$3:$G$61,"in_review"))=4,"MET",IF((COUNTIFS('Features'!$A$3:$A$61,"F-003",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-003",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-023",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-023",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-053",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-053",'Features'!$G$3:$G$61,"in_review"))=0,"OPEN — 0 of 4","PARTIAL — "&amp;(COUNTIFS('Features'!$A$3:$A$61,"F-003",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-003",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-023",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-023",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-053",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-053",'Features'!$G$3:$G$61,"in_review"))&amp;" of 4")))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$72,"F-003",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-008",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-023",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-053",'Features'!$G$3:$G$72,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$72,"F-003",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-003",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-008",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-008",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-023",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-023",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-053",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-053",'Features'!$G$3:$G$72,"in_review"))=4,"MET",IF((COUNTIFS('Features'!$A$3:$A$72,"F-003",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-003",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-008",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-008",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-023",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-023",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-053",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-053",'Features'!$G$3:$G$72,"in_review"))=0,"OPEN — 0 of 4","PARTIAL — "&amp;(COUNTIFS('Features'!$A$3:$A$72,"F-003",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-003",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-008",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-008",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-023",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-023",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-053",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-053",'Features'!$G$3:$G$72,"in_review"))&amp;" of 4")))</f>
         <v/>
       </c>
       <c r="I7" s="4" t="inlineStr">
@@ -1035,11 +1035,11 @@
         <v>4</v>
       </c>
       <c r="G8" s="4">
-        <f>(COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-020",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-020",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-021",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-021",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-055",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-055",'Features'!$G$3:$G$61,"in_review"))</f>
+        <f>(COUNTIFS('Features'!$A$3:$A$72,"F-008",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-008",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-020",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-020",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-021",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-021",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-055",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-055",'Features'!$G$3:$G$72,"in_review"))</f>
         <v/>
       </c>
       <c r="H8" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-020",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-021",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-055",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-020",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-020",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-021",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-021",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-055",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-055",'Features'!$G$3:$G$61,"in_review"))=4,"MET",IF((COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-020",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-020",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-021",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-021",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-055",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-055",'Features'!$G$3:$G$61,"in_review"))=0,"OPEN — 0 of 4","PARTIAL — "&amp;(COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-020",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-020",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-021",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-021",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-055",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-055",'Features'!$G$3:$G$61,"in_review"))&amp;" of 4")))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$72,"F-008",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-020",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-021",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-055",'Features'!$G$3:$G$72,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$72,"F-008",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-008",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-020",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-020",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-021",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-021",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-055",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-055",'Features'!$G$3:$G$72,"in_review"))=4,"MET",IF((COUNTIFS('Features'!$A$3:$A$72,"F-008",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-008",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-020",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-020",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-021",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-021",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-055",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-055",'Features'!$G$3:$G$72,"in_review"))=0,"OPEN — 0 of 4","PARTIAL — "&amp;(COUNTIFS('Features'!$A$3:$A$72,"F-008",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-008",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-020",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-020",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-021",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-021",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-055",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-055",'Features'!$G$3:$G$72,"in_review"))&amp;" of 4")))</f>
         <v/>
       </c>
       <c r="I8" s="4" t="inlineStr">
@@ -1071,18 +1071,18 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>F-007,F-008,F-020,F-021</t>
+          <t>F-007,F-008,F-020,F-021,F-063</t>
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G9" s="4">
-        <f>(COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-020",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-020",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-021",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-021",'Features'!$G$3:$G$61,"in_review"))</f>
+        <f>(COUNTIFS('Features'!$A$3:$A$72,"F-007",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-007",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-008",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-008",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-020",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-020",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-021",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-021",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-063",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-063",'Features'!$G$3:$G$72,"in_review"))</f>
         <v/>
       </c>
       <c r="H9" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-020",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-021",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-020",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-020",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-021",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-021",'Features'!$G$3:$G$61,"in_review"))=4,"MET",IF((COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-020",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-020",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-021",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-021",'Features'!$G$3:$G$61,"in_review"))=0,"OPEN — 0 of 4","PARTIAL — "&amp;(COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-020",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-020",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-021",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-021",'Features'!$G$3:$G$61,"in_review"))&amp;" of 4")))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$72,"F-007",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-008",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-020",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-021",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-063",'Features'!$G$3:$G$72,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$72,"F-007",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-007",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-008",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-008",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-020",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-020",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-021",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-021",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-063",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-063",'Features'!$G$3:$G$72,"in_review"))=5,"MET",IF((COUNTIFS('Features'!$A$3:$A$72,"F-007",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-007",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-008",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-008",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-020",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-020",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-021",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-021",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-063",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-063",'Features'!$G$3:$G$72,"in_review"))=0,"OPEN — 0 of 5","PARTIAL — "&amp;(COUNTIFS('Features'!$A$3:$A$72,"F-007",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-007",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-008",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-008",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-020",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-020",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-021",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-021",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-063",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-063",'Features'!$G$3:$G$72,"in_review"))&amp;" of 5")))</f>
         <v/>
       </c>
       <c r="I9" s="4" t="inlineStr">
@@ -1121,11 +1121,11 @@
         <v>4</v>
       </c>
       <c r="G10" s="4">
-        <f>(COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-054",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-054",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-055",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-055",'Features'!$G$3:$G$61,"in_review"))</f>
+        <f>(COUNTIFS('Features'!$A$3:$A$72,"F-006",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-006",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-007",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-007",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-054",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-054",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-055",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-055",'Features'!$G$3:$G$72,"in_review"))</f>
         <v/>
       </c>
       <c r="H10" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-054",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-055",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-054",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-054",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-055",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-055",'Features'!$G$3:$G$61,"in_review"))=4,"MET",IF((COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-054",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-054",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-055",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-055",'Features'!$G$3:$G$61,"in_review"))=0,"OPEN — 0 of 4","PARTIAL — "&amp;(COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-054",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-054",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-055",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-055",'Features'!$G$3:$G$61,"in_review"))&amp;" of 4")))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$72,"F-006",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-007",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-054",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-055",'Features'!$G$3:$G$72,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$72,"F-006",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-006",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-007",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-007",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-054",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-054",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-055",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-055",'Features'!$G$3:$G$72,"in_review"))=4,"MET",IF((COUNTIFS('Features'!$A$3:$A$72,"F-006",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-006",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-007",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-007",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-054",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-054",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-055",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-055",'Features'!$G$3:$G$72,"in_review"))=0,"OPEN — 0 of 4","PARTIAL — "&amp;(COUNTIFS('Features'!$A$3:$A$72,"F-006",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-006",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-007",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-007",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-054",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-054",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-055",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-055",'Features'!$G$3:$G$72,"in_review"))&amp;" of 4")))</f>
         <v/>
       </c>
       <c r="I10" s="4" t="inlineStr">
@@ -1164,11 +1164,11 @@
         <v>3</v>
       </c>
       <c r="G11" s="4">
-        <f>(COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-031",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-031",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-049",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-049",'Features'!$G$3:$G$61,"in_review"))</f>
+        <f>(COUNTIFS('Features'!$A$3:$A$72,"F-022",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-022",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-031",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-031",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-049",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-049",'Features'!$G$3:$G$72,"in_review"))</f>
         <v/>
       </c>
       <c r="H11" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-031",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-049",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-031",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-031",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-049",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-049",'Features'!$G$3:$G$61,"in_review"))=3,"MET",IF((COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-031",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-031",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-049",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-049",'Features'!$G$3:$G$61,"in_review"))=0,"OPEN — 0 of 3","PARTIAL — "&amp;(COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-031",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-031",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-049",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-049",'Features'!$G$3:$G$61,"in_review"))&amp;" of 3")))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$72,"F-022",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-031",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-049",'Features'!$G$3:$G$72,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$72,"F-022",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-022",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-031",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-031",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-049",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-049",'Features'!$G$3:$G$72,"in_review"))=3,"MET",IF((COUNTIFS('Features'!$A$3:$A$72,"F-022",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-022",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-031",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-031",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-049",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-049",'Features'!$G$3:$G$72,"in_review"))=0,"OPEN — 0 of 3","PARTIAL — "&amp;(COUNTIFS('Features'!$A$3:$A$72,"F-022",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-022",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-031",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-031",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-049",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-049",'Features'!$G$3:$G$72,"in_review"))&amp;" of 3")))</f>
         <v/>
       </c>
       <c r="I11" s="4" t="inlineStr">
@@ -1207,11 +1207,11 @@
         <v>3</v>
       </c>
       <c r="G12" s="4">
-        <f>(COUNTIFS('Features'!$A$3:$A$61,"F-042",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-042",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-053",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-053",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-055",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-055",'Features'!$G$3:$G$61,"in_review"))</f>
+        <f>(COUNTIFS('Features'!$A$3:$A$72,"F-042",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-042",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-053",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-053",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-055",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-055",'Features'!$G$3:$G$72,"in_review"))</f>
         <v/>
       </c>
       <c r="H12" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-042",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-053",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-055",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-042",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-042",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-053",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-053",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-055",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-055",'Features'!$G$3:$G$61,"in_review"))=3,"MET",IF((COUNTIFS('Features'!$A$3:$A$61,"F-042",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-042",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-053",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-053",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-055",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-055",'Features'!$G$3:$G$61,"in_review"))=0,"OPEN — 0 of 3","PARTIAL — "&amp;(COUNTIFS('Features'!$A$3:$A$61,"F-042",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-042",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-053",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-053",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-055",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-055",'Features'!$G$3:$G$61,"in_review"))&amp;" of 3")))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$72,"F-042",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-053",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-055",'Features'!$G$3:$G$72,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$72,"F-042",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-042",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-053",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-053",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-055",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-055",'Features'!$G$3:$G$72,"in_review"))=3,"MET",IF((COUNTIFS('Features'!$A$3:$A$72,"F-042",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-042",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-053",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-053",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-055",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-055",'Features'!$G$3:$G$72,"in_review"))=0,"OPEN — 0 of 3","PARTIAL — "&amp;(COUNTIFS('Features'!$A$3:$A$72,"F-042",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-042",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-053",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-053",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-055",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-055",'Features'!$G$3:$G$72,"in_review"))&amp;" of 3")))</f>
         <v/>
       </c>
       <c r="I12" s="4" t="inlineStr">
@@ -1250,11 +1250,11 @@
         <v>5</v>
       </c>
       <c r="G13" s="4">
-        <f>(COUNTIFS('Features'!$A$3:$A$61,"F-028",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-028",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-029",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-029",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-030",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-030",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-043",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-043",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-054",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-054",'Features'!$G$3:$G$61,"in_review"))</f>
+        <f>(COUNTIFS('Features'!$A$3:$A$72,"F-028",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-028",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-029",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-029",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-030",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-030",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-043",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-043",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-054",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-054",'Features'!$G$3:$G$72,"in_review"))</f>
         <v/>
       </c>
       <c r="H13" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-028",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-029",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-030",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-043",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-054",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-028",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-028",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-029",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-029",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-030",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-030",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-043",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-043",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-054",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-054",'Features'!$G$3:$G$61,"in_review"))=5,"MET",IF((COUNTIFS('Features'!$A$3:$A$61,"F-028",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-028",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-029",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-029",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-030",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-030",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-043",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-043",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-054",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-054",'Features'!$G$3:$G$61,"in_review"))=0,"OPEN — 0 of 5","PARTIAL — "&amp;(COUNTIFS('Features'!$A$3:$A$61,"F-028",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-028",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-029",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-029",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-030",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-030",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-043",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-043",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-054",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-054",'Features'!$G$3:$G$61,"in_review"))&amp;" of 5")))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$72,"F-028",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-029",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-030",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-043",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-054",'Features'!$G$3:$G$72,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$72,"F-028",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-028",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-029",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-029",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-030",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-030",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-043",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-043",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-054",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-054",'Features'!$G$3:$G$72,"in_review"))=5,"MET",IF((COUNTIFS('Features'!$A$3:$A$72,"F-028",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-028",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-029",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-029",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-030",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-030",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-043",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-043",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-054",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-054",'Features'!$G$3:$G$72,"in_review"))=0,"OPEN — 0 of 5","PARTIAL — "&amp;(COUNTIFS('Features'!$A$3:$A$72,"F-028",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-028",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-029",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-029",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-030",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-030",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-043",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-043",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-054",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-054",'Features'!$G$3:$G$72,"in_review"))&amp;" of 5")))</f>
         <v/>
       </c>
       <c r="I13" s="4" t="inlineStr">
@@ -1293,16 +1293,102 @@
         <v>4</v>
       </c>
       <c r="G14" s="4">
-        <f>(COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-038",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-038",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-053",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-053",'Features'!$G$3:$G$61,"in_review"))</f>
+        <f>(COUNTIFS('Features'!$A$3:$A$72,"F-008",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-008",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-022",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-022",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-038",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-038",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-053",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-053",'Features'!$G$3:$G$72,"in_review"))</f>
         <v/>
       </c>
       <c r="H14" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-038",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-053",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-038",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-038",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-053",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-053",'Features'!$G$3:$G$61,"in_review"))=4,"MET",IF((COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-038",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-038",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-053",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-053",'Features'!$G$3:$G$61,"in_review"))=0,"OPEN — 0 of 4","PARTIAL — "&amp;(COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-038",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-038",'Features'!$G$3:$G$61,"in_review")+COUNTIFS('Features'!$A$3:$A$61,"F-053",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-053",'Features'!$G$3:$G$61,"in_review"))&amp;" of 4")))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$72,"F-008",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-022",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-038",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-053",'Features'!$G$3:$G$72,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$72,"F-008",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-008",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-022",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-022",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-038",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-038",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-053",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-053",'Features'!$G$3:$G$72,"in_review"))=4,"MET",IF((COUNTIFS('Features'!$A$3:$A$72,"F-008",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-008",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-022",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-022",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-038",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-038",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-053",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-053",'Features'!$G$3:$G$72,"in_review"))=0,"OPEN — 0 of 4","PARTIAL — "&amp;(COUNTIFS('Features'!$A$3:$A$72,"F-008",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-008",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-022",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-022",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-038",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-038",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-053",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-053",'Features'!$G$3:$G$72,"in_review"))&amp;" of 4")))</f>
         <v/>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
           <t>Forensic Canvas as North Star (F-008), Coach for ongoing decisions (F-022), performance metrics (F-038) close the loop. F-053 lets decisions live at the angle level.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="48" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>P-011</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>I don't know where my brand is failing.</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>F-057,F-059,F-027</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" s="4">
+        <f>(COUNTIFS('Features'!$A$3:$A$72,"F-057",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-057",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-059",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-059",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-027",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-027",'Features'!$G$3:$G$72,"in_review"))</f>
+        <v/>
+      </c>
+      <c r="H15" s="4">
+        <f>IF((COUNTIFS('Features'!$A$3:$A$72,"F-057",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-059",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-027",'Features'!$G$3:$G$72,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$72,"F-057",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-057",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-059",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-059",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-027",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-027",'Features'!$G$3:$G$72,"in_review"))=3,"MET",IF((COUNTIFS('Features'!$A$3:$A$72,"F-057",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-057",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-059",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-059",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-027",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-027",'Features'!$G$3:$G$72,"in_review"))=0,"OPEN — 0 of 3","PARTIAL — "&amp;(COUNTIFS('Features'!$A$3:$A$72,"F-057",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-057",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-059",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-059",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-027",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-027",'Features'!$G$3:$G$72,"in_review"))&amp;" of 3")))</f>
+        <v/>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>GEN3 (2026-05-25): Trevor's problem #3/#9 — the Trust Gap™ Score (F-057) names the gap (insight / positioning / empathy / authenticity) and the bridge (F-059) turns it into momentum. MVP-critical: this is the hook, validate FIRST [Analysis 2026-05-17]. Free tier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="48" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>P-012</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Brand strategy expertise is inaccessible at my price point.</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>F-019,F-064</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" s="4">
+        <f>(COUNTIFS('Features'!$A$3:$A$72,"F-019",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-019",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-064",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-064",'Features'!$G$3:$G$72,"in_review"))</f>
+        <v/>
+      </c>
+      <c r="H16" s="4">
+        <f>IF((COUNTIFS('Features'!$A$3:$A$72,"F-019",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-064",'Features'!$G$3:$G$72,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$72,"F-019",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-019",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-064",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-064",'Features'!$G$3:$G$72,"in_review"))=2,"MET",IF((COUNTIFS('Features'!$A$3:$A$72,"F-019",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-019",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-064",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-064",'Features'!$G$3:$G$72,"in_review"))=0,"OPEN — 0 of 2","PARTIAL — "&amp;(COUNTIFS('Features'!$A$3:$A$72,"F-019",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-019",'Features'!$G$3:$G$72,"in_review")+COUNTIFS('Features'!$A$3:$A$72,"F-064",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-064",'Features'!$G$3:$G$72,"in_review"))&amp;" of 2")))</f>
+        <v/>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>GEN3 (2026-05-25): Trevor's problem #7 — a brand strategist costs £3k–£15k; the freemium app (F-019) delivers structured brand thinking at £29/mo, with locked-but-visible fields (F-064) enticing upgrade. Paid tier.</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1397,7 @@
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <conditionalFormatting sqref="H5:H14">
+  <conditionalFormatting sqref="H5:H16">
     <cfRule type="expression" priority="1" dxfId="2">
       <formula>H5="MET"</formula>
     </cfRule>
@@ -1325,7 +1411,7 @@
       <formula>ISNUMBER(SEARCH("OPEN",H5))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D5:D14">
+  <conditionalFormatting sqref="D5:D16">
     <cfRule type="cellIs" priority="5" operator="equal" dxfId="2">
       <formula>"Yes"</formula>
     </cfRule>
@@ -1337,10 +1423,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="C5:C64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Value must match one of the allowed options." type="list">
+    <dataValidation sqref="C5:C66" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Value must match one of the allowed options." type="list">
       <formula1>"Alpha,Beta,GA,Post-GA"</formula1>
     </dataValidation>
-    <dataValidation sqref="D5:D64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Value must match one of the allowed options." type="list">
+    <dataValidation sqref="D5:D66" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Value must match one of the allowed options." type="list">
       <formula1>"Yes,Partial,No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1354,7 +1440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P61"/>
+  <dimension ref="A1:P72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1531,7 +1617,7 @@
         </is>
       </c>
       <c r="P3" s="8" t="n">
-        <v>46158</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="4" ht="42" customHeight="1">
@@ -1597,7 +1683,7 @@
         </is>
       </c>
       <c r="P4" s="8" t="n">
-        <v>46158</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="5" ht="42" customHeight="1">
@@ -1667,7 +1753,7 @@
         </is>
       </c>
       <c r="P5" s="8" t="n">
-        <v>46158</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1">
@@ -1733,11 +1819,11 @@
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
-          <t>AUDIT 2026-05-16: V2 chapter UI delivers progressive disclosure + persistence well, but field schema flattens Gen 3 psychographic dimensions into coarse textareas (F-004.1 60%). 3 of 4 AI modes present; FieldChatButton missing from V2 (F-004.3 35%). Completion gate logic exists but button not mounted in render tree (F-004.5 55%).</t>
+          <t>AUDIT 2026-05-16: V2 chapter UI delivers progressive disclosure + persistence well, but field schema flattens Gen 3 psychographic dimensions into coarse textareas (F-004.1 60%). 3 of 4 AI modes present; FieldChatButton missing from V2 (F-004.3 35%). Completion gate logic exists but button not mounted in render tree (F-004.5 55%). RECONCILE (2026-05-25): maps into the new 5-stage conversational flow ending in The Signature (F-060); guided dialogue, not a 4-section form [F 144128256 @04:26]. 5-stage structure pending Trevor/Matthew sign-off.</t>
         </is>
       </c>
       <c r="P6" s="8" t="n">
-        <v>46158</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="7" ht="42" customHeight="1">
@@ -1803,11 +1889,11 @@
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>AUDIT 2026-05-16: V2 chapter map has no dedicated 'Buying Behaviour' chapter — closest is BUYER_INTENT which is conceptually different. V1 AvatarBuilder has the right tab. Data shape exists; UI split V1↔V2.</t>
+          <t>AUDIT 2026-05-16: V2 chapter map has no dedicated 'Buying Behaviour' chapter — closest is BUYER_INTENT which is conceptually different. V1 AvatarBuilder has the right tab. Data shape exists; UI split V1↔V2. RECONCILE (2026-05-25): maps into the new 5-stage conversational flow ending in The Signature (F-060); guided dialogue, not a 4-section form [F 144128256 @04:26]. 5-stage structure pending Trevor/Matthew sign-off.</t>
         </is>
       </c>
       <c r="P7" s="8" t="n">
-        <v>46158</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="8" ht="42" customHeight="1">
@@ -1828,7 +1914,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Section 3. Pre/during/post purchase emotional states; the Trigger Moment originates here.</t>
+          <t>Section 3. Pre/during/post purchase emotional states; The Decision Trigger™ originates here (captured standalone in F-058).</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -1873,11 +1959,11 @@
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>AUDIT 2026-05-16: Emotional fields exist (EMOTIONAL_CONNECTION + CUSTOMER_EXPERIENCE chapters) but Gen 3 Emotional Journey framing absent; Trigger Moment field with elevated visual treatment (F-006.2) is the most prominent miss — zero hits in codebase.</t>
+          <t>AUDIT 2026-05-16: Emotional fields exist (EMOTIONAL_CONNECTION + CUSTOMER_EXPERIENCE chapters) but Gen 3 Emotional Journey framing absent; Trigger Moment field with elevated visual treatment (F-006.2) is the most prominent miss — zero hits in codebase. RECONCILE (2026-05-25): maps into the new 5-stage conversational flow ending in The Signature (F-060); guided dialogue, not a 4-section form [F 144128256 @04:26]. 5-stage structure pending Trevor/Matthew sign-off.</t>
         </is>
       </c>
       <c r="P8" s="8" t="n">
-        <v>46158</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="9" ht="42" customHeight="1">
@@ -1943,11 +2029,11 @@
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>AUDIT 2026-05-16: Review intake is URL/ASIN-driven via ReviewAnalyzerModal (scrape model), not Gen 3 paste-raw-reviews model. voice-of-customer-analysis edge function DOES NOT EXIST. V1 analysis is fully mocked. Use/discard phrase cards (F-007.3) ~10%.</t>
+          <t>AUDIT 2026-05-16: Review intake is URL/ASIN-driven via ReviewAnalyzerModal (scrape model), not Gen 3 paste-raw-reviews model. voice-of-customer-analysis edge function DOES NOT EXIST. V1 analysis is fully mocked. Use/discard phrase cards (F-007.3) ~10%. RECONCILE (2026-05-25): maps into the new 5-stage conversational flow ending in The Signature (F-060); guided dialogue, not a 4-section form [F 144128256 @04:26]. 5-stage structure pending Trevor/Matthew sign-off.</t>
         </is>
       </c>
       <c r="P9" s="8" t="n">
-        <v>46158</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="10" ht="42" customHeight="1">
@@ -1968,7 +2054,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>28+ field canvas synthesised from Avatar Builder. Trigger Moment displayed as 'Strategic Entry Point'.</t>
+          <t>28+ field canvas synthesised from Avatar Builder, auto-populating from Avatar data partially in real time; strategy doc generable at any point (no forced step-gating). The Decision Trigger™ displayed prominently.</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -2013,11 +2099,11 @@
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>AUDIT 2026-05-16: 35-field schema exists (exceeds 28+) and Markdown export pipeline is mature, but Forensic *tier* differentiation does NOT exist — single unified synthesis path. Trigger Moment 'Strategic Entry Point' callout (F-008.3) and Draft↔Forensic toggle (F-008.4) both 0%. Rollup dropped from 80→39%: the doc ships, but the criteria asking for tier-specific behaviour are unmet.</t>
+          <t>AUDIT 2026-05-16: 35-field schema exists (exceeds 28+) and Markdown export pipeline is mature, but Forensic *tier* differentiation does NOT exist — single unified synthesis path. Trigger Moment 'Strategic Entry Point' callout (F-008.3) and Draft↔Forensic toggle (F-008.4) both 0%. Rollup dropped from 80→39%: the doc ships, but the criteria asking for tier-specific behaviour are unmet. GEN3 (2026-05-25): canvas auto-populates from Avatar data (partially real-time); no forced step-gating; 'Trigger Moment' renamed The Decision Trigger™ (also captured standalone in F-058) [F 144128256 @27:00,@31:00].</t>
         </is>
       </c>
       <c r="P10" s="8" t="n">
-        <v>46158</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="11" ht="42" customHeight="1">
@@ -2083,11 +2169,11 @@
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>AUDIT 2026-05-16: Only ONE AI mode is independently invocable — a single 'Generate with AI' button per field (AIButton.tsx). 'Think About This' and 'Real-World Examples' modes don't exist; 'Auto-Populate' is delivered implicitly via chat extraction + ghost text. No 4-mode selector UI. Rollup dropped from 30→19%.</t>
+          <t>AUDIT 2026-05-16: Only ONE AI mode is independently invocable — a single 'Generate with AI' button per field (AIButton.tsx). 'Think About This' and 'Real-World Examples' modes don't exist; 'Auto-Populate' is delivered implicitly via chat extraction + ghost text. No 4-mode selector UI. Rollup dropped from 30→19%. GEN3 (2026-05-25): MVP ships static example text for avatar/Before-State prompts; AI-suggestion path deferred and paid-tier when built [F 144128256 @11:42-12:52].</t>
         </is>
       </c>
       <c r="P11" s="8" t="n">
-        <v>46158</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="12" ht="42" customHeight="1">
@@ -2149,7 +2235,7 @@
         </is>
       </c>
       <c r="P12" s="8" t="n">
-        <v>46158</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="13" ht="42" customHeight="1">
@@ -2211,7 +2297,7 @@
         </is>
       </c>
       <c r="P13" s="8" t="n">
-        <v>46158</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="14" ht="42" customHeight="1">
@@ -2277,7 +2363,7 @@
         </is>
       </c>
       <c r="P14" s="8" t="n">
-        <v>46158</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="15" ht="42" customHeight="1">
@@ -2343,7 +2429,7 @@
         </is>
       </c>
       <c r="P15" s="8" t="n">
-        <v>46158</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="16" ht="42" customHeight="1">
@@ -2409,7 +2495,7 @@
         </is>
       </c>
       <c r="P16" s="8" t="n">
-        <v>46158</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="17" ht="42" customHeight="1">
@@ -2475,7 +2561,7 @@
         </is>
       </c>
       <c r="P17" s="8" t="n">
-        <v>46158</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="18" ht="42" customHeight="1">
@@ -2537,7 +2623,7 @@
         </is>
       </c>
       <c r="P18" s="8" t="n">
-        <v>46158</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="19" ht="42" customHeight="1">
@@ -2599,7 +2685,7 @@
         </is>
       </c>
       <c r="P19" s="8" t="n">
-        <v>46158</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="20" ht="42" customHeight="1">
@@ -2661,7 +2747,7 @@
         </is>
       </c>
       <c r="P20" s="8" t="n">
-        <v>46158</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="21" ht="42" customHeight="1">
@@ -2672,7 +2758,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Pay gate</t>
+          <t>Pay gate (freemium)</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -2682,7 +2768,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Stripe integration with two pricing options (£67 one-time, £29/mo) and post-payment action menu.</t>
+          <t>Freemium model. Free = core tools + The Signature + limited AI; paid (£29/mo; one-off £67 notional/TBD) unlocks AI-heavy features (Review Lab analysis, unlimited prompts/iterations). Stripe + post-payment action menu.</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -2714,7 +2800,11 @@
           <t>F-008</t>
         </is>
       </c>
-      <c r="L21" s="4" t="inlineStr"/>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>P-012</t>
+        </is>
+      </c>
       <c r="M21" s="4" t="n">
         <v>40</v>
       </c>
@@ -2723,11 +2813,11 @@
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>Central conversion test of beta. Pay-gate previews must use real canvas data.</t>
+          <t>Central conversion test of beta. Pay-gate previews must use real canvas data. GEN3 (2026-05-25): reframed from two pricing tiers to freemium; canvas fields locked-but-visible for non-subscribers (F-064) [F 144128256 @32:26-34:29].</t>
         </is>
       </c>
       <c r="P21" s="8" t="n">
-        <v>46158</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="22" ht="42" customHeight="1">
@@ -2797,7 +2887,7 @@
         </is>
       </c>
       <c r="P22" s="8" t="n">
-        <v>46158</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="23" ht="42" customHeight="1">
@@ -2863,7 +2953,7 @@
       </c>
       <c r="O23" s="4" t="inlineStr"/>
       <c r="P23" s="8" t="n">
-        <v>46158</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="24" ht="42" customHeight="1">
@@ -2929,11 +3019,11 @@
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>Required to deliver the £29/mo subscription value prop per Trevor's spec.</t>
+          <t>Required to deliver the £29/mo subscription value prop per Trevor's spec. GEN3 (2026-05-25): Coach auto-briefed on Diagnostic + Avatar data — no manual re-paste (fixes Gen-1 CX) [F 144128256 @34:29].</t>
         </is>
       </c>
       <c r="P24" s="8" t="n">
-        <v>46158</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="25" ht="42" customHeight="1">
@@ -3003,7 +3093,7 @@
         </is>
       </c>
       <c r="P25" s="8" t="n">
-        <v>46158</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="26" ht="42" customHeight="1">
@@ -3065,7 +3155,7 @@
         </is>
       </c>
       <c r="P26" s="8" t="n">
-        <v>46158</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="27" ht="42" customHeight="1">
@@ -3127,7 +3217,7 @@
         </is>
       </c>
       <c r="P27" s="8" t="n">
-        <v>46158</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="28" ht="42" customHeight="1">
@@ -3193,7 +3283,7 @@
         </is>
       </c>
       <c r="P28" s="8" t="n">
-        <v>46158</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="29" ht="42" customHeight="1">
@@ -3242,7 +3332,11 @@
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr"/>
-      <c r="L29" s="4" t="inlineStr"/>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>P-011</t>
+        </is>
+      </c>
       <c r="M29" s="4" t="n">
         <v>20</v>
       </c>
@@ -3251,11 +3345,11 @@
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>Diagnostic largely exists (FreeDiagnostic + BetaFeedback components). Handoff into Layer 1 still loose.</t>
+          <t>Diagnostic largely exists (FreeDiagnostic + BetaFeedback components). Handoff into Layer 1 still loose. GEN3 (2026-05-25): feeds the Trust Gap™ Score (F-057); beta signup capture writes to the same DB [F 140678453 @16:26].</t>
         </is>
       </c>
       <c r="P29" s="8" t="n">
-        <v>46158</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="30" ht="42" customHeight="1">
@@ -3329,7 +3423,7 @@
         </is>
       </c>
       <c r="P30" s="8" t="n">
-        <v>46158</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="31" ht="42" customHeight="1">
@@ -3403,7 +3497,7 @@
         </is>
       </c>
       <c r="P31" s="8" t="n">
-        <v>46158</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="32" ht="42" customHeight="1">
@@ -3477,7 +3571,7 @@
         </is>
       </c>
       <c r="P32" s="8" t="n">
-        <v>46158</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="33" ht="42" customHeight="1">
@@ -3547,7 +3641,7 @@
         </is>
       </c>
       <c r="P33" s="8" t="n">
-        <v>46158</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="34" ht="42" customHeight="1">
@@ -3613,7 +3707,7 @@
         </is>
       </c>
       <c r="P34" s="8" t="n">
-        <v>46158</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="35" ht="42" customHeight="1">
@@ -3675,7 +3769,7 @@
         </is>
       </c>
       <c r="P35" s="8" t="n">
-        <v>46158</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="36" ht="42" customHeight="1">
@@ -3741,7 +3835,7 @@
         </is>
       </c>
       <c r="P36" s="8" t="n">
-        <v>46158</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="37" ht="42" customHeight="1">
@@ -3803,7 +3897,7 @@
         </is>
       </c>
       <c r="P37" s="8" t="n">
-        <v>46158</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="38" ht="42" customHeight="1">
@@ -3869,7 +3963,7 @@
         </is>
       </c>
       <c r="P38" s="8" t="n">
-        <v>46158</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="39" ht="42" customHeight="1">
@@ -3931,7 +4025,7 @@
         </is>
       </c>
       <c r="P39" s="8" t="n">
-        <v>46158</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="40" ht="42" customHeight="1">
@@ -4001,7 +4095,7 @@
         </is>
       </c>
       <c r="P40" s="8" t="n">
-        <v>46158</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="41" ht="42" customHeight="1">
@@ -4067,7 +4161,7 @@
         </is>
       </c>
       <c r="P41" s="8" t="n">
-        <v>46158</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="42" ht="42" customHeight="1">
@@ -4129,7 +4223,7 @@
         </is>
       </c>
       <c r="P42" s="8" t="n">
-        <v>46158</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="43" ht="42" customHeight="1">
@@ -4191,7 +4285,7 @@
         </is>
       </c>
       <c r="P43" s="8" t="n">
-        <v>46158</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="44" ht="42" customHeight="1">
@@ -4261,7 +4355,7 @@
         </is>
       </c>
       <c r="P44" s="8" t="n">
-        <v>46158</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="45" ht="42" customHeight="1">
@@ -4331,7 +4425,7 @@
         </is>
       </c>
       <c r="P45" s="8" t="n">
-        <v>46158</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="46" ht="42" customHeight="1">
@@ -4397,7 +4491,7 @@
         </is>
       </c>
       <c r="P46" s="8" t="n">
-        <v>46158</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="47" ht="42" customHeight="1">
@@ -4463,7 +4557,7 @@
         </is>
       </c>
       <c r="P47" s="8" t="n">
-        <v>46158</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="48" ht="42" customHeight="1">
@@ -4525,7 +4619,7 @@
       </c>
       <c r="O48" s="4" t="inlineStr"/>
       <c r="P48" s="8" t="n">
-        <v>46158</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="49" ht="42" customHeight="1">
@@ -4583,7 +4677,7 @@
       </c>
       <c r="O49" s="4" t="inlineStr"/>
       <c r="P49" s="8" t="n">
-        <v>46158</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="50" ht="42" customHeight="1">
@@ -4645,7 +4739,7 @@
         </is>
       </c>
       <c r="P50" s="8" t="n">
-        <v>46158</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="51" ht="42" customHeight="1">
@@ -4707,7 +4801,7 @@
         </is>
       </c>
       <c r="P51" s="8" t="n">
-        <v>46158</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="52" ht="42" customHeight="1">
@@ -4769,7 +4863,7 @@
       </c>
       <c r="O52" s="4" t="inlineStr"/>
       <c r="P52" s="8" t="n">
-        <v>46158</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="53" ht="42" customHeight="1">
@@ -4831,7 +4925,7 @@
         </is>
       </c>
       <c r="P53" s="8" t="n">
-        <v>46158</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="54" ht="42" customHeight="1">
@@ -4901,7 +4995,7 @@
         </is>
       </c>
       <c r="P54" s="8" t="n">
-        <v>46158</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="55" ht="42" customHeight="1">
@@ -4963,7 +5057,7 @@
         </is>
       </c>
       <c r="P55" s="8" t="n">
-        <v>46158</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="56" ht="42" customHeight="1">
@@ -5025,7 +5119,7 @@
         </is>
       </c>
       <c r="P56" s="8" t="n">
-        <v>46158</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="57" ht="42" customHeight="1">
@@ -5095,7 +5189,7 @@
         </is>
       </c>
       <c r="P57" s="8" t="n">
-        <v>46158</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="58" ht="42" customHeight="1">
@@ -5169,7 +5263,7 @@
         </is>
       </c>
       <c r="P58" s="8" t="n">
-        <v>46158</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="59" ht="42" customHeight="1">
@@ -5239,7 +5333,7 @@
         </is>
       </c>
       <c r="P59" s="8" t="n">
-        <v>46158</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="60" ht="42" customHeight="1">
@@ -5250,7 +5344,7 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Image generation (coming soon)</t>
+          <t>Image generation — deliberate non-goal</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -5260,7 +5354,7 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Generate brand-aligned imagery directly from canvas + design brief. Marked 'coming soon' — Post-GA feature, not in active build.</t>
+          <t>NOT building. Deliberate non-goal: position IDEA as the brand brief upstream of image tools like Pixii — 'build your brand brief in IDEA, execute anywhere.'</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
@@ -5301,11 +5395,11 @@
       </c>
       <c r="O60" s="4" t="inlineStr">
         <is>
-          <t>Surfaced as 'coming soon' in UI (teaser). Closes the loop from canvas → design brief → generated imagery. No model choice locked in; defer until Post-GA stability work is done.</t>
+          <t>DECISION (2026-05-25): deliberate non-goal, not a backlog item. Image gen needs separate infra + ongoing cost and doesn't improve the core understanding product. Strategy: be the brief upstream of Pixii [Analysis 2026-05-17 'On Image Generation']. Pending Matthew formal sign-off to fully cut.</t>
         </is>
       </c>
       <c r="P60" s="8" t="n">
-        <v>46158</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="61" ht="42" customHeight="1">
@@ -5341,17 +5435,13 @@
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="H61" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" s="4" t="inlineStr">
-        <is>
-          <t>Awaiting decision — flagged Critical in Risk Register</t>
-        </is>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="I61" s="4" t="inlineStr"/>
       <c r="J61" s="4" t="inlineStr">
         <is>
           <t>Matthew</t>
@@ -5367,18 +5457,760 @@
       </c>
       <c r="O61" s="4" t="inlineStr">
         <is>
-          <t>DEFERRED DECISION. Trevor's Gen 3 Brief specifies Lovable; existing codebase is React + Supabase. Don't half-port. Default: extend existing repo until Matthew decides otherwise.</t>
+          <t>RESOLVED 2026-04-23 [F 140678453]: split dev — Matthew builds backend in Claude Code, Trevor builds the marketing site in Lovable; beta stays on Lovable; ideabrandcoach.com on the same codebase/DB initially; custom server deferred until traction. R-013 downgraded to resolved.</t>
         </is>
       </c>
       <c r="P61" s="8" t="n">
-        <v>46158</v>
+        <v>46167</v>
+      </c>
+    </row>
+    <row r="62" ht="42" customHeight="1">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>F-057</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>Trust Gap™ Score results screen</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>conversation</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>Diagnostic results reframed as an aggregated Trust Gap™ Score (e.g. 73) that flags the widest-gap pillar (e.g. empathy). Same 6 questions / 4 pillars; UI + copy only, logic unchanged.</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>not_started</t>
+        </is>
+      </c>
+      <c r="H62" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" s="4" t="inlineStr"/>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>Matthew</t>
+        </is>
+      </c>
+      <c r="K62" s="4" t="inlineStr">
+        <is>
+          <t>F-027</t>
+        </is>
+      </c>
+      <c r="L62" s="4" t="inlineStr">
+        <is>
+          <t>P-011</t>
+        </is>
+      </c>
+      <c r="M62" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="N62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" s="4" t="inlineStr">
+        <is>
+          <t>GEN3 (2026-05-25): the Alpha hook — the #1 thing to validate (must resonate). Underlying diagnostic logic already exists ('all of that code exists as is'); this is the score-screen reframe [F 144128256 @01:45,@05:00].</t>
+        </is>
+      </c>
+      <c r="P62" s="8" t="n">
+        <v>46167</v>
+      </c>
+    </row>
+    <row r="63" ht="42" customHeight="1">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>F-058</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>The Decision Trigger™ capture (Stage 2B)</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>avatar_builder</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>Dedicated screen capturing the event that made the customer act today (the photograph, the comment, the wedding). Was previously only a canvas field.</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>not_started</t>
+        </is>
+      </c>
+      <c r="H63" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="4" t="inlineStr"/>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>Matthew</t>
+        </is>
+      </c>
+      <c r="K63" s="4" t="inlineStr">
+        <is>
+          <t>F-059</t>
+        </is>
+      </c>
+      <c r="L63" s="4" t="inlineStr">
+        <is>
+          <t>P-001</t>
+        </is>
+      </c>
+      <c r="M63" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="N63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" s="4" t="inlineStr">
+        <is>
+          <t>GEN3 (2026-05-25): blue-water line #2 vs Pixii — operates at the level of WHEN the customer is ready to act, not just who they are [F 144128256 @09:13-14:50].</t>
+        </is>
+      </c>
+      <c r="P63" s="8" t="n">
+        <v>46167</v>
+      </c>
+    </row>
+    <row r="64" ht="42" customHeight="1">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>F-059</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>Bridge screen (diagnostic → avatar)</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>conversation</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>Two screens that quote the user's empathy score and explain why building the avatar is the next step. 'A good coach wouldn't just present a score and move on.'</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>not_started</t>
+        </is>
+      </c>
+      <c r="H64" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" s="4" t="inlineStr"/>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>Matthew</t>
+        </is>
+      </c>
+      <c r="K64" s="4" t="inlineStr">
+        <is>
+          <t>F-057</t>
+        </is>
+      </c>
+      <c r="L64" s="4" t="inlineStr">
+        <is>
+          <t>P-011</t>
+        </is>
+      </c>
+      <c r="M64" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" s="4" t="inlineStr">
+        <is>
+          <t>GEN3 (2026-05-25): connective tissue that turns the Trust Gap score into momentum into the avatar build [F 144128256 @07:20].</t>
+        </is>
+      </c>
+      <c r="P64" s="8" t="n">
+        <v>46167</v>
+      </c>
+    </row>
+    <row r="65" ht="42" customHeight="1">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>F-060</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>The Signature (Stage-5 output)</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>avatar_builder</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>One-sentence customer truth — e.g. 'My customer isn't buying shampoo; they're buying the feeling of still being in control of how they age.' The output of the research stages.</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t>not_started</t>
+        </is>
+      </c>
+      <c r="H65" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" s="4" t="inlineStr"/>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>Matthew</t>
+        </is>
+      </c>
+      <c r="K65" s="4" t="inlineStr">
+        <is>
+          <t>F-004,F-005,F-006,F-007</t>
+        </is>
+      </c>
+      <c r="L65" s="4" t="inlineStr">
+        <is>
+          <t>P-001,P-002</t>
+        </is>
+      </c>
+      <c r="M65" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="N65" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" s="4" t="inlineStr">
+        <is>
+          <t>GEN3 (2026-05-25): THE retention / word-of-mouth moment. MVP must validate this + the Trust Gap™ Score first; everything else is downstream [Analysis 2026-05-17]. A draft Signature may surface earlier at the Draft Canvas (F-003).</t>
+        </is>
+      </c>
+      <c r="P65" s="8" t="n">
+        <v>46167</v>
+      </c>
+    </row>
+    <row r="66" ht="42" customHeight="1">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>F-061</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>"Before State" emotional prompt screen</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>avatar_builder</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>Prompts the user to articulate the customer's emotional 'before' state as part of the avatar build.</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>not_started</t>
+        </is>
+      </c>
+      <c r="H66" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" s="4" t="inlineStr"/>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>Matthew</t>
+        </is>
+      </c>
+      <c r="K66" s="4" t="inlineStr"/>
+      <c r="L66" s="4" t="inlineStr">
+        <is>
+          <t>P-002</t>
+        </is>
+      </c>
+      <c r="M66" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="N66" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" s="4" t="inlineStr">
+        <is>
+          <t>GEN3 (2026-05-25): MVP ships static example text; AI-suggestion path deferred (see F-009) [F 144128256 @09:13].</t>
+        </is>
+      </c>
+      <c r="P66" s="8" t="n">
+        <v>46167</v>
+      </c>
+    </row>
+    <row r="67" ht="42" customHeight="1">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>F-062</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>Decision Mode sliders</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>avatar_builder</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>Slider inputs for shopper type (Shopify 4 types), researcher-vs-gut, stakes, and loyalty — so users needn't type free text.</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>not_started</t>
+        </is>
+      </c>
+      <c r="H67" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" s="4" t="inlineStr"/>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>Matthew</t>
+        </is>
+      </c>
+      <c r="K67" s="4" t="inlineStr"/>
+      <c r="L67" s="4" t="inlineStr">
+        <is>
+          <t>P-002</t>
+        </is>
+      </c>
+      <c r="M67" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="N67" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" s="4" t="inlineStr">
+        <is>
+          <t>GEN3 (2026-05-25): lowers friction in the avatar build [F 144128256 @22:00-25:16].</t>
+        </is>
+      </c>
+      <c r="P67" s="8" t="n">
+        <v>46167</v>
+      </c>
+    </row>
+    <row r="68" ht="42" customHeight="1">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>F-063</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>Review Lab (competitor + own review analysis)</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>create_mode</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>'Research mode' that analyses competitor and own reviews. MVP = CSV / pasted-text upload (no scraping) to de-risk; AI analysis is a paid-tier feature.</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
+          <t>not_started</t>
+        </is>
+      </c>
+      <c r="H68" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" s="4" t="inlineStr"/>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>Matthew</t>
+        </is>
+      </c>
+      <c r="K68" s="4" t="inlineStr">
+        <is>
+          <t>F-019</t>
+        </is>
+      </c>
+      <c r="L68" s="4" t="inlineStr">
+        <is>
+          <t>P-005</t>
+        </is>
+      </c>
+      <c r="M68" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="N68" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" s="4" t="inlineStr">
+        <is>
+          <t>GEN3 (2026-05-25): paid-tier AI work behind the freemium gate (F-019). MVP deliberately avoids scraping [F 144128256 @16:31-18:47].</t>
+        </is>
+      </c>
+      <c r="P68" s="8" t="n">
+        <v>46167</v>
+      </c>
+    </row>
+    <row r="69" ht="42" customHeight="1">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>F-064</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>Locked-but-visible canvas fields (free tier)</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>pay_gate</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>Non-subscribers see canvas fields locked rather than hidden, to entice signup/upgrade.</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>not_started</t>
+        </is>
+      </c>
+      <c r="H69" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" s="4" t="inlineStr"/>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>Matthew</t>
+        </is>
+      </c>
+      <c r="K69" s="4" t="inlineStr">
+        <is>
+          <t>F-019</t>
+        </is>
+      </c>
+      <c r="L69" s="4" t="inlineStr">
+        <is>
+          <t>P-012</t>
+        </is>
+      </c>
+      <c r="M69" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="N69" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" s="4" t="inlineStr">
+        <is>
+          <t>GEN3 (2026-05-25): core freemium conversion mechanic [F 144128256 @28:50-32:01].</t>
+        </is>
+      </c>
+      <c r="P69" s="8" t="n">
+        <v>46167</v>
+      </c>
+    </row>
+    <row r="70" ht="42" customHeight="1">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>F-065</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>"Skip avatar" / self-populate path</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>canvas</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>Lets a user skip the avatar build and self-populate the canvas, with an 'avatar not complete' reminder.</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t>not_started</t>
+        </is>
+      </c>
+      <c r="H70" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" s="4" t="inlineStr"/>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>Matthew</t>
+        </is>
+      </c>
+      <c r="K70" s="4" t="inlineStr"/>
+      <c r="L70" s="4" t="inlineStr"/>
+      <c r="M70" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" s="4" t="inlineStr">
+        <is>
+          <t>GEN3 (2026-05-25): Matthew ambivalent — keep loosely scoped [F 144128256 @29:22].</t>
+        </is>
+      </c>
+      <c r="P70" s="8" t="n">
+        <v>46167</v>
+      </c>
+    </row>
+    <row r="71" ht="42" customHeight="1">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>F-066</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>Landing-page A/B split test (ProductPinion)</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>analytics</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>Split-test V1 (ChatGPT-built, polished) vs V2 (Claude-built, simpler) landing pages.</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="inlineStr">
+        <is>
+          <t>not_started</t>
+        </is>
+      </c>
+      <c r="H71" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" s="4" t="inlineStr"/>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>Matthew</t>
+        </is>
+      </c>
+      <c r="K71" s="4" t="inlineStr">
+        <is>
+          <t>F-067</t>
+        </is>
+      </c>
+      <c r="L71" s="4" t="inlineStr"/>
+      <c r="M71" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="N71" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" s="4" t="inlineStr">
+        <is>
+          <t>GEN3 (2026-05-25): confirm ProductPinion supports landing-page split testing (R-019); else build scaffolding [F 140678453 @29:25-34:09].</t>
+        </is>
+      </c>
+      <c r="P71" s="8" t="n">
+        <v>46167</v>
+      </c>
+    </row>
+    <row r="72" ht="42" customHeight="1">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>F-067</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>Marketing site on ideabrandcoach.com (same codebase/DB)</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>infrastructure</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>Public marketing site; app gated, revealing feature sets as they become beta-ready. Same codebase/DB initially.</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>not_started</t>
+        </is>
+      </c>
+      <c r="H72" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" s="4" t="inlineStr"/>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>Matthew</t>
+        </is>
+      </c>
+      <c r="K72" s="4" t="inlineStr"/>
+      <c r="L72" s="4" t="inlineStr"/>
+      <c r="M72" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="N72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" s="4" t="inlineStr">
+        <is>
+          <t>GEN3 (2026-05-25): old consultancy site expires June. Trevor owns this track in Lovable (split-dev, F-052) [F 140691318 @00:19,@00:42].</t>
+        </is>
+      </c>
+      <c r="P72" s="8" t="n">
+        <v>46167</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:P1"/>
   </mergeCells>
-  <conditionalFormatting sqref="G3:G261">
+  <conditionalFormatting sqref="G3:G272">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="2">
       <formula>"complete"</formula>
     </cfRule>
@@ -5396,16 +6228,16 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation sqref="C3:C261" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Value must match one of the allowed options." type="list">
+    <dataValidation sqref="C3:C272" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Value must match one of the allowed options." type="list">
       <formula1>"conversation,avatar_builder,canvas,create_mode,coach_mode,pay_gate,export,accounts,asset_tracking,feedback_loop,analytics,infrastructure,design_system"</formula1>
     </dataValidation>
-    <dataValidation sqref="E3:E261" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Value must match one of the allowed options." type="list">
+    <dataValidation sqref="E3:E272" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Value must match one of the allowed options." type="list">
       <formula1>"Alpha,Beta,GA,Post-GA"</formula1>
     </dataValidation>
-    <dataValidation sqref="F3:F261" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Value must match one of the allowed options." type="list">
+    <dataValidation sqref="F3:F272" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Value must match one of the allowed options." type="list">
       <formula1>"P0,P1,P2"</formula1>
     </dataValidation>
-    <dataValidation sqref="G3:G261" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Value must match one of the allowed options." type="list">
+    <dataValidation sqref="G3:G272" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Value must match one of the allowed options." type="list">
       <formula1>"not_started,in_progress,blocked,in_review,complete"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8543,7 +9375,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8622,7 +9454,7 @@
         </is>
       </c>
       <c r="E5" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-001",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-002",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-001",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-002",'Features'!$G$3:$G$61,"complete"))=2,"MET","OPEN — "&amp;(2-(COUNTIFS('Features'!$A$3:$A$61,"F-001",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-002",'Features'!$G$3:$G$61,"complete")))&amp;" of 2 remaining"))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$72,"F-001",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-002",'Features'!$G$3:$G$72,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$72,"F-001",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-002",'Features'!$G$3:$G$72,"complete"))=2,"MET","OPEN — "&amp;(2-(COUNTIFS('Features'!$A$3:$A$72,"F-001",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-002",'Features'!$G$3:$G$72,"complete")))&amp;" of 2 remaining"))</f>
         <v/>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -8653,7 +9485,7 @@
         </is>
       </c>
       <c r="E6" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-003",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-003",'Features'!$G$3:$G$61,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$61,"F-003",'Features'!$G$3:$G$61,"complete")))&amp;" of 1 remaining"))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$72,"F-003",'Features'!$G$3:$G$72,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$72,"F-003",'Features'!$G$3:$G$72,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$72,"F-003",'Features'!$G$3:$G$72,"complete")))&amp;" of 1 remaining"))</f>
         <v/>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -8675,7 +9507,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>All 4 sections accept input, persist, and surface AI assistance modes.</t>
+          <t>All sections accept input, persist, and surface AI assistance modes. NB reconcile the 4 sections with the new 5-stage conversational flow ending in The Signature (F-060) — pending sign-off.</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -8684,7 +9516,7 @@
         </is>
       </c>
       <c r="E7" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-004",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-005",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-009",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-004",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-005",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-009",'Features'!$G$3:$G$61,"complete"))=5,"MET","OPEN — "&amp;(5-(COUNTIFS('Features'!$A$3:$A$61,"F-004",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-005",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-009",'Features'!$G$3:$G$61,"complete")))&amp;" of 5 remaining"))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$72,"F-004",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-005",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-006",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-007",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-009",'Features'!$G$3:$G$72,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$72,"F-004",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-005",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-006",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-007",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-009",'Features'!$G$3:$G$72,"complete"))=5,"MET","OPEN — "&amp;(5-(COUNTIFS('Features'!$A$3:$A$72,"F-004",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-005",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-006",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-007",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-009",'Features'!$G$3:$G$72,"complete")))&amp;" of 5 remaining"))</f>
         <v/>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -8706,7 +9538,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>All 28+ fields render. Trigger Moment displayed prominently as 'Strategic Entry Point'.</t>
+          <t>All 28+ fields render, auto-populated from Avatar data. The Decision Trigger™ displayed prominently.</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -8715,7 +9547,7 @@
         </is>
       </c>
       <c r="E8" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"complete")))&amp;" of 1 remaining"))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$72,"F-008",'Features'!$G$3:$G$72,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$72,"F-008",'Features'!$G$3:$G$72,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$72,"F-008",'Features'!$G$3:$G$72,"complete")))&amp;" of 1 remaining"))</f>
         <v/>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -8746,7 +9578,7 @@
         </is>
       </c>
       <c r="E9" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-011",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-011",'Features'!$G$3:$G$61,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$61,"F-011",'Features'!$G$3:$G$61,"complete")))&amp;" of 1 remaining"))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$72,"F-011",'Features'!$G$3:$G$72,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$72,"F-011",'Features'!$G$3:$G$72,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$72,"F-011",'Features'!$G$3:$G$72,"complete")))&amp;" of 1 remaining"))</f>
         <v/>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -8777,7 +9609,7 @@
         </is>
       </c>
       <c r="E10" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-013",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-014",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-015",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-016",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-013",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-014",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-015",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-016",'Features'!$G$3:$G$61,"complete"))=4,"MET","OPEN — "&amp;(4-(COUNTIFS('Features'!$A$3:$A$61,"F-013",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-014",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-015",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-016",'Features'!$G$3:$G$61,"complete")))&amp;" of 4 remaining"))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$72,"F-013",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-014",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-015",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-016",'Features'!$G$3:$G$72,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$72,"F-013",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-014",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-015",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-016",'Features'!$G$3:$G$72,"complete"))=4,"MET","OPEN — "&amp;(4-(COUNTIFS('Features'!$A$3:$A$72,"F-013",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-014",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-015",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-016",'Features'!$G$3:$G$72,"complete")))&amp;" of 4 remaining"))</f>
         <v/>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -8808,7 +9640,7 @@
         </is>
       </c>
       <c r="E11" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-017",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-017",'Features'!$G$3:$G$61,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$61,"F-017",'Features'!$G$3:$G$61,"complete")))&amp;" of 1 remaining"))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$72,"F-017",'Features'!$G$3:$G$72,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$72,"F-017",'Features'!$G$3:$G$72,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$72,"F-017",'Features'!$G$3:$G$72,"complete")))&amp;" of 1 remaining"))</f>
         <v/>
       </c>
       <c r="F11" s="4" t="inlineStr"/>
@@ -8835,7 +9667,7 @@
         </is>
       </c>
       <c r="E12" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-018",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-018",'Features'!$G$3:$G$61,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$61,"F-018",'Features'!$G$3:$G$61,"complete")))&amp;" of 1 remaining"))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$72,"F-018",'Features'!$G$3:$G$72,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$72,"F-018",'Features'!$G$3:$G$72,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$72,"F-018",'Features'!$G$3:$G$72,"complete")))&amp;" of 1 remaining"))</f>
         <v/>
       </c>
       <c r="F12" s="4" t="inlineStr"/>
@@ -8862,7 +9694,7 @@
         </is>
       </c>
       <c r="E13" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-052",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-052",'Features'!$G$3:$G$61,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$61,"F-052",'Features'!$G$3:$G$61,"complete")))&amp;" of 1 remaining"))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$72,"F-052",'Features'!$G$3:$G$72,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$72,"F-052",'Features'!$G$3:$G$72,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$72,"F-052",'Features'!$G$3:$G$72,"complete")))&amp;" of 1 remaining"))</f>
         <v/>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -8893,7 +9725,7 @@
         </is>
       </c>
       <c r="E14" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-016",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-016",'Features'!$G$3:$G$61,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$61,"F-016",'Features'!$G$3:$G$61,"complete")))&amp;" of 1 remaining"))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$72,"F-016",'Features'!$G$3:$G$72,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$72,"F-016",'Features'!$G$3:$G$72,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$72,"F-016",'Features'!$G$3:$G$72,"complete")))&amp;" of 1 remaining"))</f>
         <v/>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -8924,7 +9756,7 @@
         </is>
       </c>
       <c r="E15" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-019",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-019",'Features'!$G$3:$G$61,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$61,"F-019",'Features'!$G$3:$G$61,"complete")))&amp;" of 1 remaining"))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$72,"F-019",'Features'!$G$3:$G$72,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$72,"F-019",'Features'!$G$3:$G$72,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$72,"F-019",'Features'!$G$3:$G$72,"complete")))&amp;" of 1 remaining"))</f>
         <v/>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -8955,7 +9787,7 @@
         </is>
       </c>
       <c r="E16" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-020",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-021",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-020",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-021",'Features'!$G$3:$G$61,"complete"))=2,"MET","OPEN — "&amp;(2-(COUNTIFS('Features'!$A$3:$A$61,"F-020",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-021",'Features'!$G$3:$G$61,"complete")))&amp;" of 2 remaining"))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$72,"F-020",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-021",'Features'!$G$3:$G$72,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$72,"F-020",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-021",'Features'!$G$3:$G$72,"complete"))=2,"MET","OPEN — "&amp;(2-(COUNTIFS('Features'!$A$3:$A$72,"F-020",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-021",'Features'!$G$3:$G$72,"complete")))&amp;" of 2 remaining"))</f>
         <v/>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -8986,7 +9818,7 @@
         </is>
       </c>
       <c r="E17" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"complete")))&amp;" of 1 remaining"))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$72,"F-022",'Features'!$G$3:$G$72,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$72,"F-022",'Features'!$G$3:$G$72,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$72,"F-022",'Features'!$G$3:$G$72,"complete")))&amp;" of 1 remaining"))</f>
         <v/>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -9017,7 +9849,7 @@
         </is>
       </c>
       <c r="E18" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-023",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-023",'Features'!$G$3:$G$61,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$61,"F-023",'Features'!$G$3:$G$61,"complete")))&amp;" of 1 remaining"))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$72,"F-023",'Features'!$G$3:$G$72,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$72,"F-023",'Features'!$G$3:$G$72,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$72,"F-023",'Features'!$G$3:$G$72,"complete")))&amp;" of 1 remaining"))</f>
         <v/>
       </c>
       <c r="F18" s="4" t="inlineStr"/>
@@ -9044,7 +9876,7 @@
         </is>
       </c>
       <c r="E19" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-028",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-028",'Features'!$G$3:$G$61,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$61,"F-028",'Features'!$G$3:$G$61,"complete")))&amp;" of 1 remaining"))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$72,"F-028",'Features'!$G$3:$G$72,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$72,"F-028",'Features'!$G$3:$G$72,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$72,"F-028",'Features'!$G$3:$G$72,"complete")))&amp;" of 1 remaining"))</f>
         <v/>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -9075,7 +9907,7 @@
         </is>
       </c>
       <c r="E20" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-024",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-024",'Features'!$G$3:$G$61,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$61,"F-024",'Features'!$G$3:$G$61,"complete")))&amp;" of 1 remaining"))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$72,"F-024",'Features'!$G$3:$G$72,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$72,"F-024",'Features'!$G$3:$G$72,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$72,"F-024",'Features'!$G$3:$G$72,"complete")))&amp;" of 1 remaining"))</f>
         <v/>
       </c>
       <c r="F20" s="4" t="inlineStr"/>
@@ -9102,7 +9934,7 @@
         </is>
       </c>
       <c r="E21" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-025",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-025",'Features'!$G$3:$G$61,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$61,"F-025",'Features'!$G$3:$G$61,"complete")))&amp;" of 1 remaining"))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$72,"F-025",'Features'!$G$3:$G$72,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$72,"F-025",'Features'!$G$3:$G$72,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$72,"F-025",'Features'!$G$3:$G$72,"complete")))&amp;" of 1 remaining"))</f>
         <v/>
       </c>
       <c r="F21" s="4" t="inlineStr"/>
@@ -9129,7 +9961,7 @@
         </is>
       </c>
       <c r="E22" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-027",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-027",'Features'!$G$3:$G$61,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$61,"F-027",'Features'!$G$3:$G$61,"complete")))&amp;" of 1 remaining"))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$72,"F-027",'Features'!$G$3:$G$72,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$72,"F-027",'Features'!$G$3:$G$72,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$72,"F-027",'Features'!$G$3:$G$72,"complete")))&amp;" of 1 remaining"))</f>
         <v/>
       </c>
       <c r="F22" s="4" t="inlineStr"/>
@@ -9156,7 +9988,7 @@
         </is>
       </c>
       <c r="E23" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-031",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-031",'Features'!$G$3:$G$61,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$61,"F-031",'Features'!$G$3:$G$61,"complete")))&amp;" of 1 remaining"))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$72,"F-031",'Features'!$G$3:$G$72,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$72,"F-031",'Features'!$G$3:$G$72,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$72,"F-031",'Features'!$G$3:$G$72,"complete")))&amp;" of 1 remaining"))</f>
         <v/>
       </c>
       <c r="F23" s="4" t="inlineStr"/>
@@ -9183,7 +10015,7 @@
         </is>
       </c>
       <c r="E24" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-032",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-032",'Features'!$G$3:$G$61,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$61,"F-032",'Features'!$G$3:$G$61,"complete")))&amp;" of 1 remaining"))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$72,"F-032",'Features'!$G$3:$G$72,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$72,"F-032",'Features'!$G$3:$G$72,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$72,"F-032",'Features'!$G$3:$G$72,"complete")))&amp;" of 1 remaining"))</f>
         <v/>
       </c>
       <c r="F24" s="4" t="inlineStr"/>
@@ -9210,7 +10042,7 @@
         </is>
       </c>
       <c r="E25" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-033",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-033",'Features'!$G$3:$G$61,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$61,"F-033",'Features'!$G$3:$G$61,"complete")))&amp;" of 1 remaining"))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$72,"F-033",'Features'!$G$3:$G$72,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$72,"F-033",'Features'!$G$3:$G$72,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$72,"F-033",'Features'!$G$3:$G$72,"complete")))&amp;" of 1 remaining"))</f>
         <v/>
       </c>
       <c r="F25" s="4" t="inlineStr"/>
@@ -9237,7 +10069,7 @@
         </is>
       </c>
       <c r="E26" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-034",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-034",'Features'!$G$3:$G$61,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$61,"F-034",'Features'!$G$3:$G$61,"complete")))&amp;" of 1 remaining"))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$72,"F-034",'Features'!$G$3:$G$72,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$72,"F-034",'Features'!$G$3:$G$72,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$72,"F-034",'Features'!$G$3:$G$72,"complete")))&amp;" of 1 remaining"))</f>
         <v/>
       </c>
       <c r="F26" s="4" t="inlineStr"/>
@@ -9264,7 +10096,7 @@
         </is>
       </c>
       <c r="E27" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-037",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-037",'Features'!$G$3:$G$61,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$61,"F-037",'Features'!$G$3:$G$61,"complete")))&amp;" of 1 remaining"))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$72,"F-037",'Features'!$G$3:$G$72,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$72,"F-037",'Features'!$G$3:$G$72,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$72,"F-037",'Features'!$G$3:$G$72,"complete")))&amp;" of 1 remaining"))</f>
         <v/>
       </c>
       <c r="F27" s="4" t="inlineStr"/>
@@ -9291,7 +10123,7 @@
         </is>
       </c>
       <c r="E28" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-035",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-035",'Features'!$G$3:$G$61,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$61,"F-035",'Features'!$G$3:$G$61,"complete")))&amp;" of 1 remaining"))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$72,"F-035",'Features'!$G$3:$G$72,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$72,"F-035",'Features'!$G$3:$G$72,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$72,"F-035",'Features'!$G$3:$G$72,"complete")))&amp;" of 1 remaining"))</f>
         <v/>
       </c>
       <c r="F28" s="4" t="inlineStr"/>
@@ -9318,7 +10150,7 @@
         </is>
       </c>
       <c r="E29" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-036",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-036",'Features'!$G$3:$G$61,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$61,"F-036",'Features'!$G$3:$G$61,"complete")))&amp;" of 1 remaining"))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$72,"F-036",'Features'!$G$3:$G$72,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$72,"F-036",'Features'!$G$3:$G$72,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$72,"F-036",'Features'!$G$3:$G$72,"complete")))&amp;" of 1 remaining"))</f>
         <v/>
       </c>
       <c r="F29" s="4" t="inlineStr"/>
@@ -9345,7 +10177,7 @@
         </is>
       </c>
       <c r="E30" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-034",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-034",'Features'!$G$3:$G$61,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$61,"F-034",'Features'!$G$3:$G$61,"complete")))&amp;" of 1 remaining"))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$72,"F-034",'Features'!$G$3:$G$72,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$72,"F-034",'Features'!$G$3:$G$72,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$72,"F-034",'Features'!$G$3:$G$72,"complete")))&amp;" of 1 remaining"))</f>
         <v/>
       </c>
       <c r="F30" s="4" t="inlineStr"/>
@@ -9372,12 +10204,136 @@
         </is>
       </c>
       <c r="E31" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-038",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-038",'Features'!$G$3:$G$61,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$61,"F-038",'Features'!$G$3:$G$61,"complete")))&amp;" of 1 remaining"))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$72,"F-038",'Features'!$G$3:$G$72,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$72,"F-038",'Features'!$G$3:$G$72,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$72,"F-038",'Features'!$G$3:$G$72,"complete")))&amp;" of 1 remaining"))</f>
         <v/>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
           <t>OPEN QUESTION: Gen 3 spec does not address; existing V2 PRD scopes it. Treated here as GA P0 pending Matthew sign-off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="42" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Trust Gap™ Score lands</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Tester sees an aggregated Trust Gap™ Score + widest-gap pillar and feels it's accurate; the bridge explains why building the avatar is next.</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>F-057,F-059</t>
+        </is>
+      </c>
+      <c r="E32" s="4">
+        <f>IF((COUNTIFS('Features'!$A$3:$A$72,"F-057",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-059",'Features'!$G$3:$G$72,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$72,"F-057",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-059",'Features'!$G$3:$G$72,"complete"))=2,"MET","OPEN — "&amp;(2-(COUNTIFS('Features'!$A$3:$A$72,"F-057",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-059",'Features'!$G$3:$G$72,"complete")))&amp;" of 2 remaining"))</f>
+        <v/>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>The #1 thing to validate (Trevor). If the score doesn't resonate, nothing downstream matters.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="42" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>The Signature</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Tester produces a one-sentence Signature they recognise as true and had not previously articulated.</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>F-060</t>
+        </is>
+      </c>
+      <c r="E33" s="4">
+        <f>IF((COUNTIFS('Features'!$A$3:$A$72,"F-060",'Features'!$G$3:$G$72,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$72,"F-060",'Features'!$G$3:$G$72,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$72,"F-060",'Features'!$G$3:$G$72,"complete")))&amp;" of 1 remaining"))</f>
+        <v/>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>The retention / word-of-mouth moment. Validate alongside the Trust Gap Score, before everything else.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="42" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>The Decision Trigger™ captured</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>A dedicated screen captures the event that made the customer act today ('why today').</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>F-058</t>
+        </is>
+      </c>
+      <c r="E34" s="4">
+        <f>IF((COUNTIFS('Features'!$A$3:$A$72,"F-058",'Features'!$G$3:$G$72,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$72,"F-058",'Features'!$G$3:$G$72,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$72,"F-058",'Features'!$G$3:$G$72,"complete")))&amp;" of 1 remaining"))</f>
+        <v/>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>Blue-water line #2 vs Pixii — operates at the level of WHEN, not just who.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="42" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Marketing site live (gated)</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>ideabrandcoach.com is live; the app is gated, revealing feature sets as they become beta-ready.</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>F-067</t>
+        </is>
+      </c>
+      <c r="E35" s="4">
+        <f>IF((COUNTIFS('Features'!$A$3:$A$72,"F-067",'Features'!$G$3:$G$72,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$72,"F-067",'Features'!$G$3:$G$72,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$72,"F-067",'Features'!$G$3:$G$72,"complete")))&amp;" of 1 remaining"))</f>
+        <v/>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>Old consultancy site expires June; Trevor owns this track in Lovable (split-dev).</t>
         </is>
       </c>
     </row>
@@ -9386,7 +10342,7 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <conditionalFormatting sqref="E5:E31">
+  <conditionalFormatting sqref="E5:E35">
     <cfRule type="expression" priority="1" dxfId="2">
       <formula>E5="MET"</formula>
     </cfRule>
@@ -9398,7 +10354,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5:A131" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Value must match one of the allowed options." type="list">
+    <dataValidation sqref="A5:A135" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Value must match one of the allowed options." type="list">
       <formula1>"Alpha,Beta,GA,Post-GA"</formula1>
     </dataValidation>
   </dataValidations>
@@ -9491,7 +10447,7 @@
         </is>
       </c>
       <c r="E5" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-001",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-004",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-005",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-023",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-001",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-004",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-005",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-023",'Features'!$G$3:$G$61,"complete"))=8,"MET","OPEN — "&amp;(8-(COUNTIFS('Features'!$A$3:$A$61,"F-001",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-004",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-005",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-008",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-022",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-023",'Features'!$G$3:$G$61,"complete")))&amp;" of 8 remaining"))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$72,"F-001",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-004",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-005",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-006",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-007",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-008",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-022",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-023",'Features'!$G$3:$G$72,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$72,"F-001",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-004",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-005",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-006",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-007",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-008",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-022",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-023",'Features'!$G$3:$G$72,"complete"))=8,"MET","OPEN — "&amp;(8-(COUNTIFS('Features'!$A$3:$A$72,"F-001",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-004",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-005",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-006",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-007",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-008",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-022",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-023",'Features'!$G$3:$G$72,"complete")))&amp;" of 8 remaining"))</f>
         <v/>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -9522,7 +10478,7 @@
         </is>
       </c>
       <c r="E6" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-054",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-054",'Features'!$G$3:$G$61,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$61,"F-054",'Features'!$G$3:$G$61,"complete")))&amp;" of 1 remaining"))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$72,"F-054",'Features'!$G$3:$G$72,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$72,"F-054",'Features'!$G$3:$G$72,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$72,"F-054",'Features'!$G$3:$G$72,"complete")))&amp;" of 1 remaining"))</f>
         <v/>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -9553,7 +10509,7 @@
         </is>
       </c>
       <c r="E7" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-054",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-054",'Features'!$G$3:$G$61,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$61,"F-054",'Features'!$G$3:$G$61,"complete")))&amp;" of 1 remaining"))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$72,"F-054",'Features'!$G$3:$G$72,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$72,"F-054",'Features'!$G$3:$G$72,"complete"))=1,"MET","OPEN — "&amp;(1-(COUNTIFS('Features'!$A$3:$A$72,"F-054",'Features'!$G$3:$G$72,"complete")))&amp;" of 1 remaining"))</f>
         <v/>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -9584,7 +10540,7 @@
         </is>
       </c>
       <c r="E8" s="4">
-        <f>IF((COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-054",'Features'!$G$3:$G$61,"blocked")+COUNTIFS('Features'!$A$3:$A$61,"F-055",'Features'!$G$3:$G$61,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-054",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-055",'Features'!$G$3:$G$61,"complete"))=4,"MET","OPEN — "&amp;(4-(COUNTIFS('Features'!$A$3:$A$61,"F-006",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-007",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-054",'Features'!$G$3:$G$61,"complete")+COUNTIFS('Features'!$A$3:$A$61,"F-055",'Features'!$G$3:$G$61,"complete")))&amp;" of 4 remaining"))</f>
+        <f>IF((COUNTIFS('Features'!$A$3:$A$72,"F-006",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-007",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-054",'Features'!$G$3:$G$72,"blocked")+COUNTIFS('Features'!$A$3:$A$72,"F-055",'Features'!$G$3:$G$72,"blocked"))&gt;0,"BLOCKED — see mapped features",IF((COUNTIFS('Features'!$A$3:$A$72,"F-006",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-007",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-054",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-055",'Features'!$G$3:$G$72,"complete"))=4,"MET","OPEN — "&amp;(4-(COUNTIFS('Features'!$A$3:$A$72,"F-006",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-007",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-054",'Features'!$G$3:$G$72,"complete")+COUNTIFS('Features'!$A$3:$A$72,"F-055",'Features'!$G$3:$G$72,"complete")))&amp;" of 4 remaining"))</f>
         <v/>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -9619,7 +10575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -9715,7 +10671,7 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>At Alpha exit, fewer than 2 of {P-001, P-002, P-003} verified PARTIAL+ via tester debriefs; OR &lt;50% of testers can articulate one concrete way the canvas changed how they think about their customer; OR fewer than 60% of shipped features map to ≥1 problem.</t>
+          <t>At Alpha exit, the Trust Gap™ Score does NOT resonate (testers don't feel the gap is real/accurate) OR The Signature does NOT surprise testers with its accuracy — i.e. fewer than 2 of {P-011 Diagnostic, P-001 Signature/articulation, P-003 strategy doc} verified PARTIAL+ via tester debriefs; OR &lt;50% of testers can articulate one concrete way the canvas changed how they think about their customer; OR fewer than 60% of shipped features map to ≥1 problem.</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
@@ -9725,7 +10681,7 @@
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>Problems sheet operationalises tracking. Alpha feedback Moments 1 + 2 measure perceived value directly. If signal is low at Alpha midpoint, narrow scope to deepen 1-2 problems rather than adding features.</t>
+          <t>Problems sheet operationalises tracking. Alpha feedback Moments 1 + 2 measure perceived value directly. If signal is low at Alpha midpoint, narrow scope to deepen 1-2 problems rather than adding features. GEN3 (2026-05-25): Trevor's two MVP-critical problems are the Trust Gap™ Score (P-011) and The Signature (P-001) — test those first [Analysis 2026-05-17]. ~2-3yr defensibility window → ship Alpha fast, don't gold-plate; full strategic frame in the Launch Roadmap Overview.</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
@@ -10233,12 +11189,12 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>triggered</t>
+          <t>resolved</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -10253,12 +11209,12 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>Decide explicitly at sprint start which is canonical (F-052)</t>
+          <t>RESOLVED — split-dev decision recorded (F-052)</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>Status set to triggered because the decision is currently open and Gen 3 work is paused on this call.</t>
+          <t>RESOLVED 2026-04-23 [F 140678453]: split dev — Matthew builds backend in Claude Code, Trevor builds the marketing site in Lovable; beta stays on Lovable; custom server deferred until traction. Downgraded Critical→Low.</t>
         </is>
       </c>
     </row>
@@ -10270,7 +11226,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Competitor launches similar tool</t>
+          <t>Competitor launches similar tool (StoryBrand framework / Pixii execution)</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -10300,10 +11256,14 @@
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>Speed; first-mover positioning on Forensic Avatar Builder; lean into Voice of Customer differentiator</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr"/>
+          <t>Speed; first-mover positioning on the Forensic Avatar Builder; lean into the Voice of Customer differentiator</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>Two distinct vectors: StoryBrand (framework competitor) and Pixii (execution/image tool with a strategy layer). GEN3 (2026-05-25): 5 blue-water lines vs Pixii — (1) evidence vs inference, (2) The Decision Trigger™, (3) Trust Gap™ Diagnostic, (4) Coach as a live briefing not a one-shot PDF, (5) framework ownership. Position upstream of Pixii ('build the brief in IDEA, execute anywhere'), not as a competitor [Analysis 2026-05-17].</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="42" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
@@ -10347,12 +11307,200 @@
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>R-016</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Single-developer velocity / availability</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>monitoring</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>No app progress in any 2-week window; another deadline slips</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>Matthew</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Lock a small hard Alpha scope; timebox; Trevor owns the marketing-site track in parallel</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>GEN3 (2026-05-25): the dominant live risk. Matthew is repeatedly pulled to higher-paying work; the May-1 beta target was already missed and the project is in a re-planning holding pattern [WA 2026-01-23,02-20,04-18,05-13..16].</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>R-017</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Knowledge-storage architecture undecided</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>monitoring</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>KB work blocks F-049 / coach grounding</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>Matthew</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>Pick one for Alpha; defer 'offer both'; spike before committing</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>Knowledge-graph vs spreadsheet vs Obsidian; 'where does the KB sit — Supabase?' [WA 2026-04-24,05-19].</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>R-018</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Titan conflict-of-interest</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>monitoring</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Titan declines or restricts promotion</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>Matthew</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>Resolve with Dan/Titan before relying on that channel; line up alternative beta sources</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>Athena said Trevor 'can't promote this to members', yet the beta targets the Titan AI work party [F 140678453 @31:30].</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>R-019</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>ProductPinion may not support landing-page A/B</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>monitoring</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>Capability unconfirmed at site launch</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>Trevor</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>Trevor confirms with ProductPinion contact; else build split-test scaffolding (F-066)</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>ProductPinion may only support listing A/B, not landing-page split testing [F 140678453 @34:09].</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
-  <conditionalFormatting sqref="E4:E118">
+  <conditionalFormatting sqref="E4:E122">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="3">
       <formula>"monitoring"</formula>
     </cfRule>
@@ -10366,7 +11514,7 @@
       <formula>"resolved"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D4:D118">
+  <conditionalFormatting sqref="D4:D122">
     <cfRule type="cellIs" priority="5" operator="equal" dxfId="5">
       <formula>"Critical"</formula>
     </cfRule>
@@ -10381,13 +11529,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="C4:C118" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Value must match one of the allowed options." type="list">
+    <dataValidation sqref="C4:C122" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Value must match one of the allowed options." type="list">
       <formula1>"Alpha,Beta,GA,Post-GA,All"</formula1>
     </dataValidation>
-    <dataValidation sqref="D4:D118" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Value must match one of the allowed options." type="list">
+    <dataValidation sqref="D4:D122" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Value must match one of the allowed options." type="list">
       <formula1>"Critical,High,Medium,Low"</formula1>
     </dataValidation>
-    <dataValidation sqref="E4:E118" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Value must match one of the allowed options." type="list">
+    <dataValidation sqref="E4:E122" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Value must match one of the allowed options." type="list">
       <formula1>"monitoring,triggered,mitigated,resolved"</formula1>
     </dataValidation>
   </dataValidations>
@@ -10401,7 +11549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10442,88 +11590,484 @@
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Matthew (via Claude Code)</t>
+          <t>Matthew ↔ Trevor (WhatsApp)</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Initial workbook created</t>
+          <t>Core thesis: get brand owners to switch from ChatGPT to the app (work gets lost in threads)</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Operational counterpart to Launch Roadmap; seeded from Gen 3 brief, V2 PRD, and Launch Roadmap workbook.</t>
+          <t>Area(s): conversation | Source: WhatsApp 2025-11-22.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Matthew (via Claude Code)</t>
+          <t>Matthew ↔ Trevor (WhatsApp)</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Added F-053..F-056 + Brand Needs sheet</t>
+          <t>Pre-fill fields from users' existing brand docs (initially via a NotebookLM template) rather than re-typing</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Captured multi-angle, image comparison, design brief, and (post-GA) image generation features. Added Brand Needs sheet seeded with InfinityVault as the first validation case.</t>
+          <t>Area(s): avatar_builder, infrastructure | Source: WhatsApp 2025-11-27.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Matthew (via Claude Code)</t>
+          <t>Matthew ↔ Trevor (WhatsApp)</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Corrected status for brand strategy doc + PDF export; added Problems sheet</t>
+          <t>Data model → per-user AND per-brand separation (triggered by the coach conflating two brands)</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>F-008 was wrongly marked not_started — corrected to in_review 80% based on shipped generate-brand-strategy-document. F-023 corrected to in_progress 65% (PDF + Markdown shipped, Word still missing). Added Problems sheet with the 10 problems we solve mapped to features; added problems_addressed column on Features.</t>
+          <t>Area(s): infrastructure, accounts, coach_mode | Source: WhatsApp 2025-12-15.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
+          <t>2025-12-19</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Matthew ↔ Trevor (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Brand Canvas = central synthesis layer pulling from all modules</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Area(s): canvas | Source: WhatsApp 2025-12-19.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>2025-12-25</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Matthew ↔ Trevor (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>System Knowledge Base (vector store) seeded with Trevor's book; RAG-grounded</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Area(s): infrastructure, coach_mode | Source: WhatsApp 2025-12-25.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Matthew ↔ Trevor (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Beta-Ready Scope formalized ($1000/Phase 1): Insight Module + Approval Gate + single unified strategy doc; billing deferred</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Area(s): multi | Source: WhatsApp 2026-01-16.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Matthew ↔ Trevor (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Cut non-functional pages — every page must produce an output</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Area(s): design_system | Source: WhatsApp 2026-01-26.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Matthew ↔ Trevor (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Trevor freezes scope: 'no additional features, speed is priority'</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Area(s): all | Source: WhatsApp 2026-02-21.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Matthew ↔ Trevor (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Positioning: authority on branding/avatar/messaging + results tracking; don't compete on content generation</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Area(s): strategy | Source: WhatsApp 2026-03-01.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Matthew ↔ Trevor (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>3-tier commercial model (App / Brand Community / 1:1 Consultancy); Agentic Commerce / AVM module idea</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Area(s): create_mode | Source: WhatsApp 2026-03-18.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Matthew ↔ Trevor (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Migrate AI backend OpenAI → Anthropic/Claude (cost + maintainability)</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Area(s): infrastructure | Source: WhatsApp 2026-04-06.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Matthew ↔ Trevor (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Gen 3 respec: conversation-first; Avatar Builder = core; three modes Canvas/Create/Coach</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Area(s): all | Source: WhatsApp 2026-04-12.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Gen 3 meeting (Fathom 140678453, 140691318)</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Split dev (Matthew backend in Claude Code / Trevor marketing in Lovable); beta on Lovable; ideabrandcoach.com</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Area(s): infrastructure | Source: Fathom 140678453 + 140691318. Resolves F-052 / R-013.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Matthew ↔ Trevor (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Gen 3 doc set delivered (8 docs incl. Avatar 2.0 field spec + Decision Trigger™)</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Area(s): all | Source: WhatsApp 2026-05-02.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Gen 3 meeting (Fathom 144128256)</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Gen 3 mockup: Trust Gap™ Score, Decision Trigger™ screen, Customer Insight Engine™, bridge screen, freemium, locked-but-visible fields</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Area(s): conversation, avatar_builder, canvas, pay_gate | Source: Fathom 144128256. Basis for F-057..F-064.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Matthew (via Claude Code)</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Initial workbook created</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Operational counterpart to Launch Roadmap; seeded from Gen 3 brief, V2 PRD, and Launch Roadmap workbook.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Matthew (via Claude Code)</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Added F-053..F-056 + Brand Needs sheet</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Captured multi-angle, image comparison, design brief, and (post-GA) image generation features. Added Brand Needs sheet seeded with InfinityVault as the first validation case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
           <t>2026-05-16</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Matthew ↔ Trevor (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Three-phase launch (Alpha→Beta→GA) formalized; Launch Roadmap + Feature Status Tracker created; placeholder 6-week target (to tighten)</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Area(s): all | Source: WhatsApp 2026-05-16.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>Matthew (via Claude Code)</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Corrected status for brand strategy doc + PDF export; added Problems sheet</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>F-008 was wrongly marked not_started — corrected to in_review 80% based on shipped generate-brand-strategy-document. F-023 corrected to in_progress 65% (PDF + Markdown shipped, Word still missing). Added Problems sheet with the 10 problems we solve mapped to features; added problems_addressed column on Features.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Matthew (via Claude Code)</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>Full sub-feature audit against the codebase (6 parallel agents)</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>Audited all 64 sub-features against actual code on main. Major findings: (a) F-008 dropped 80→39% — the strategy doc ships but the Forensic *tier* concept and Trigger Moment callout don't exist in code; (b) F-002.2 + F-012.2 reduced from 100% — quality badges use value heuristics, not extractor confidence; (c) F-009 dropped 30→19% — only ONE AI mode is independently invocable, not four; (d) F-011.1 reduced from 100→70% — code uses field_source + separate is_locked, not a manuallyEdited boolean; (e) all of F-013/F-014/F-015/F-016 confirmed 0 — no three-moment infra exists; existing BetaFeedback is a separate older system that won't compose; (f) F-017 confirmed 0 — no Sentry installed. Per-sub-feature notes updated with file:line evidence; parent features rolled up to averages.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Trevor (strategic analysis)</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Strategic analysis: 10 problems; MVP must validate Trust Gap™ + The Signature first; no image generation; 'blue water' vs Pixii</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Area(s): strategy | Source: IDEA App 3 v3 Claude Analysis 17 May 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Matthew (via Claude Code)</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Folded in Context Delta 2026-05-25 + v2 Launch Roadmap (WhatsApp + Gen 3 Fathom transcripts)</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Added F-057..F-067; freemium reframe (F-019); F-052/R-013 resolved (split dev, 4/23); F-056 → deliberate non-goal; added R-016..R-019; reconciled Avatar Builder 4→5 stages (flagged); added P-011/P-012; sharpened R-001 to the Trust Gap + Signature validation bar; named StoryBrand + Pixii in R-014; added Alpha gates for Trust Gap / Signature / Decision Trigger; seeded the dated decision trail.</t>
         </is>
       </c>
     </row>
